--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -1446,7 +1446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1485,6 +1485,7 @@
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2300,19 +2301,19 @@
       <c r="A4" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="36">
         <v>15</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="36">
         <v>22</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="36">
         <v>30</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="36">
         <v>36</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="36">
         <v>40</v>
       </c>
     </row>
@@ -2330,19 +2331,19 @@
       <c r="A7" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>90000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>135960</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>190962</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>236029</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>270122</v>
       </c>
     </row>
@@ -2350,19 +2351,19 @@
       <c r="A8" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>3000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>4532</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>6365</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>7868</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>9004</v>
       </c>
     </row>
@@ -2370,19 +2371,19 @@
       <c r="A9" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>105000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>158620</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>222789</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>275367</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>315142</v>
       </c>
     </row>
@@ -2390,19 +2391,19 @@
       <c r="A10" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>3000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>3090</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>3183</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>3278</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>3377</v>
       </c>
     </row>
@@ -2410,23 +2411,23 @@
       <c r="A11" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>SUM(B7:B10)</f>
         <v>201000</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>SUM(C7:C10)</f>
         <v>302202</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <f>SUM(D7:D10)</f>
         <v>423299</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="33">
         <f>SUM(E7:E10)</f>
         <v>522542</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="33">
         <f>SUM(F7:F10)</f>
         <v>597645</v>
       </c>
@@ -2435,19 +2436,19 @@
       <c r="A13" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>13400</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>13736</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>14110</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>14515</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>14941</v>
       </c>
     </row>
@@ -2519,19 +2520,19 @@
       <c r="A5" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>13456</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>16632</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>17131</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>17645</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>18174</v>
       </c>
     </row>
@@ -2539,23 +2540,23 @@
       <c r="A6" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="32">
         <f>SUM(B5:B5)</f>
         <v>13456</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <f>SUM(C5:C5)</f>
         <v>16632</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="32">
         <f>SUM(D5:D5)</f>
         <v>17131</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>SUM(E5:E5)</f>
         <v>17645</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <f>SUM(F5:F5)</f>
         <v>18174</v>
       </c>
@@ -2574,19 +2575,19 @@
       <c r="A8" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>51060</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>63110</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>65003</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>66954</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>68962</v>
       </c>
     </row>
@@ -2594,23 +2595,23 @@
       <c r="A9" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="32">
         <f>SUM(B8:B8)</f>
         <v>51060</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C8:C8)</f>
         <v>63110</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D8:D8)</f>
         <v>65003</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E8:E8)</f>
         <v>66954</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F8:F8)</f>
         <v>68962</v>
       </c>
@@ -2619,23 +2620,23 @@
       <c r="A11" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>B6+B9</f>
         <v>64516</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>C6+C9</f>
         <v>79742</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <f>D6+D9</f>
         <v>82134</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="33">
         <f>E6+E9</f>
         <v>84598</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="33">
         <f>F6+F9</f>
         <v>87136</v>
       </c>
@@ -2708,19 +2709,19 @@
       <c r="A5" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>75000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>135960</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>190962</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>236029</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>270122</v>
       </c>
     </row>
@@ -2728,19 +2729,19 @@
       <c r="A6" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>2500</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>4532</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>6365</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>7868</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>9004</v>
       </c>
     </row>
@@ -2748,19 +2749,19 @@
       <c r="A7" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>87500</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>158620</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>222789</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>275367</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>315142</v>
       </c>
     </row>
@@ -2768,19 +2769,19 @@
       <c r="A8" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>2500</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>3090</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>3183</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>3278</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>3377</v>
       </c>
     </row>
@@ -2788,23 +2789,23 @@
       <c r="A9" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
         <v>167500</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
         <v>302202</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
         <v>423299</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
         <v>522542</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
         <v>597645</v>
       </c>
@@ -2823,19 +2824,19 @@
       <c r="A12" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <v>51060</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>63110</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>65003</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>66954</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>68962</v>
       </c>
     </row>
@@ -2843,19 +2844,19 @@
       <c r="A13" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>13456</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>16632</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>17131</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>17645</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>18174</v>
       </c>
     </row>
@@ -2863,23 +2864,23 @@
       <c r="A14" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>SUM(B12:B13)</f>
         <v>64516</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>SUM(C12:C13)</f>
         <v>79742</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>SUM(D12:D13)</f>
         <v>82134</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>SUM(E12:E13)</f>
         <v>84598</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>SUM(F12:F13)</f>
         <v>87136</v>
       </c>
@@ -2895,7 +2896,7 @@
       <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="37" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2903,24 +2904,24 @@
       <c r="A18" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <v>5000</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <v>9064</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <v>12731</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <v>15735</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <v>18008</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="37" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2928,24 +2929,24 @@
       <c r="A20" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="31">
         <v>3125</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>5665</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>7957</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>9835</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>11255</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="37" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2953,19 +2954,19 @@
       <c r="A22" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="31">
         <v>18000</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <v>22248</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <v>22915</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <v>23603</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <v>24311</v>
       </c>
     </row>
@@ -2973,19 +2974,19 @@
       <c r="A23" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="31">
         <v>2000</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <v>2472</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <v>2546</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <v>2623</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="31">
         <v>2701</v>
       </c>
     </row>
@@ -2993,19 +2994,19 @@
       <c r="A24" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="31">
         <v>1500</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <v>1854</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <v>1910</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <v>1967</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <v>2026</v>
       </c>
     </row>
@@ -3013,23 +3014,23 @@
       <c r="A25" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="32">
         <f>SUM(B22:B24)</f>
         <v>21500</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <f>SUM(C22:C24)</f>
         <v>26574</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <f>SUM(D22:D24)</f>
         <v>27371</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <f>SUM(E22:E24)</f>
         <v>28192</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <f>SUM(F22:F24)</f>
         <v>29038</v>
       </c>
@@ -3038,23 +3039,23 @@
       <c r="A26" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="32">
         <f>B18+B20+B25</f>
         <v>29625</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="32">
         <f>C18+C20+C25</f>
         <v>41303</v>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="32">
         <f>D18+D20+D25</f>
         <v>48059</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="32">
         <f>E18+E20+E25</f>
         <v>53762</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="32">
         <f>F18+F20+F25</f>
         <v>58301</v>
       </c>
@@ -3073,23 +3074,23 @@
       <c r="A29" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="B29" s="31" t="str">
+      <c r="B29" s="32" t="str">
         <f>SUM(B29:B28)</f>
         <v>0</v>
       </c>
-      <c r="C29" s="31" t="str">
+      <c r="C29" s="32" t="str">
         <f>SUM(C29:C28)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="31" t="str">
+      <c r="D29" s="32" t="str">
         <f>SUM(D29:D28)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="31" t="str">
+      <c r="E29" s="32" t="str">
         <f>SUM(E29:E28)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="31" t="str">
+      <c r="F29" s="32" t="str">
         <f>SUM(F29:F28)</f>
         <v>0</v>
       </c>
@@ -3152,23 +3153,23 @@
       <c r="A4" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="34">
         <f>'Budget Detail'!B9</f>
         <v>167500</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="34">
         <f>'Budget Detail'!C9</f>
         <v>302202</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="34">
         <f>'Budget Detail'!D9</f>
         <v>423299</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="34">
         <f>'Budget Detail'!E9</f>
         <v>522542</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="34">
         <f>'Budget Detail'!F9</f>
         <v>597645</v>
       </c>
@@ -3177,23 +3178,23 @@
       <c r="A5" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="34">
         <f>'Budget Detail'!B14</f>
         <v>64516</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="34">
         <f>'Budget Detail'!C14</f>
         <v>79742</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="34">
         <f>'Budget Detail'!D14</f>
         <v>82134</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="34">
         <f>'Budget Detail'!E14</f>
         <v>84598</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="34">
         <f>'Budget Detail'!F14</f>
         <v>87136</v>
       </c>
@@ -3202,23 +3203,23 @@
       <c r="A6" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="34">
         <f>'Budget Detail'!B26</f>
         <v>29625</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="34">
         <f>'Budget Detail'!C26</f>
         <v>41303</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="34">
         <f>'Budget Detail'!D26</f>
         <v>48059</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="34">
         <f>'Budget Detail'!E26</f>
         <v>53762</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="34">
         <f>'Budget Detail'!F26</f>
         <v>58301</v>
       </c>
@@ -3227,23 +3228,23 @@
       <c r="A7" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B7" s="33" t="str">
+      <c r="B7" s="34" t="str">
         <f>'Budget Detail'!B29</f>
         <v>0</v>
       </c>
-      <c r="C7" s="33" t="str">
+      <c r="C7" s="34" t="str">
         <f>'Budget Detail'!C29</f>
         <v>0</v>
       </c>
-      <c r="D7" s="33" t="str">
+      <c r="D7" s="34" t="str">
         <f>'Budget Detail'!D29</f>
         <v>0</v>
       </c>
-      <c r="E7" s="33" t="str">
+      <c r="E7" s="34" t="str">
         <f>'Budget Detail'!E29</f>
         <v>0</v>
       </c>
-      <c r="F7" s="33" t="str">
+      <c r="F7" s="34" t="str">
         <f>'Budget Detail'!F29</f>
         <v>0</v>
       </c>
@@ -3252,23 +3253,23 @@
       <c r="A8" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
         <v>94141</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>SUM(C5:C7)</f>
         <v>121045</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>SUM(D5:D7)</f>
         <v>130193</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>SUM(E5:E7)</f>
         <v>138361</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>SUM(F5:F7)</f>
         <v>145438</v>
       </c>
@@ -3287,23 +3288,23 @@
       <c r="A11" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>B4-B8</f>
         <v>73359</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>C4-C8</f>
         <v>181157</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <f>D4-D8</f>
         <v>293106</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="33">
         <f>E4-E8</f>
         <v>384182</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="33">
         <f>F4-F8</f>
         <v>452207</v>
       </c>
@@ -3337,19 +3338,19 @@
       <c r="A13" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>73359</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>254516</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>547622</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>931803</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>1384011</v>
       </c>
     </row>
@@ -3357,19 +3358,19 @@
       <c r="A14" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <v>11167</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>13736</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>14110</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>14515</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>14941</v>
       </c>
     </row>
@@ -3377,19 +3378,19 @@
       <c r="A15" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <v>6276</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>5502</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>4340</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>3843</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>3636</v>
       </c>
     </row>
@@ -3502,43 +3503,43 @@
       <c r="A4" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="32">
         <v>11050</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="32">
         <v>20050</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="32">
         <v>20050</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="32">
         <v>20050</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="32">
         <v>20050</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="32">
         <v>20050</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="32">
         <v>20050</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="32">
         <v>20050</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="32">
         <v>20050</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="32">
         <v>20050</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="32">
         <v>9250</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="32">
         <v>250</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="32">
         <f>SUM(B4:M4)</f>
         <v>201000</v>
       </c>
@@ -3565,43 +3566,43 @@
       <c r="A7" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>6452</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>6452</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>6452</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>6452</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>6452</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <v>6452</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <v>6452</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <v>6452</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="31">
         <v>6452</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="31">
         <v>6452</v>
       </c>
-      <c r="L7" s="30">
-        <v>0</v>
-      </c>
-      <c r="M7" s="30">
-        <v>0</v>
-      </c>
-      <c r="N7" s="30">
+      <c r="L7" s="31">
+        <v>0</v>
+      </c>
+      <c r="M7" s="31">
+        <v>0</v>
+      </c>
+      <c r="N7" s="31">
         <f>SUM(B7:M7)</f>
         <v>64516</v>
       </c>
@@ -3610,43 +3611,43 @@
       <c r="A8" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>2963</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>2963</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>2963</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>2963</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>2963</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <v>2963</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="31">
         <v>2963</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <v>2963</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="31">
         <v>2963</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="31">
         <v>2963</v>
       </c>
-      <c r="L8" s="30">
-        <v>0</v>
-      </c>
-      <c r="M8" s="30">
-        <v>0</v>
-      </c>
-      <c r="N8" s="30">
+      <c r="L8" s="31">
+        <v>0</v>
+      </c>
+      <c r="M8" s="31">
+        <v>0</v>
+      </c>
+      <c r="N8" s="31">
         <f>SUM(B8:M8)</f>
         <v>29625</v>
       </c>
@@ -3655,43 +3656,43 @@
       <c r="A9" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="B9" s="30">
-        <v>0</v>
-      </c>
-      <c r="C9" s="30">
-        <v>0</v>
-      </c>
-      <c r="D9" s="30">
-        <v>0</v>
-      </c>
-      <c r="E9" s="30">
-        <v>0</v>
-      </c>
-      <c r="F9" s="30">
-        <v>0</v>
-      </c>
-      <c r="G9" s="30">
-        <v>0</v>
-      </c>
-      <c r="H9" s="30">
-        <v>0</v>
-      </c>
-      <c r="I9" s="30">
-        <v>0</v>
-      </c>
-      <c r="J9" s="30">
-        <v>0</v>
-      </c>
-      <c r="K9" s="30">
-        <v>0</v>
-      </c>
-      <c r="L9" s="30">
-        <v>0</v>
-      </c>
-      <c r="M9" s="30">
-        <v>0</v>
-      </c>
-      <c r="N9" s="30" t="str">
+      <c r="B9" s="31">
+        <v>0</v>
+      </c>
+      <c r="C9" s="31">
+        <v>0</v>
+      </c>
+      <c r="D9" s="31">
+        <v>0</v>
+      </c>
+      <c r="E9" s="31">
+        <v>0</v>
+      </c>
+      <c r="F9" s="31">
+        <v>0</v>
+      </c>
+      <c r="G9" s="31">
+        <v>0</v>
+      </c>
+      <c r="H9" s="31">
+        <v>0</v>
+      </c>
+      <c r="I9" s="31">
+        <v>0</v>
+      </c>
+      <c r="J9" s="31">
+        <v>0</v>
+      </c>
+      <c r="K9" s="31">
+        <v>0</v>
+      </c>
+      <c r="L9" s="31">
+        <v>0</v>
+      </c>
+      <c r="M9" s="31">
+        <v>0</v>
+      </c>
+      <c r="N9" s="31" t="str">
         <f>SUM(B9:M9)</f>
         <v>0</v>
       </c>
@@ -3718,55 +3719,55 @@
       <c r="A12" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="34">
         <f>B7+B8+B9</f>
         <v>9415</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="34">
         <f>C7+C8+C9</f>
         <v>9415</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <f>D7+D8+D9</f>
         <v>9415</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>E7+E8+E9</f>
         <v>9415</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <f>F7+F8+F9</f>
         <v>9415</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="34">
         <f>G7+G8+G9</f>
         <v>9415</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="34">
         <f>H7+H8+H9</f>
         <v>9415</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="34">
         <f>I7+I8+I9</f>
         <v>9415</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="34">
         <f>J7+J8+J9</f>
         <v>9415</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="34">
         <f>K7+K8+K9</f>
         <v>9415</v>
       </c>
-      <c r="L12" s="33" t="str">
+      <c r="L12" s="34" t="str">
         <f>L7+L8+L9</f>
         <v>0</v>
       </c>
-      <c r="M12" s="33" t="str">
+      <c r="M12" s="34" t="str">
         <f>M7+M8+M9</f>
         <v>0</v>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="34">
         <f>SUM(B12:M12)</f>
         <v>94150</v>
       </c>
@@ -3775,55 +3776,55 @@
       <c r="A13" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="34">
         <f>B4-B12</f>
         <v>1635</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="34">
         <f>C4-C12</f>
         <v>10635</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="34">
         <f>D4-D12</f>
         <v>10635</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="34">
         <f>E4-E12</f>
         <v>10635</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="34">
         <f>F4-F12</f>
         <v>10635</v>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="34">
         <f>G4-G12</f>
         <v>10635</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="34">
         <f>H4-H12</f>
         <v>10635</v>
       </c>
-      <c r="I13" s="33">
+      <c r="I13" s="34">
         <f>I4-I12</f>
         <v>10635</v>
       </c>
-      <c r="J13" s="33">
+      <c r="J13" s="34">
         <f>J4-J12</f>
         <v>10635</v>
       </c>
-      <c r="K13" s="33">
+      <c r="K13" s="34">
         <f>K4-K12</f>
         <v>10635</v>
       </c>
-      <c r="L13" s="33">
+      <c r="L13" s="34">
         <f>L4-L12</f>
         <v>9250</v>
       </c>
-      <c r="M13" s="33">
+      <c r="M13" s="34">
         <f>M4-M12</f>
         <v>250</v>
       </c>
-      <c r="N13" s="33">
+      <c r="N13" s="34">
         <f>SUM(B13:M13)</f>
         <v>106850</v>
       </c>
@@ -3832,55 +3833,55 @@
       <c r="A14" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="38">
         <f>B17+B13</f>
         <v>1635</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="38">
         <f>B14+C13</f>
         <v>12270</v>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="38">
         <f>C14+D13</f>
         <v>22905</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="38">
         <f>D14+E13</f>
         <v>33540</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="38">
         <f>E14+F13</f>
         <v>44175</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="38">
         <f>F14+G13</f>
         <v>54810</v>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="38">
         <f>G14+H13</f>
         <v>65445</v>
       </c>
-      <c r="I14" s="37">
+      <c r="I14" s="38">
         <f>H14+I13</f>
         <v>76080</v>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="38">
         <f>I14+J13</f>
         <v>86715</v>
       </c>
-      <c r="K14" s="37">
+      <c r="K14" s="38">
         <f>J14+K13</f>
         <v>97350</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="38">
         <f>K14+L13</f>
         <v>106600</v>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="38">
         <f>L14+M13</f>
         <v>106850</v>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="33">
         <f>M14</f>
         <v>106850</v>
       </c>
@@ -3904,7 +3905,7 @@
       <c r="A18" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="38">
         <f>M14</f>
         <v>106850</v>
       </c>
@@ -3913,7 +3914,7 @@
       <c r="A19" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>MIN(B14:M14)</f>
         <v>1635</v>
       </c>
@@ -3983,22 +3984,22 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="32">
         <v>167500</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="32">
         <v>302202</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="32">
         <v>423299</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <v>522542</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <v>597645</v>
       </c>
     </row>
@@ -4016,19 +4017,19 @@
       <c r="A8" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="34">
         <v>64516</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <v>79742</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="34">
         <v>82134</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <v>84598</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <v>87136</v>
       </c>
     </row>
@@ -4036,19 +4037,19 @@
       <c r="A9" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="34">
         <v>29625</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <v>41303</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="34">
         <v>48059</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="34">
         <v>53762</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="34">
         <v>58301</v>
       </c>
     </row>
@@ -4056,43 +4057,43 @@
       <c r="A10" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33">
-        <v>0</v>
-      </c>
-      <c r="D10" s="33">
-        <v>0</v>
-      </c>
-      <c r="E10" s="33">
-        <v>0</v>
-      </c>
-      <c r="F10" s="33">
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34">
+        <v>0</v>
+      </c>
+      <c r="D10" s="34">
+        <v>0</v>
+      </c>
+      <c r="E10" s="34">
+        <v>0</v>
+      </c>
+      <c r="F10" s="34">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
         <v>242</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
         <f>SUM(B8:B10)</f>
         <v>94141</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>SUM(C8:C10)</f>
         <v>121045</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>SUM(D8:D10)</f>
         <v>130193</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>SUM(E8:E10)</f>
         <v>138361</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>SUM(F8:F10)</f>
         <v>145438</v>
       </c>
@@ -4108,26 +4109,26 @@
       <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="39" t="s">
         <v>244</v>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <f>B5-B11</f>
         <v>73359</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>C5-C11</f>
         <v>181157</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <f>D5-D11</f>
         <v>293106</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>E5-E11</f>
         <v>384182</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>F5-F11</f>
         <v>452207</v>
       </c>
@@ -4161,23 +4162,23 @@
       <c r="A16" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="34">
         <f>B14</f>
         <v>73359</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="34">
         <f>B16+C14</f>
         <v>254516</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="34">
         <f>C16+D14</f>
         <v>547622</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="34">
         <f>D16+E14</f>
         <v>931803</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="34">
         <f>E16+F14</f>
         <v>1384011</v>
       </c>
@@ -4186,19 +4187,19 @@
       <c r="A17" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="40" t="s">
         <v>276</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="41" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4267,19 +4268,19 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="44" t="s">
         <v>279</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="43" t="s">
         <v>210</v>
       </c>
     </row>
@@ -4351,23 +4352,23 @@
       <c r="A5" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="B5" s="44">
+      <c r="B5" s="45">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>106850</v>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>288007</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>581113</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>965294</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>1417502</v>
       </c>
@@ -4376,19 +4377,19 @@
       <c r="A6" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="B6" s="30">
-        <v>0</v>
-      </c>
-      <c r="C6" s="30">
-        <v>0</v>
-      </c>
-      <c r="D6" s="30">
-        <v>0</v>
-      </c>
-      <c r="E6" s="30">
-        <v>0</v>
-      </c>
-      <c r="F6" s="30">
+      <c r="B6" s="31">
+        <v>0</v>
+      </c>
+      <c r="C6" s="31">
+        <v>0</v>
+      </c>
+      <c r="D6" s="31">
+        <v>0</v>
+      </c>
+      <c r="E6" s="31">
+        <v>0</v>
+      </c>
+      <c r="F6" s="31">
         <v>0</v>
       </c>
     </row>
@@ -4396,19 +4397,19 @@
       <c r="A7" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>2000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>2000</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>2000</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>2000</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>2000</v>
       </c>
     </row>
@@ -4416,19 +4417,19 @@
       <c r="A8" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="B8" s="30">
-        <v>0</v>
-      </c>
-      <c r="C8" s="30">
-        <v>0</v>
-      </c>
-      <c r="D8" s="30">
-        <v>0</v>
-      </c>
-      <c r="E8" s="30">
-        <v>0</v>
-      </c>
-      <c r="F8" s="30">
+      <c r="B8" s="31">
+        <v>0</v>
+      </c>
+      <c r="C8" s="31">
+        <v>0</v>
+      </c>
+      <c r="D8" s="31">
+        <v>0</v>
+      </c>
+      <c r="E8" s="31">
+        <v>0</v>
+      </c>
+      <c r="F8" s="31">
         <v>0</v>
       </c>
     </row>
@@ -4436,23 +4437,23 @@
       <c r="A9" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
         <v>108850</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
         <v>290007</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
         <v>583113</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
         <v>967294</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
         <v>1419502</v>
       </c>
@@ -4471,19 +4472,19 @@
       <c r="A12" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="B12" s="30">
-        <v>0</v>
-      </c>
-      <c r="C12" s="30">
-        <v>0</v>
-      </c>
-      <c r="D12" s="30">
-        <v>0</v>
-      </c>
-      <c r="E12" s="30">
-        <v>0</v>
-      </c>
-      <c r="F12" s="30">
+      <c r="B12" s="31">
+        <v>0</v>
+      </c>
+      <c r="C12" s="31">
+        <v>0</v>
+      </c>
+      <c r="D12" s="31">
+        <v>0</v>
+      </c>
+      <c r="E12" s="31">
+        <v>0</v>
+      </c>
+      <c r="F12" s="31">
         <v>0</v>
       </c>
     </row>
@@ -4491,19 +4492,19 @@
       <c r="A13" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="B13" s="30">
-        <v>0</v>
-      </c>
-      <c r="C13" s="30">
-        <v>0</v>
-      </c>
-      <c r="D13" s="30">
-        <v>0</v>
-      </c>
-      <c r="E13" s="30">
-        <v>0</v>
-      </c>
-      <c r="F13" s="30">
+      <c r="B13" s="31">
+        <v>0</v>
+      </c>
+      <c r="C13" s="31">
+        <v>0</v>
+      </c>
+      <c r="D13" s="31">
+        <v>0</v>
+      </c>
+      <c r="E13" s="31">
+        <v>0</v>
+      </c>
+      <c r="F13" s="31">
         <v>0</v>
       </c>
     </row>
@@ -4511,23 +4512,23 @@
       <c r="A14" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B14" s="31" t="str">
+      <c r="B14" s="32" t="str">
         <f>SUM(B12:B13)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="31" t="str">
+      <c r="C14" s="32" t="str">
         <f>SUM(C12:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="31" t="str">
+      <c r="D14" s="32" t="str">
         <f>SUM(D12:D13)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="31" t="str">
+      <c r="E14" s="32" t="str">
         <f>SUM(E12:E13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="31" t="str">
+      <c r="F14" s="32" t="str">
         <f>SUM(F12:F13)</f>
         <v>0</v>
       </c>
@@ -4546,23 +4547,23 @@
       <c r="A17" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="33">
         <f>B9-B14</f>
         <v>108850</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>C9-C14</f>
         <v>290007</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="33">
         <f>D9-D14</f>
         <v>583113</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <f>E9-E14</f>
         <v>967294</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="33">
         <f>F9-F14</f>
         <v>1419502</v>
       </c>
@@ -4571,23 +4572,23 @@
       <c r="A19" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B19" s="45" t="str">
+      <c r="B19" s="46" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="45" t="str">
+      <c r="C19" s="46" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="45" t="str">
+      <c r="D19" s="46" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="45" t="str">
+      <c r="E19" s="46" t="str">
         <f>E9-E14-E17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="45" t="str">
+      <c r="F19" s="46" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -4660,19 +4661,19 @@
       <c r="A5" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>167500</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>302202</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>423299</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>522542</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>597645</v>
       </c>
     </row>
@@ -4680,19 +4681,19 @@
       <c r="A6" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>64516</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>79742</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>82134</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>84598</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>87136</v>
       </c>
     </row>
@@ -4700,19 +4701,19 @@
       <c r="A7" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>29625</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>41303</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>48059</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>53762</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>58301</v>
       </c>
     </row>
@@ -4720,23 +4721,23 @@
       <c r="A8" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="34">
         <f>B5-B6-B7</f>
         <v>73359</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <f>C5-C6-C7</f>
         <v>181157</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="34">
         <f>D5-D6-D7</f>
         <v>293106</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <f>E5-E6-E7</f>
         <v>384182</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <f>F5-F6-F7</f>
         <v>452207</v>
       </c>
@@ -4745,19 +4746,19 @@
       <c r="A9" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="B9" s="30">
-        <v>0</v>
-      </c>
-      <c r="C9" s="30">
-        <v>0</v>
-      </c>
-      <c r="D9" s="30">
-        <v>0</v>
-      </c>
-      <c r="E9" s="30">
-        <v>0</v>
-      </c>
-      <c r="F9" s="30">
+      <c r="B9" s="31">
+        <v>0</v>
+      </c>
+      <c r="C9" s="31">
+        <v>0</v>
+      </c>
+      <c r="D9" s="31">
+        <v>0</v>
+      </c>
+      <c r="E9" s="31">
+        <v>0</v>
+      </c>
+      <c r="F9" s="31">
         <v>0</v>
       </c>
     </row>
@@ -4765,19 +4766,19 @@
       <c r="A10" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="47" t="s">
         <v>300</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="47" t="s">
         <v>300</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="47" t="s">
         <v>300</v>
       </c>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="47" t="s">
         <v>300</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="47" t="s">
         <v>300</v>
       </c>
     </row>
@@ -4795,19 +4796,19 @@
       <c r="A13" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>106850</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>288007</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>581113</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>965294</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>1417502</v>
       </c>
     </row>
@@ -4815,23 +4816,23 @@
       <c r="A14" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="B14" s="47">
+      <c r="B14" s="48">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>414</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="48">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>868</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="48">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>1629</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="48">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>2546</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="48">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>3557</v>
       </c>
@@ -4840,23 +4841,23 @@
       <c r="A15" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
         <v>13.6</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
         <v>28.6</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
         <v>53.6</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
         <v>83.7</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
         <v>117</v>
       </c>
@@ -4895,19 +4896,19 @@
       <c r="A19" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <v>11167</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>13736</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>14110</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>14515</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>14941</v>
       </c>
     </row>
@@ -4915,19 +4916,19 @@
       <c r="A20" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="31">
         <v>64516</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>79742</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>82134</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>84598</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>87136</v>
       </c>
     </row>
@@ -4935,19 +4936,19 @@
       <c r="A21" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="31">
         <v>1975</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>1877</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>1602</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>1493</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>1458</v>
       </c>
     </row>
@@ -4955,19 +4956,19 @@
       <c r="A22" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="B22" s="48">
+      <c r="B22" s="49">
         <v>8</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="49">
         <v>7</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="49">
         <v>7</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="49">
         <v>7</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="49">
         <v>7</v>
       </c>
     </row>
@@ -4985,19 +4986,19 @@
       <c r="A25" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="B25" s="49" t="s">
+      <c r="B25" s="50" t="s">
         <v>300</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="50" t="s">
         <v>300</v>
       </c>
-      <c r="D25" s="49" t="s">
+      <c r="D25" s="50" t="s">
         <v>300</v>
       </c>
-      <c r="E25" s="49" t="s">
+      <c r="E25" s="50" t="s">
         <v>300</v>
       </c>
-      <c r="F25" s="49" t="s">
+      <c r="F25" s="50" t="s">
         <v>300</v>
       </c>
     </row>
@@ -5005,19 +5006,19 @@
       <c r="A26" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="B26" s="50" t="s">
+      <c r="B26" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="D26" s="50" t="s">
+      <c r="D26" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="E26" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="51" t="s">
         <v>312</v>
       </c>
     </row>
@@ -5025,19 +5026,19 @@
       <c r="A27" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="52" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="52" t="s">
         <v>314</v>
       </c>
-      <c r="D27" s="50" t="s">
+      <c r="D27" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="51" t="s">
         <v>312</v>
       </c>
     </row>
@@ -5045,19 +5046,19 @@
       <c r="A28" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="B28" s="50" t="s">
+      <c r="B28" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="C28" s="50" t="s">
+      <c r="C28" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="D28" s="50" t="s">
+      <c r="D28" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="E28" s="50" t="s">
+      <c r="E28" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="F28" s="50" t="s">
+      <c r="F28" s="51" t="s">
         <v>312</v>
       </c>
     </row>
@@ -5065,19 +5066,19 @@
       <c r="A29" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="D29" s="50" t="s">
+      <c r="D29" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="E29" s="50" t="s">
+      <c r="E29" s="51" t="s">
         <v>312</v>
       </c>
-      <c r="F29" s="50" t="s">
+      <c r="F29" s="51" t="s">
         <v>312</v>
       </c>
     </row>
@@ -5118,16 +5119,16 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="53" t="s">
         <v>317</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="53" t="s">
         <v>318</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="53" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5135,13 +5136,13 @@
       <c r="A4" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="31">
         <v>12000</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>12000</v>
       </c>
     </row>
@@ -5149,13 +5150,13 @@
       <c r="A6" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="33">
         <v>12000</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="33">
         <v>12000</v>
       </c>
     </row>
@@ -5163,7 +5164,7 @@
       <c r="A7" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="46">
         <v>0</v>
       </c>
     </row>
@@ -5556,19 +5557,19 @@
       <c r="A6" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>167500</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>302202</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>423299</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>522542</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>597645</v>
       </c>
     </row>
@@ -5576,19 +5577,19 @@
       <c r="A7" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>94141</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>121045</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>130193</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>138361</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>145438</v>
       </c>
     </row>
@@ -5596,19 +5597,19 @@
       <c r="A8" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="33">
         <v>73359</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <v>181157</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="33">
         <v>293106</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="33">
         <v>384182</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="33">
         <v>452207</v>
       </c>
     </row>
@@ -5636,19 +5637,19 @@
       <c r="A10" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="D10" s="53" t="s">
+      <c r="D10" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="E10" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="54" t="s">
         <v>300</v>
       </c>
     </row>
@@ -5656,19 +5657,19 @@
       <c r="A11" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="48">
         <v>8</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="48">
         <v>7</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="48">
         <v>7</v>
       </c>
-      <c r="E11" s="47">
+      <c r="E11" s="48">
         <v>7</v>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="48">
         <v>7</v>
       </c>
     </row>
@@ -5711,19 +5712,19 @@
       <c r="A16" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="31">
         <v>125625</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>226652</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>317474</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>391907</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>448234</v>
       </c>
     </row>
@@ -5731,19 +5732,19 @@
       <c r="A17" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <v>94141</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>121045</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>130193</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>138361</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>145438</v>
       </c>
     </row>
@@ -5751,19 +5752,19 @@
       <c r="A18" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="33">
         <v>31484</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <v>105606</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <v>187281</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <v>253546</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <v>302796</v>
       </c>
     </row>
@@ -5791,19 +5792,19 @@
       <c r="A20" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="E20" s="53" t="s">
+      <c r="E20" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="F20" s="53" t="s">
+      <c r="F20" s="54" t="s">
         <v>300</v>
       </c>
     </row>
@@ -5811,19 +5812,19 @@
       <c r="A21" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="B21" s="47">
+      <c r="B21" s="48">
         <v>8</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="48">
         <v>8</v>
       </c>
-      <c r="D21" s="47">
+      <c r="D21" s="48">
         <v>8</v>
       </c>
-      <c r="E21" s="47">
+      <c r="E21" s="48">
         <v>7</v>
       </c>
-      <c r="F21" s="47">
+      <c r="F21" s="48">
         <v>7</v>
       </c>
     </row>
@@ -5941,19 +5942,19 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="54" t="s">
+      <c r="E12" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="F12" s="54" t="s">
+      <c r="F12" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="54" t="s">
+      <c r="G12" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="54" t="s">
+      <c r="H12" s="55" t="s">
         <v>106</v>
       </c>
     </row>
@@ -5961,19 +5962,19 @@
       <c r="A13" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>167500</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>302202</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>423299</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <v>522542</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <v>597645</v>
       </c>
     </row>
@@ -5981,19 +5982,19 @@
       <c r="A14" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>94141</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>121045</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>130193</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <v>138361</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <v>145438</v>
       </c>
     </row>
@@ -6001,19 +6002,19 @@
       <c r="A15" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>73359</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>181157</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>293106</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <v>384182</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <v>452207</v>
       </c>
     </row>
@@ -6021,19 +6022,19 @@
       <c r="A16" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>106850</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>288007</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>581113</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <v>965294</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="31">
         <v>1417502</v>
       </c>
     </row>
@@ -6041,19 +6042,19 @@
       <c r="A17" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="D17" s="30">
-        <v>0</v>
-      </c>
-      <c r="E17" s="30">
-        <v>0</v>
-      </c>
-      <c r="F17" s="30">
-        <v>0</v>
-      </c>
-      <c r="G17" s="30">
-        <v>0</v>
-      </c>
-      <c r="H17" s="30">
+      <c r="D17" s="31">
+        <v>0</v>
+      </c>
+      <c r="E17" s="31">
+        <v>0</v>
+      </c>
+      <c r="F17" s="31">
+        <v>0</v>
+      </c>
+      <c r="G17" s="31">
+        <v>0</v>
+      </c>
+      <c r="H17" s="31">
         <v>0</v>
       </c>
     </row>
@@ -6079,19 +6080,19 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="54" t="s">
+      <c r="D20" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="54" t="s">
+      <c r="E20" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="54" t="s">
+      <c r="F20" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="54" t="s">
+      <c r="G20" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="H20" s="54" t="s">
+      <c r="H20" s="55" t="s">
         <v>106</v>
       </c>
     </row>
@@ -6119,19 +6120,19 @@
       <c r="A22" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="D22" s="53" t="s">
+      <c r="D22" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="E22" s="53" t="s">
+      <c r="E22" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="F22" s="53" t="s">
+      <c r="F22" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="G22" s="53" t="s">
+      <c r="G22" s="54" t="s">
         <v>300</v>
       </c>
-      <c r="H22" s="53" t="s">
+      <c r="H22" s="54" t="s">
         <v>300</v>
       </c>
     </row>
@@ -6159,19 +6160,19 @@
       <c r="A24" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="D24" s="47">
+      <c r="D24" s="48">
         <v>15</v>
       </c>
-      <c r="E24" s="47">
+      <c r="E24" s="48">
         <v>22</v>
       </c>
-      <c r="F24" s="47">
+      <c r="F24" s="48">
         <v>30</v>
       </c>
-      <c r="G24" s="47">
+      <c r="G24" s="48">
         <v>36</v>
       </c>
-      <c r="H24" s="47">
+      <c r="H24" s="48">
         <v>40</v>
       </c>
     </row>
@@ -6228,24 +6229,24 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="56" t="s">
         <v>340</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="57" t="s">
         <v>341</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D4" s="58" t="s">
         <v>342</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="59" t="s">
         <v>343</v>
       </c>
     </row>
@@ -6253,22 +6254,22 @@
       <c r="B6" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="60" t="s">
         <v>345</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="60" t="s">
         <v>346</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="60" t="s">
         <v>347</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="60" t="s">
         <v>348</v>
       </c>
-      <c r="G6" s="59" t="s">
+      <c r="G6" s="60" t="s">
         <v>349</v>
       </c>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="60" t="s">
         <v>350</v>
       </c>
     </row>
@@ -6276,19 +6277,19 @@
       <c r="B7" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="C7" s="60">
+      <c r="C7" s="61">
         <v>15</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="61">
         <v>22</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E7" s="61">
         <v>30</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="61">
         <v>36</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="61">
         <v>40</v>
       </c>
     </row>
@@ -6296,19 +6297,19 @@
       <c r="B8" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="C8" s="61">
+      <c r="C8" s="62">
         <v>167500</v>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="62">
         <v>302202</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="62">
         <v>423299.1</v>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="62">
         <v>522542.0514</v>
       </c>
-      <c r="G8" s="61">
+      <c r="G8" s="62">
         <v>597645.1781100001</v>
       </c>
     </row>
@@ -6316,19 +6317,19 @@
       <c r="B9" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="62">
         <v>64516.25</v>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="62">
         <v>79742.085</v>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="62">
         <v>82134.34754999999</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="62">
         <v>84598.3779765</v>
       </c>
-      <c r="G9" s="61">
+      <c r="G9" s="62">
         <v>87136.32931579501</v>
       </c>
     </row>
@@ -6336,19 +6337,19 @@
       <c r="B10" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="C10" s="61">
+      <c r="C10" s="62">
         <v>29625</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="62">
         <v>41303</v>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="62">
         <v>48058.77</v>
       </c>
-      <c r="F10" s="61">
+      <c r="F10" s="62">
         <v>53762.168399999995</v>
       </c>
-      <c r="G10" s="61">
+      <c r="G10" s="62">
         <v>58301.35635800001</v>
       </c>
     </row>
@@ -6356,19 +6357,19 @@
       <c r="B11" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="C11" s="61">
-        <v>0</v>
-      </c>
-      <c r="D11" s="61">
-        <v>0</v>
-      </c>
-      <c r="E11" s="61">
-        <v>0</v>
-      </c>
-      <c r="F11" s="61">
-        <v>0</v>
-      </c>
-      <c r="G11" s="61">
+      <c r="C11" s="62">
+        <v>0</v>
+      </c>
+      <c r="D11" s="62">
+        <v>0</v>
+      </c>
+      <c r="E11" s="62">
+        <v>0</v>
+      </c>
+      <c r="F11" s="62">
+        <v>0</v>
+      </c>
+      <c r="G11" s="62">
         <v>0</v>
       </c>
     </row>
@@ -6376,19 +6377,19 @@
       <c r="B12" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C12" s="62">
+      <c r="C12" s="63">
         <v>73358.75</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="63">
         <v>181156.91499999998</v>
       </c>
-      <c r="E12" s="62">
+      <c r="E12" s="63">
         <v>293105.98245</v>
       </c>
-      <c r="F12" s="62">
+      <c r="F12" s="63">
         <v>384181.5050235</v>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="63">
         <v>452207.49243620504</v>
       </c>
     </row>
@@ -6396,19 +6397,19 @@
       <c r="B13" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="C13" s="62">
+      <c r="C13" s="63">
         <v>106850</v>
       </c>
-      <c r="D13" s="62">
+      <c r="D13" s="63">
         <v>288006.915</v>
       </c>
-      <c r="E13" s="62">
+      <c r="E13" s="63">
         <v>581112.89745</v>
       </c>
-      <c r="F13" s="62">
+      <c r="F13" s="63">
         <v>965294.4024735</v>
       </c>
-      <c r="G13" s="62">
+      <c r="G13" s="63">
         <v>1417501.894909705</v>
       </c>
     </row>
@@ -6416,19 +6417,19 @@
       <c r="B14" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="C14" s="63">
+      <c r="C14" s="64">
         <v>0.4379626865671642</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="64">
         <v>0.5994563735514655</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="64">
         <v>0.6924323308270677</v>
       </c>
-      <c r="F14" s="63">
+      <c r="F14" s="64">
         <v>0.7352164366373902</v>
       </c>
-      <c r="G14" s="63">
+      <c r="G14" s="64">
         <v>0.7566487758945385</v>
       </c>
     </row>
@@ -6436,22 +6437,22 @@
       <c r="B15" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="C15" s="64">
+      <c r="C15" s="65">
         <v>11166.666666666666</v>
       </c>
-      <c r="D15" s="64">
+      <c r="D15" s="65">
         <v>13736.454545454546</v>
       </c>
-      <c r="E15" s="64">
+      <c r="E15" s="65">
         <v>14109.97</v>
       </c>
-      <c r="F15" s="64">
+      <c r="F15" s="65">
         <v>14515.056983333334</v>
       </c>
-      <c r="G15" s="64">
+      <c r="G15" s="65">
         <v>14941.129452750003</v>
       </c>
-      <c r="H15" s="65" t="s">
+      <c r="H15" s="66" t="s">
         <v>351</v>
       </c>
     </row>
@@ -6459,22 +6460,22 @@
       <c r="B16" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="C16" s="63">
+      <c r="C16" s="64">
         <v>0.3851716417910448</v>
       </c>
-      <c r="D16" s="63">
+      <c r="D16" s="64">
         <v>0.26387014314928425</v>
       </c>
-      <c r="E16" s="63">
+      <c r="E16" s="64">
         <v>0.19403383458646614</v>
       </c>
-      <c r="F16" s="63">
+      <c r="F16" s="64">
         <v>0.1618977415307403</v>
       </c>
-      <c r="G16" s="63">
+      <c r="G16" s="64">
         <v>0.14579943502824858</v>
       </c>
-      <c r="H16" s="65" t="s">
+      <c r="H16" s="66" t="s">
         <v>353</v>
       </c>
     </row>
@@ -6482,22 +6483,22 @@
       <c r="B17" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="C17" s="66">
+      <c r="C17" s="67">
         <v>0.15402985074626865</v>
       </c>
-      <c r="D17" s="63">
+      <c r="D17" s="64">
         <v>0.08793456032719836</v>
       </c>
-      <c r="E17" s="63">
+      <c r="E17" s="64">
         <v>0.06466165413533834</v>
       </c>
-      <c r="F17" s="63">
+      <c r="F17" s="64">
         <v>0.053952321204516936</v>
       </c>
-      <c r="G17" s="63">
+      <c r="G17" s="64">
         <v>0.04858757062146892</v>
       </c>
-      <c r="H17" s="65" t="s">
+      <c r="H17" s="66" t="s">
         <v>355</v>
       </c>
     </row>
@@ -6505,22 +6506,22 @@
       <c r="B18" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="63">
+      <c r="C18" s="64">
         <v>0.4379626865671642</v>
       </c>
-      <c r="D18" s="63">
+      <c r="D18" s="64">
         <v>0.5994563735514655</v>
       </c>
-      <c r="E18" s="63">
+      <c r="E18" s="64">
         <v>0.6924323308270676</v>
       </c>
-      <c r="F18" s="63">
+      <c r="F18" s="64">
         <v>0.7352164366373901</v>
       </c>
-      <c r="G18" s="63">
+      <c r="G18" s="64">
         <v>0.7566487758945386</v>
       </c>
-      <c r="H18" s="65" t="s">
+      <c r="H18" s="66" t="s">
         <v>357</v>
       </c>
     </row>
@@ -6528,22 +6529,22 @@
       <c r="B19" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="C19" s="67">
+      <c r="C19" s="68">
         <v>3</v>
       </c>
-      <c r="D19" s="67">
+      <c r="D19" s="68">
         <v>3</v>
       </c>
-      <c r="E19" s="67">
+      <c r="E19" s="68">
         <v>3</v>
       </c>
-      <c r="F19" s="67">
+      <c r="F19" s="68">
         <v>3</v>
       </c>
-      <c r="G19" s="67">
+      <c r="G19" s="68">
         <v>3</v>
       </c>
-      <c r="H19" s="65" t="s">
+      <c r="H19" s="66" t="s">
         <v>359</v>
       </c>
     </row>
@@ -6551,22 +6552,22 @@
       <c r="B20" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="C20" s="68" t="s">
+      <c r="C20" s="69" t="s">
         <v>300</v>
       </c>
-      <c r="D20" s="68" t="s">
+      <c r="D20" s="69" t="s">
         <v>300</v>
       </c>
-      <c r="E20" s="68" t="s">
+      <c r="E20" s="69" t="s">
         <v>300</v>
       </c>
-      <c r="F20" s="68" t="s">
+      <c r="F20" s="69" t="s">
         <v>300</v>
       </c>
-      <c r="G20" s="68" t="s">
+      <c r="G20" s="69" t="s">
         <v>300</v>
       </c>
-      <c r="H20" s="65" t="s">
+      <c r="H20" s="66" t="s">
         <v>300</v>
       </c>
     </row>
@@ -6574,27 +6575,27 @@
       <c r="B21" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="C21" s="39" t="str">
+      <c r="C21" s="40" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="69" t="str">
+      <c r="D21" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="69" t="str">
+      <c r="E21" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="69" t="str">
+      <c r="F21" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="69" t="str">
+      <c r="G21" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="65" t="s">
+      <c r="H21" s="66" t="s">
         <v>345</v>
       </c>
     </row>
@@ -6602,22 +6603,22 @@
       <c r="B22" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="C22" s="70">
+      <c r="C22" s="71">
         <v>14</v>
       </c>
-      <c r="D22" s="67">
+      <c r="D22" s="68">
         <v>29</v>
       </c>
-      <c r="E22" s="67">
+      <c r="E22" s="68">
         <v>54</v>
       </c>
-      <c r="F22" s="71" t="s">
+      <c r="F22" s="72" t="s">
         <v>362</v>
       </c>
-      <c r="G22" s="71" t="s">
+      <c r="G22" s="72" t="s">
         <v>362</v>
       </c>
-      <c r="H22" s="65" t="s">
+      <c r="H22" s="66" t="s">
         <v>363</v>
       </c>
     </row>
@@ -6639,109 +6640,109 @@
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="42" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="D25" s="72" t="s">
+      <c r="D25" s="73" t="s">
         <v>370</v>
       </c>
-      <c r="E25" s="72"/>
-      <c r="F25" s="73" t="s">
+      <c r="E25" s="73"/>
+      <c r="F25" s="74" t="s">
         <v>371</v>
       </c>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="42" t="s">
         <v>372</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="D26" s="72" t="s">
+      <c r="D26" s="73" t="s">
         <v>373</v>
       </c>
-      <c r="E26" s="72"/>
-      <c r="F26" s="73" t="s">
+      <c r="E26" s="73"/>
+      <c r="F26" s="74" t="s">
         <v>374</v>
       </c>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="42" t="s">
         <v>375</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="D27" s="72" t="s">
+      <c r="D27" s="73" t="s">
         <v>376</v>
       </c>
-      <c r="E27" s="72"/>
-      <c r="F27" s="73" t="s">
+      <c r="E27" s="73"/>
+      <c r="F27" s="74" t="s">
         <v>377</v>
       </c>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="42" t="s">
         <v>378</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="D28" s="72" t="s">
+      <c r="D28" s="73" t="s">
         <v>379</v>
       </c>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73" t="s">
+      <c r="E28" s="73"/>
+      <c r="F28" s="74" t="s">
         <v>380</v>
       </c>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="42" t="s">
         <v>381</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="D29" s="72" t="s">
+      <c r="D29" s="73" t="s">
         <v>382</v>
       </c>
-      <c r="E29" s="72"/>
-      <c r="F29" s="73" t="s">
+      <c r="E29" s="73"/>
+      <c r="F29" s="74" t="s">
         <v>383</v>
       </c>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="42" t="s">
         <v>384</v>
       </c>
-      <c r="C30" s="39" t="s">
+      <c r="C30" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="D30" s="72" t="s">
+      <c r="D30" s="73" t="s">
         <v>385</v>
       </c>
-      <c r="E30" s="72"/>
-      <c r="F30" s="73" t="s">
+      <c r="E30" s="73"/>
+      <c r="F30" s="74" t="s">
         <v>386</v>
       </c>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="42" t="s">
         <v>387</v>
       </c>
       <c r="C32" s="10" t="s">
@@ -6752,15 +6753,15 @@
       <c r="F32" s="10"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="74" t="s">
+      <c r="B34" s="75" t="s">
         <v>389</v>
       </c>
-      <c r="C34" s="74"/>
-      <c r="D34" s="74"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="74"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -7803,19 +7804,24 @@
       <c r="A14" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="30">
+        <f>Assumptions!B51</f>
         <v>3</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="30">
+        <f>Assumptions!C51</f>
         <v>4</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="30">
+        <f>Assumptions!D51</f>
         <v>5</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="30">
+        <f>Assumptions!E51</f>
         <v>6</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="30">
+        <f>Assumptions!F51</f>
         <v>6</v>
       </c>
     </row>
@@ -7823,19 +7829,24 @@
       <c r="A15" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="30">
+        <f>Assumptions!B52</f>
         <v>2</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="30">
+        <f>Assumptions!C52</f>
         <v>3</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="30">
+        <f>Assumptions!D52</f>
         <v>4</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="30">
+        <f>Assumptions!E52</f>
         <v>5</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="30">
+        <f>Assumptions!F52</f>
         <v>5</v>
       </c>
     </row>
@@ -7843,19 +7854,24 @@
       <c r="A16" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="30">
+        <f>Assumptions!B53</f>
         <v>5</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="30">
+        <f>Assumptions!C53</f>
         <v>7</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="30">
+        <f>Assumptions!D53</f>
         <v>9</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="30">
+        <f>Assumptions!E53</f>
         <v>10</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="30">
+        <f>Assumptions!F53</f>
         <v>12</v>
       </c>
     </row>
@@ -7864,18 +7880,23 @@
         <v>183</v>
       </c>
       <c r="B17" s="27">
+        <f>B14+B15+B16</f>
         <v>10</v>
       </c>
       <c r="C17" s="27">
+        <f>C14+C15+C16</f>
         <v>14</v>
       </c>
       <c r="D17" s="27">
+        <f>D14+D15+D16</f>
         <v>18</v>
       </c>
       <c r="E17" s="27">
+        <f>E14+E15+E16</f>
         <v>21</v>
       </c>
       <c r="F17" s="27">
+        <f>F14+F15+F16</f>
         <v>23</v>
       </c>
     </row>
@@ -7884,18 +7905,23 @@
         <v>184</v>
       </c>
       <c r="B18" s="28">
-        <v>0.6666666666666666</v>
+        <f>IF(B6=0,0,B17/B6)</f>
+        <v>0.66666667</v>
       </c>
       <c r="C18" s="28">
-        <v>0.6363636363636364</v>
+        <f>IF(C6=0,0,C17/C6)</f>
+        <v>0.63636364</v>
       </c>
       <c r="D18" s="28">
+        <f>IF(D6=0,0,D17/D6)</f>
         <v>0.6</v>
       </c>
       <c r="E18" s="28">
-        <v>0.5833333333333334</v>
+        <f>IF(E6=0,0,E17/E6)</f>
+        <v>0.58333333</v>
       </c>
       <c r="F18" s="28">
+        <f>IF(F6=0,0,F17/F6)</f>
         <v>0.575</v>
       </c>
     </row>
@@ -7967,19 +7993,19 @@
       <c r="A5" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>90000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>135960</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>190962</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>236029</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>270122</v>
       </c>
     </row>
@@ -7987,19 +8013,19 @@
       <c r="A6" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>3000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>4532</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>6365</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>7868</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>9004</v>
       </c>
     </row>
@@ -8007,23 +8033,23 @@
       <c r="A7" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="32">
         <f>SUM(B5,B6)</f>
         <v>93000</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>SUM(C5,C6)</f>
         <v>140492</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>SUM(D5,D6)</f>
         <v>197327</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>SUM(E5,E6)</f>
         <v>243897</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>SUM(F5,F6)</f>
         <v>279126</v>
       </c>
@@ -8042,19 +8068,19 @@
       <c r="A9" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>105000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>158620</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>222789</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>275367</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>315142</v>
       </c>
     </row>
@@ -8062,23 +8088,23 @@
       <c r="A10" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="32">
         <f>SUM(B9)</f>
         <v>105000</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>SUM(C9)</f>
         <v>158620</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>SUM(D9)</f>
         <v>222789</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>SUM(E9)</f>
         <v>275367</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>SUM(F9)</f>
         <v>315142</v>
       </c>
@@ -8100,16 +8126,16 @@
       <c r="B12" s="23">
         <v>3000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>3090</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>3183</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>3278</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>3377</v>
       </c>
     </row>
@@ -8117,23 +8143,23 @@
       <c r="A13" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="32">
         <f>SUM(B12)</f>
         <v>3000</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>SUM(C12)</f>
         <v>3090</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>SUM(D12)</f>
         <v>3183</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>SUM(E12)</f>
         <v>3278</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>SUM(F12)</f>
         <v>3377</v>
       </c>
@@ -8142,23 +8168,23 @@
       <c r="A15" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="33">
         <f>SUM(B7,B10,B13)</f>
         <v>201000</v>
       </c>
-      <c r="C15" s="32">
+      <c r="C15" s="33">
         <f>SUM(C7,C10,C13)</f>
         <v>302202</v>
       </c>
-      <c r="D15" s="32">
+      <c r="D15" s="33">
         <f>SUM(D7,D10,D13)</f>
         <v>423299</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="33">
         <f>SUM(E7,E10,E13)</f>
         <v>522542</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="33">
         <f>SUM(F7,F10,F13)</f>
         <v>597645</v>
       </c>
@@ -8244,7 +8270,7 @@
       <c r="F4" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="34">
         <v>61272</v>
       </c>
     </row>
@@ -8267,7 +8293,7 @@
       <c r="F5" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="34">
         <v>16148</v>
       </c>
     </row>
@@ -8306,19 +8332,19 @@
       <c r="A9" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B9" s="32">
+      <c r="B9" s="33">
         <v>64516</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <v>79742</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <v>82134</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <v>84598</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <v>87136</v>
       </c>
     </row>
@@ -8346,19 +8372,19 @@
       <c r="A11" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="35">
         <v>10</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="35">
         <v>14.7</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="35">
         <v>20</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="35">
         <v>24</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="35">
         <v>26.7</v>
       </c>
     </row>
@@ -8430,19 +8456,19 @@
       <c r="A5" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>6000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>9064</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>12731</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>15735</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>18008</v>
       </c>
     </row>
@@ -8450,23 +8476,23 @@
       <c r="A6" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="32">
         <f>SUM(B5:B5)</f>
         <v>6000</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <f>SUM(C5:C5)</f>
         <v>9064</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="32">
         <f>SUM(D5:D5)</f>
         <v>12731</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>SUM(E5:E5)</f>
         <v>15735</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <f>SUM(F5:F5)</f>
         <v>18008</v>
       </c>
@@ -8485,19 +8511,19 @@
       <c r="A8" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>3750</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>5665</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>7957</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>9835</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>11255</v>
       </c>
     </row>
@@ -8505,23 +8531,23 @@
       <c r="A9" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="32">
         <f>SUM(B8:B8)</f>
         <v>3750</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C8:C8)</f>
         <v>5665</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D8:D8)</f>
         <v>7957</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E8:E8)</f>
         <v>9835</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F8:F8)</f>
         <v>11255</v>
       </c>
@@ -8540,19 +8566,19 @@
       <c r="A11" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <v>21600</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>22248</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>22915</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>23603</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>24311</v>
       </c>
     </row>
@@ -8560,19 +8586,19 @@
       <c r="A12" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <v>2400</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>2472</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>2546</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>2623</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>2701</v>
       </c>
     </row>
@@ -8580,19 +8606,19 @@
       <c r="A13" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>1800</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>1854</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>1910</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>1967</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>2026</v>
       </c>
     </row>
@@ -8600,23 +8626,23 @@
       <c r="A14" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>SUM(B11:B13)</f>
         <v>25800</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>SUM(C11:C13)</f>
         <v>26574</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>SUM(D11:D13)</f>
         <v>27371</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>SUM(E11:E13)</f>
         <v>28192</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>SUM(F11:F13)</f>
         <v>29038</v>
       </c>
@@ -8625,23 +8651,23 @@
       <c r="A16" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="33">
         <f>B6+B9+B14</f>
         <v>35550</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="33">
         <f>C6+C9+C14</f>
         <v>41303</v>
       </c>
-      <c r="D16" s="32">
+      <c r="D16" s="33">
         <f>D6+D9+D14</f>
         <v>48059</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="33">
         <f>E6+E9+E14</f>
         <v>53762</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="33">
         <f>F6+F9+F14</f>
         <v>58301</v>
       </c>
@@ -8705,7 +8731,7 @@
       <c r="A5" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="33">
         <v>0</v>
       </c>
     </row>
@@ -8713,7 +8739,7 @@
       <c r="A6" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <v>0</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="392">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -688,43 +688,49 @@
     <t>Staffing Costs Forecast</t>
   </si>
   <si>
+    <t xml:space="preserve">  Assistant Educator [0.5 FTE]</t>
+  </si>
+  <si>
+    <t>Total Instructional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Director / Lead Educator [1 FTE]</t>
+  </si>
+  <si>
+    <t>Total School Leadership</t>
+  </si>
+  <si>
+    <t>TOTAL PERSONNEL</t>
+  </si>
+  <si>
+    <t>Liberty Learning Co-Op - Budget Detail</t>
+  </si>
+  <si>
+    <t>REVENUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Co-Op Tuition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Materials Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ESA Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Annual Fundraising</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>PERSONNEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Director / Lead Educator</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Assistant Educator</t>
-  </si>
-  <si>
-    <t>Total Instructional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Director / Lead Educator</t>
-  </si>
-  <si>
-    <t>Total School Leadership</t>
-  </si>
-  <si>
-    <t>TOTAL PERSONNEL</t>
-  </si>
-  <si>
-    <t>Liberty Learning Co-Op - Budget Detail</t>
-  </si>
-  <si>
-    <t>REVENUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Co-Op Tuition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Materials Fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ESA Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Annual Fundraising</t>
-  </si>
-  <si>
-    <t>Total Revenue</t>
-  </si>
-  <si>
-    <t>PERSONNEL</t>
   </si>
   <si>
     <t xml:space="preserve">    Curriculum &amp; Materials</t>
@@ -2822,7 +2828,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="B12" s="31">
         <v>51060</v>
@@ -2842,7 +2848,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B13" s="31">
         <v>13456</v>
@@ -2902,7 +2908,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B18" s="31">
         <v>5000</v>
@@ -2927,7 +2933,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B20" s="31">
         <v>3125</v>
@@ -2952,7 +2958,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B22" s="31">
         <v>18000</v>
@@ -2972,7 +2978,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B23" s="31">
         <v>2000</v>
@@ -2992,7 +2998,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B24" s="31">
         <v>1500</v>
@@ -3012,7 +3018,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B25" s="32">
         <f>SUM(B22:B24)</f>
@@ -3037,7 +3043,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B26" s="32">
         <f>B18+B20+B25</f>
@@ -3062,7 +3068,7 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -3072,7 +3078,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B29" s="32" t="str">
         <f>SUM(B29:B28)</f>
@@ -3121,7 +3127,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3201,7 +3207,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B6" s="34">
         <f>'Budget Detail'!B26</f>
@@ -3226,7 +3232,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B7" s="34" t="str">
         <f>'Budget Detail'!B29</f>
@@ -3251,7 +3257,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
@@ -3276,7 +3282,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -3286,7 +3292,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B11" s="33">
         <f>B4-B8</f>
@@ -3311,7 +3317,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3336,7 +3342,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B13" s="31">
         <v>73359</v>
@@ -3376,7 +3382,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B15" s="31">
         <v>6276</v>
@@ -3421,7 +3427,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3442,43 +3448,43 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3546,7 +3552,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -3564,7 +3570,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B7" s="31">
         <v>6452</v>
@@ -3609,7 +3615,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B8" s="31">
         <v>2963</v>
@@ -3654,7 +3660,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B9" s="31">
         <v>0</v>
@@ -3699,7 +3705,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -3717,7 +3723,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B12" s="34">
         <f>B7+B8+B9</f>
@@ -3774,7 +3780,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B13" s="34">
         <f>B4-B12</f>
@@ -3831,7 +3837,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B14" s="38">
         <f>B17+B13</f>
@@ -3888,7 +3894,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -3903,7 +3909,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B18" s="38">
         <f>M14</f>
@@ -3912,7 +3918,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B19" s="31">
         <f>MIN(B14:M14)</f>
@@ -3945,7 +3951,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4005,7 +4011,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4015,7 +4021,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B8" s="34">
         <v>64516</v>
@@ -4035,7 +4041,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B9" s="34">
         <v>29625</v>
@@ -4055,7 +4061,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B10" s="34">
         <v>0</v>
@@ -4075,7 +4081,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B11" s="32">
         <f>SUM(B8:B10)</f>
@@ -4100,7 +4106,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -4110,7 +4116,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B14" s="33">
         <f>B5-B11</f>
@@ -4135,7 +4141,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B15" s="29">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4160,7 +4166,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B16" s="34">
         <f>B14</f>
@@ -4185,10 +4191,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C17" s="41" t="s">
         <v>7</v>
@@ -4259,7 +4265,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4269,16 +4275,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B5" s="43" t="s">
         <v>147</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E5" s="43" t="s">
         <v>210</v>
@@ -4310,7 +4316,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4340,7 +4346,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4350,7 +4356,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B5" s="45">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -4375,7 +4381,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B6" s="31">
         <v>0</v>
@@ -4395,7 +4401,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B7" s="31">
         <v>2000</v>
@@ -4415,7 +4421,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B8" s="31">
         <v>0</v>
@@ -4435,7 +4441,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
@@ -4460,7 +4466,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4470,7 +4476,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B12" s="31">
         <v>0</v>
@@ -4490,7 +4496,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B13" s="31">
         <v>0</v>
@@ -4510,7 +4516,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B14" s="32" t="str">
         <f>SUM(B12:B13)</f>
@@ -4535,7 +4541,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4545,7 +4551,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B17" s="33">
         <f>B9-B14</f>
@@ -4570,7 +4576,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B19" s="46" t="str">
         <f>B9-B14-B17</f>
@@ -4619,7 +4625,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4649,7 +4655,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4659,7 +4665,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B5" s="31">
         <v>167500</v>
@@ -4679,7 +4685,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B6" s="31">
         <v>64516</v>
@@ -4699,7 +4705,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B7" s="31">
         <v>29625</v>
@@ -4719,7 +4725,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B8" s="34">
         <f>B5-B6-B7</f>
@@ -4744,7 +4750,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B9" s="31">
         <v>0</v>
@@ -4764,27 +4770,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -4794,7 +4800,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B13" s="31">
         <v>106850</v>
@@ -4814,7 +4820,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B14" s="48">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -4839,7 +4845,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B15" s="35">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -4884,7 +4890,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -4914,7 +4920,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B20" s="31">
         <v>64516</v>
@@ -4934,7 +4940,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B21" s="31">
         <v>1975</v>
@@ -4954,7 +4960,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B22" s="49">
         <v>8</v>
@@ -4974,7 +4980,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -4984,102 +4990,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B27" s="52" t="s">
+        <v>316</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>316</v>
+      </c>
+      <c r="D27" s="51" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="52" t="s">
+      <c r="E27" s="51" t="s">
         <v>314</v>
       </c>
-      <c r="D27" s="51" t="s">
-        <v>312</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>312</v>
-      </c>
       <c r="F27" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -5120,13 +5126,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B3" s="53" t="s">
         <v>112</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E3" s="53" t="s">
         <v>112</v>
@@ -5134,13 +5140,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B4" s="31">
         <v>12000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E4" s="31">
         <v>12000</v>
@@ -5148,13 +5154,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B6" s="33">
         <v>12000</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E6" s="33">
         <v>12000</v>
@@ -5162,7 +5168,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B7" s="46">
         <v>0</v>
@@ -5510,7 +5516,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5520,7 +5526,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -5530,7 +5536,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5555,7 +5561,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B6" s="31">
         <v>167500</v>
@@ -5575,7 +5581,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B7" s="31">
         <v>94141</v>
@@ -5595,7 +5601,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B8" s="33">
         <v>73359</v>
@@ -5615,7 +5621,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B9" s="29">
         <v>0.4379626865671642</v>
@@ -5635,27 +5641,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D10" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F10" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B11" s="48">
         <v>8</v>
@@ -5675,7 +5681,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -5685,7 +5691,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5710,7 +5716,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B16" s="31">
         <v>125625</v>
@@ -5730,7 +5736,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B17" s="31">
         <v>94141</v>
@@ -5750,7 +5756,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B18" s="33">
         <v>31484</v>
@@ -5770,7 +5776,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B19" s="29">
         <v>0.25061691542288556</v>
@@ -5790,27 +5796,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B20" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C20" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D20" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E20" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F20" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B21" s="48">
         <v>8</v>
@@ -5856,7 +5862,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5890,7 +5896,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -5914,7 +5920,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -5922,7 +5928,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -5960,7 +5966,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D13" s="31">
         <v>167500</v>
@@ -5980,7 +5986,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D14" s="31">
         <v>94141</v>
@@ -6000,7 +6006,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D15" s="31">
         <v>73359</v>
@@ -6020,7 +6026,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D16" s="31">
         <v>106850</v>
@@ -6040,7 +6046,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D17" s="31">
         <v>0</v>
@@ -6060,7 +6066,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -6098,7 +6104,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D21" s="29">
         <v>0.4379626865671642</v>
@@ -6118,22 +6124,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E22" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F22" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G22" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H22" s="54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -6158,7 +6164,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D24" s="48">
         <v>15</v>
@@ -6178,7 +6184,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -6219,7 +6225,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6230,7 +6236,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="56" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C3" s="56"/>
       <c r="D3" s="56"/>
@@ -6241,41 +6247,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="57" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F4" s="59" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C6" s="60" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D6" s="60" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E6" s="60" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F6" s="60" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G6" s="60" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H6" s="60" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C7" s="61">
         <v>15</v>
@@ -6295,7 +6301,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C8" s="62">
         <v>167500</v>
@@ -6315,7 +6321,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C9" s="62">
         <v>64516.25</v>
@@ -6335,7 +6341,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C10" s="62">
         <v>29625</v>
@@ -6355,7 +6361,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C11" s="62">
         <v>0</v>
@@ -6375,7 +6381,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C12" s="63">
         <v>73358.75</v>
@@ -6395,7 +6401,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C13" s="63">
         <v>106850</v>
@@ -6415,7 +6421,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C14" s="64">
         <v>0.4379626865671642</v>
@@ -6453,12 +6459,12 @@
         <v>14941.129452750003</v>
       </c>
       <c r="H15" s="66" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C16" s="64">
         <v>0.3851716417910448</v>
@@ -6476,12 +6482,12 @@
         <v>0.14579943502824858</v>
       </c>
       <c r="H16" s="66" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C17" s="67">
         <v>0.15402985074626865</v>
@@ -6499,12 +6505,12 @@
         <v>0.04858757062146892</v>
       </c>
       <c r="H17" s="66" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C18" s="64">
         <v>0.4379626865671642</v>
@@ -6522,12 +6528,12 @@
         <v>0.7566487758945386</v>
       </c>
       <c r="H18" s="66" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C19" s="68">
         <v>3</v>
@@ -6545,35 +6551,35 @@
         <v>3</v>
       </c>
       <c r="H19" s="66" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C20" s="69" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D20" s="69" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E20" s="69" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F20" s="69" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G20" s="69" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H20" s="66" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C21" s="40" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
@@ -6596,12 +6602,12 @@
         <v>0</v>
       </c>
       <c r="H21" s="66" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C22" s="71">
         <v>14</v>
@@ -6613,140 +6619,140 @@
         <v>54</v>
       </c>
       <c r="F22" s="72" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G22" s="72" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H22" s="66" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="42" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D25" s="73" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E25" s="73"/>
       <c r="F25" s="74" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G25" s="74"/>
       <c r="H25" s="74"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="42" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D26" s="73" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E26" s="73"/>
       <c r="F26" s="74" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G26" s="74"/>
       <c r="H26" s="74"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D27" s="73" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E27" s="73"/>
       <c r="F27" s="74" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G27" s="74"/>
       <c r="H27" s="74"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="42" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D28" s="73" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E28" s="73"/>
       <c r="F28" s="74" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G28" s="74"/>
       <c r="H28" s="74"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D29" s="73" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E29" s="73"/>
       <c r="F29" s="74" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G29" s="74"/>
       <c r="H29" s="74"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D30" s="73" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E30" s="73"/>
       <c r="F30" s="74" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G30" s="74"/>
       <c r="H30" s="74"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="42" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
@@ -6754,7 +6760,7 @@
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="75" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C34" s="75"/>
       <c r="D34" s="75"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="393">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1130,6 +1130,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -6213,7 +6216,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6628,153 +6631,174 @@
         <v>365</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C23" s="68">
+        <v>414</v>
+      </c>
+      <c r="D23" s="68">
+        <v>868</v>
+      </c>
+      <c r="E23" s="68">
+        <v>1629</v>
+      </c>
+      <c r="F23" s="68">
+        <v>2546</v>
+      </c>
+      <c r="G23" s="68">
+        <v>3557</v>
+      </c>
+      <c r="H23" s="66" t="s">
         <v>366</v>
       </c>
-      <c r="C24" s="19" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="C25" s="19" t="s">
         <v>368</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19" t="s">
+      <c r="D25" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="42" t="s">
+      <c r="E25" s="19"/>
+      <c r="F25" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="C25" s="40" t="s">
-        <v>371</v>
-      </c>
-      <c r="D25" s="73" t="s">
-        <v>372</v>
-      </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="42" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D26" s="73" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E26" s="73"/>
       <c r="F26" s="74" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G26" s="74"/>
       <c r="H26" s="74"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D27" s="73" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E27" s="73"/>
       <c r="F27" s="74" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G27" s="74"/>
       <c r="H27" s="74"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="42" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D28" s="73" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E28" s="73"/>
       <c r="F28" s="74" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G28" s="74"/>
       <c r="H28" s="74"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D29" s="73" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E29" s="73"/>
       <c r="F29" s="74" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G29" s="74"/>
       <c r="H29" s="74"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D30" s="73" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E30" s="73"/>
       <c r="F30" s="74" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G30" s="74"/>
       <c r="H30" s="74"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="42" t="s">
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="42" t="s">
+        <v>387</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>372</v>
+      </c>
+      <c r="D31" s="73" t="s">
+        <v>388</v>
+      </c>
+      <c r="E31" s="73"/>
+      <c r="F31" s="74" t="s">
         <v>389</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="42" t="s">
         <v>390</v>
       </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="75" t="s">
+      <c r="C33" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="75" t="s">
+        <v>392</v>
+      </c>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -6787,8 +6811,10 @@
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="397">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1094,6 +1094,18 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1455,7 +1467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1555,6 +1567,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6216,7 +6234,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6465,356 +6483,439 @@
         <v>353</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C16" s="67">
+        <v>6276.083333333333</v>
+      </c>
+      <c r="D16" s="67">
+        <v>5502.049318181818</v>
+      </c>
+      <c r="E16" s="67">
+        <v>4339.770585</v>
+      </c>
+      <c r="F16" s="67">
+        <v>3843.348510458333</v>
+      </c>
+      <c r="G16" s="67">
+        <v>3635.9421418448756</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="C16" s="64">
-        <v>0.3851716417910448</v>
-      </c>
-      <c r="D16" s="64">
-        <v>0.26387014314928425</v>
-      </c>
-      <c r="E16" s="64">
-        <v>0.19403383458646614</v>
-      </c>
-      <c r="F16" s="64">
-        <v>0.1618977415307403</v>
-      </c>
-      <c r="G16" s="64">
-        <v>0.14579943502824858</v>
-      </c>
-      <c r="H16" s="66" t="s">
+      <c r="C17" s="62">
+        <v>400</v>
+      </c>
+      <c r="D17" s="62">
+        <v>412</v>
+      </c>
+      <c r="E17" s="62">
+        <v>424.35999999999996</v>
+      </c>
+      <c r="F17" s="62">
+        <v>437.0908</v>
+      </c>
+      <c r="G17" s="62">
+        <v>450.20352400000013</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="65">
+        <v>1720</v>
+      </c>
+      <c r="D18" s="65">
+        <v>1207.909090909091</v>
+      </c>
+      <c r="E18" s="65">
+        <v>912.3739999999999</v>
+      </c>
+      <c r="F18" s="65">
+        <v>783.1210166666666</v>
+      </c>
+      <c r="G18" s="65">
+        <v>725.9531824500001</v>
+      </c>
+      <c r="H18" s="66" t="s">
         <v>356</v>
       </c>
-      <c r="C17" s="67">
-        <v>0.15402985074626865</v>
-      </c>
-      <c r="D17" s="64">
-        <v>0.08793456032719836</v>
-      </c>
-      <c r="E17" s="64">
-        <v>0.06466165413533834</v>
-      </c>
-      <c r="F17" s="64">
-        <v>0.053952321204516936</v>
-      </c>
-      <c r="G17" s="64">
-        <v>0.04858757062146892</v>
-      </c>
-      <c r="H17" s="66" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="C18" s="64">
-        <v>0.4379626865671642</v>
-      </c>
-      <c r="D18" s="64">
-        <v>0.5994563735514655</v>
-      </c>
-      <c r="E18" s="64">
-        <v>0.6924323308270676</v>
-      </c>
-      <c r="F18" s="64">
-        <v>0.7352164366373901</v>
-      </c>
-      <c r="G18" s="64">
-        <v>0.7566487758945386</v>
-      </c>
-      <c r="H18" s="66" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>360</v>
-      </c>
       <c r="C19" s="68">
-        <v>3</v>
+        <v>4890.583333333333</v>
       </c>
       <c r="D19" s="68">
-        <v>3</v>
+        <v>8234.405227272726</v>
       </c>
       <c r="E19" s="68">
-        <v>3</v>
+        <v>9770.199415000001</v>
       </c>
       <c r="F19" s="68">
-        <v>3</v>
+        <v>10671.708472875</v>
       </c>
       <c r="G19" s="68">
-        <v>3</v>
-      </c>
-      <c r="H19" s="66" t="s">
-        <v>361</v>
+        <v>11305.187310905127</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="C20" s="69" t="s">
-        <v>302</v>
-      </c>
-      <c r="D20" s="69" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="69" t="s">
-        <v>302</v>
-      </c>
-      <c r="F20" s="69" t="s">
-        <v>302</v>
-      </c>
-      <c r="G20" s="69" t="s">
-        <v>302</v>
+        <v>358</v>
+      </c>
+      <c r="C20" s="64">
+        <v>0.3851716417910448</v>
+      </c>
+      <c r="D20" s="64">
+        <v>0.26387014314928425</v>
+      </c>
+      <c r="E20" s="64">
+        <v>0.19403383458646614</v>
+      </c>
+      <c r="F20" s="64">
+        <v>0.1618977415307403</v>
+      </c>
+      <c r="G20" s="64">
+        <v>0.14579943502824858</v>
       </c>
       <c r="H20" s="66" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="C21" s="69">
+        <v>0.15402985074626865</v>
+      </c>
+      <c r="D21" s="64">
+        <v>0.08793456032719836</v>
+      </c>
+      <c r="E21" s="64">
+        <v>0.06466165413533834</v>
+      </c>
+      <c r="F21" s="64">
+        <v>0.053952321204516936</v>
+      </c>
+      <c r="G21" s="64">
+        <v>0.04858757062146892</v>
+      </c>
+      <c r="H21" s="66" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="C21" s="40" t="str">
+      <c r="C22" s="64">
+        <v>0.4379626865671642</v>
+      </c>
+      <c r="D22" s="64">
+        <v>0.5994563735514655</v>
+      </c>
+      <c r="E22" s="64">
+        <v>0.6924323308270676</v>
+      </c>
+      <c r="F22" s="64">
+        <v>0.7352164366373901</v>
+      </c>
+      <c r="G22" s="64">
+        <v>0.7566487758945386</v>
+      </c>
+      <c r="H22" s="66" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="C23" s="70">
+        <v>3</v>
+      </c>
+      <c r="D23" s="70">
+        <v>3</v>
+      </c>
+      <c r="E23" s="70">
+        <v>3</v>
+      </c>
+      <c r="F23" s="70">
+        <v>3</v>
+      </c>
+      <c r="G23" s="70">
+        <v>3</v>
+      </c>
+      <c r="H23" s="66" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C24" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="D24" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="E24" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="F24" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="G24" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="H24" s="66" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="C25" s="40" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="70" t="str">
+      <c r="D25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="70" t="str">
+      <c r="E25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="70" t="str">
+      <c r="F25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="70" t="str">
+      <c r="G25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="66" t="s">
+      <c r="H25" s="66" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C22" s="71">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C26" s="73">
         <v>14</v>
       </c>
-      <c r="D22" s="68">
+      <c r="D26" s="70">
         <v>29</v>
       </c>
-      <c r="E22" s="68">
+      <c r="E26" s="70">
         <v>54</v>
       </c>
-      <c r="F22" s="72" t="s">
-        <v>364</v>
-      </c>
-      <c r="G22" s="72" t="s">
-        <v>364</v>
-      </c>
-      <c r="H22" s="66" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
+      <c r="F26" s="74" t="s">
+        <v>368</v>
+      </c>
+      <c r="G26" s="74" t="s">
+        <v>368</v>
+      </c>
+      <c r="H26" s="66" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="C23" s="68">
+      <c r="C27" s="70">
         <v>414</v>
       </c>
-      <c r="D23" s="68">
+      <c r="D27" s="70">
         <v>868</v>
       </c>
-      <c r="E23" s="68">
+      <c r="E27" s="70">
         <v>1629</v>
       </c>
-      <c r="F23" s="68">
+      <c r="F27" s="70">
         <v>2546</v>
       </c>
-      <c r="G23" s="68">
+      <c r="G27" s="70">
         <v>3557</v>
       </c>
-      <c r="H23" s="66" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19" t="s">
+      <c r="H27" s="66" t="s">
         <v>370</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="42" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
         <v>371</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C29" s="19" t="s">
         <v>372</v>
       </c>
-      <c r="D26" s="73" t="s">
+      <c r="D29" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="42" t="s">
-        <v>375</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>372</v>
-      </c>
-      <c r="D27" s="73" t="s">
-        <v>376</v>
-      </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74" t="s">
-        <v>377</v>
-      </c>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="42" t="s">
-        <v>378</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>372</v>
-      </c>
-      <c r="D28" s="73" t="s">
-        <v>379</v>
-      </c>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74" t="s">
-        <v>380</v>
-      </c>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
-        <v>381</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>372</v>
-      </c>
-      <c r="D29" s="73" t="s">
-        <v>382</v>
-      </c>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74" t="s">
-        <v>383</v>
-      </c>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>372</v>
-      </c>
-      <c r="D30" s="73" t="s">
-        <v>385</v>
-      </c>
-      <c r="E30" s="73"/>
-      <c r="F30" s="74" t="s">
-        <v>386</v>
-      </c>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
+        <v>376</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>377</v>
+      </c>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
+        <v>378</v>
+      </c>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D31" s="75" t="s">
+        <v>380</v>
+      </c>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
+        <v>381</v>
+      </c>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D32" s="75" t="s">
+        <v>383</v>
+      </c>
+      <c r="E32" s="75"/>
+      <c r="F32" s="76" t="s">
+        <v>384</v>
+      </c>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="42" t="s">
+        <v>385</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D33" s="75" t="s">
+        <v>386</v>
+      </c>
+      <c r="E33" s="75"/>
+      <c r="F33" s="76" t="s">
         <v>387</v>
       </c>
-      <c r="C31" s="40" t="s">
-        <v>372</v>
-      </c>
-      <c r="D31" s="73" t="s">
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="42" t="s">
         <v>388</v>
       </c>
-      <c r="E31" s="73"/>
-      <c r="F31" s="74" t="s">
+      <c r="C34" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D34" s="75" t="s">
         <v>389</v>
       </c>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="42" t="s">
+      <c r="E34" s="75"/>
+      <c r="F34" s="76" t="s">
         <v>390</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="42" t="s">
         <v>391</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="75" t="s">
+      <c r="C35" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D35" s="75" t="s">
         <v>392</v>
       </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
       <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
+      <c r="F35" s="76" t="s">
+        <v>393</v>
+      </c>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="42" t="s">
+        <v>394</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="77" t="s">
+        <v>396</v>
+      </c>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -6860,37 +6961,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="392">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1096,18 +1096,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -1142,9 +1130,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1467,7 +1452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1567,12 +1552,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6234,7 +6213,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6483,439 +6462,333 @@
         <v>353</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="C16" s="67">
-        <v>6276.083333333333</v>
-      </c>
-      <c r="D16" s="67">
-        <v>5502.049318181818</v>
-      </c>
-      <c r="E16" s="67">
-        <v>4339.770585</v>
-      </c>
-      <c r="F16" s="67">
-        <v>3843.348510458333</v>
-      </c>
-      <c r="G16" s="67">
-        <v>3635.9421418448756</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="C17" s="62">
-        <v>400</v>
-      </c>
-      <c r="D17" s="62">
-        <v>412</v>
-      </c>
-      <c r="E17" s="62">
-        <v>424.35999999999996</v>
-      </c>
-      <c r="F17" s="62">
-        <v>437.0908</v>
-      </c>
-      <c r="G17" s="62">
-        <v>450.20352400000013</v>
+      <c r="C16" s="64">
+        <v>0.3851716417910448</v>
+      </c>
+      <c r="D16" s="64">
+        <v>0.26387014314928425</v>
+      </c>
+      <c r="E16" s="64">
+        <v>0.19403383458646614</v>
+      </c>
+      <c r="F16" s="64">
+        <v>0.1618977415307403</v>
+      </c>
+      <c r="G16" s="64">
+        <v>0.14579943502824858</v>
+      </c>
+      <c r="H16" s="66" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="C17" s="67">
+        <v>0.15402985074626865</v>
+      </c>
+      <c r="D17" s="64">
+        <v>0.08793456032719836</v>
+      </c>
+      <c r="E17" s="64">
+        <v>0.06466165413533834</v>
+      </c>
+      <c r="F17" s="64">
+        <v>0.053952321204516936</v>
+      </c>
+      <c r="G17" s="64">
+        <v>0.04858757062146892</v>
+      </c>
+      <c r="H17" s="66" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="C18" s="65">
-        <v>1720</v>
-      </c>
-      <c r="D18" s="65">
-        <v>1207.909090909091</v>
-      </c>
-      <c r="E18" s="65">
-        <v>912.3739999999999</v>
-      </c>
-      <c r="F18" s="65">
-        <v>783.1210166666666</v>
-      </c>
-      <c r="G18" s="65">
-        <v>725.9531824500001</v>
+      <c r="B18" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C18" s="64">
+        <v>0.4379626865671642</v>
+      </c>
+      <c r="D18" s="64">
+        <v>0.5994563735514655</v>
+      </c>
+      <c r="E18" s="64">
+        <v>0.6924323308270676</v>
+      </c>
+      <c r="F18" s="64">
+        <v>0.7352164366373901</v>
+      </c>
+      <c r="G18" s="64">
+        <v>0.7566487758945386</v>
       </c>
       <c r="H18" s="66" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C19" s="68">
-        <v>4890.583333333333</v>
+        <v>3</v>
       </c>
       <c r="D19" s="68">
-        <v>8234.405227272726</v>
+        <v>3</v>
       </c>
       <c r="E19" s="68">
-        <v>9770.199415000001</v>
+        <v>3</v>
       </c>
       <c r="F19" s="68">
-        <v>10671.708472875</v>
+        <v>3</v>
       </c>
       <c r="G19" s="68">
-        <v>11305.187310905127</v>
+        <v>3</v>
+      </c>
+      <c r="H19" s="66" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="C20" s="64">
-        <v>0.3851716417910448</v>
-      </c>
-      <c r="D20" s="64">
-        <v>0.26387014314928425</v>
-      </c>
-      <c r="E20" s="64">
-        <v>0.19403383458646614</v>
-      </c>
-      <c r="F20" s="64">
-        <v>0.1618977415307403</v>
-      </c>
-      <c r="G20" s="64">
-        <v>0.14579943502824858</v>
+        <v>301</v>
+      </c>
+      <c r="C20" s="69" t="s">
+        <v>302</v>
+      </c>
+      <c r="D20" s="69" t="s">
+        <v>302</v>
+      </c>
+      <c r="E20" s="69" t="s">
+        <v>302</v>
+      </c>
+      <c r="F20" s="69" t="s">
+        <v>302</v>
+      </c>
+      <c r="G20" s="69" t="s">
+        <v>302</v>
       </c>
       <c r="H20" s="66" t="s">
-        <v>359</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="C21" s="69">
-        <v>0.15402985074626865</v>
-      </c>
-      <c r="D21" s="64">
-        <v>0.08793456032719836</v>
-      </c>
-      <c r="E21" s="64">
-        <v>0.06466165413533834</v>
-      </c>
-      <c r="F21" s="64">
-        <v>0.053952321204516936</v>
-      </c>
-      <c r="G21" s="64">
-        <v>0.04858757062146892</v>
+        <v>362</v>
+      </c>
+      <c r="C21" s="40" t="str">
+        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="70" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="70" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="70" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="70" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="66" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="C22" s="64">
-        <v>0.4379626865671642</v>
-      </c>
-      <c r="D22" s="64">
-        <v>0.5994563735514655</v>
-      </c>
-      <c r="E22" s="64">
-        <v>0.6924323308270676</v>
-      </c>
-      <c r="F22" s="64">
-        <v>0.7352164366373901</v>
-      </c>
-      <c r="G22" s="64">
-        <v>0.7566487758945386</v>
+        <v>363</v>
+      </c>
+      <c r="C22" s="71">
+        <v>14</v>
+      </c>
+      <c r="D22" s="68">
+        <v>29</v>
+      </c>
+      <c r="E22" s="68">
+        <v>54</v>
+      </c>
+      <c r="F22" s="72" t="s">
+        <v>364</v>
+      </c>
+      <c r="G22" s="72" t="s">
+        <v>364</v>
       </c>
       <c r="H22" s="66" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="C23" s="70">
-        <v>3</v>
-      </c>
-      <c r="D23" s="70">
-        <v>3</v>
-      </c>
-      <c r="E23" s="70">
-        <v>3</v>
-      </c>
-      <c r="F23" s="70">
-        <v>3</v>
-      </c>
-      <c r="G23" s="70">
-        <v>3</v>
-      </c>
-      <c r="H23" s="66" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="C24" s="71" t="s">
-        <v>302</v>
-      </c>
-      <c r="D24" s="71" t="s">
-        <v>302</v>
-      </c>
-      <c r="E24" s="71" t="s">
-        <v>302</v>
-      </c>
-      <c r="F24" s="71" t="s">
-        <v>302</v>
-      </c>
-      <c r="G24" s="71" t="s">
-        <v>302</v>
-      </c>
-      <c r="H24" s="66" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
         <v>366</v>
       </c>
-      <c r="C25" s="40" t="str">
-        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="D25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="66" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="10" t="s">
+      <c r="C24" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="C26" s="73">
-        <v>14</v>
-      </c>
-      <c r="D26" s="70">
-        <v>29</v>
-      </c>
-      <c r="E26" s="70">
-        <v>54</v>
-      </c>
+      <c r="D24" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="D25" s="73" t="s">
+        <v>372</v>
+      </c>
+      <c r="E25" s="73"/>
+      <c r="F25" s="74" t="s">
+        <v>373</v>
+      </c>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="42" t="s">
+        <v>374</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="D26" s="73" t="s">
+        <v>375</v>
+      </c>
+      <c r="E26" s="73"/>
       <c r="F26" s="74" t="s">
-        <v>368</v>
-      </c>
-      <c r="G26" s="74" t="s">
-        <v>368</v>
-      </c>
-      <c r="H26" s="66" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="C27" s="70">
-        <v>414</v>
-      </c>
-      <c r="D27" s="70">
-        <v>868</v>
-      </c>
-      <c r="E27" s="70">
-        <v>1629</v>
-      </c>
-      <c r="F27" s="70">
-        <v>2546</v>
-      </c>
-      <c r="G27" s="70">
-        <v>3557</v>
-      </c>
-      <c r="H27" s="66" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="42" t="s">
+        <v>377</v>
+      </c>
+      <c r="C27" s="40" t="s">
         <v>371</v>
       </c>
-      <c r="C29" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
+      <c r="D27" s="73" t="s">
+        <v>378</v>
+      </c>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74" t="s">
+        <v>379</v>
+      </c>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="D28" s="73" t="s">
+        <v>381</v>
+      </c>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74" t="s">
+        <v>382</v>
+      </c>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>371</v>
+      </c>
+      <c r="D29" s="73" t="s">
+        <v>384</v>
+      </c>
+      <c r="E29" s="73"/>
+      <c r="F29" s="74" t="s">
+        <v>385</v>
+      </c>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>377</v>
-      </c>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76" t="s">
-        <v>378</v>
-      </c>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="42" t="s">
-        <v>379</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D31" s="75" t="s">
-        <v>380</v>
-      </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76" t="s">
-        <v>381</v>
-      </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+      <c r="D30" s="73" t="s">
+        <v>387</v>
+      </c>
+      <c r="E30" s="73"/>
+      <c r="F30" s="74" t="s">
+        <v>388</v>
+      </c>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="42" t="s">
-        <v>382</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D32" s="75" t="s">
-        <v>383</v>
-      </c>
-      <c r="E32" s="75"/>
-      <c r="F32" s="76" t="s">
-        <v>384</v>
-      </c>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="42" t="s">
-        <v>385</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D33" s="75" t="s">
-        <v>386</v>
-      </c>
-      <c r="E33" s="75"/>
-      <c r="F33" s="76" t="s">
-        <v>387</v>
-      </c>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="42" t="s">
-        <v>388</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D34" s="75" t="s">
         <v>389</v>
       </c>
+      <c r="C32" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="75" t="s">
+        <v>391</v>
+      </c>
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
       <c r="E34" s="75"/>
-      <c r="F34" s="76" t="s">
-        <v>390</v>
-      </c>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="42" t="s">
-        <v>391</v>
-      </c>
-      <c r="C35" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D35" s="75" t="s">
-        <v>392</v>
-      </c>
-      <c r="E35" s="75"/>
-      <c r="F35" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="42" t="s">
-        <v>394</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="77" t="s">
-        <v>396</v>
-      </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="B34:H34"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -6961,37 +6834,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="397">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1096,6 +1096,18 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -1130,6 +1142,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1452,7 +1467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1552,6 +1567,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6213,7 +6234,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6462,333 +6483,439 @@
         <v>353</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C16" s="67">
+        <v>6276.083333333333</v>
+      </c>
+      <c r="D16" s="67">
+        <v>5502.049318181818</v>
+      </c>
+      <c r="E16" s="67">
+        <v>4339.770585</v>
+      </c>
+      <c r="F16" s="67">
+        <v>3843.348510458333</v>
+      </c>
+      <c r="G16" s="67">
+        <v>3635.9421418448756</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="C16" s="64">
-        <v>0.3851716417910448</v>
-      </c>
-      <c r="D16" s="64">
-        <v>0.26387014314928425</v>
-      </c>
-      <c r="E16" s="64">
-        <v>0.19403383458646614</v>
-      </c>
-      <c r="F16" s="64">
-        <v>0.1618977415307403</v>
-      </c>
-      <c r="G16" s="64">
-        <v>0.14579943502824858</v>
-      </c>
-      <c r="H16" s="66" t="s">
+      <c r="C17" s="62">
+        <v>400</v>
+      </c>
+      <c r="D17" s="62">
+        <v>412</v>
+      </c>
+      <c r="E17" s="62">
+        <v>424.35999999999996</v>
+      </c>
+      <c r="F17" s="62">
+        <v>437.0908</v>
+      </c>
+      <c r="G17" s="62">
+        <v>450.20352400000013</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="65">
+        <v>1720</v>
+      </c>
+      <c r="D18" s="65">
+        <v>1207.909090909091</v>
+      </c>
+      <c r="E18" s="65">
+        <v>912.3739999999999</v>
+      </c>
+      <c r="F18" s="65">
+        <v>783.1210166666666</v>
+      </c>
+      <c r="G18" s="65">
+        <v>725.9531824500001</v>
+      </c>
+      <c r="H18" s="66" t="s">
         <v>356</v>
       </c>
-      <c r="C17" s="67">
-        <v>0.15402985074626865</v>
-      </c>
-      <c r="D17" s="64">
-        <v>0.08793456032719836</v>
-      </c>
-      <c r="E17" s="64">
-        <v>0.06466165413533834</v>
-      </c>
-      <c r="F17" s="64">
-        <v>0.053952321204516936</v>
-      </c>
-      <c r="G17" s="64">
-        <v>0.04858757062146892</v>
-      </c>
-      <c r="H17" s="66" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="C18" s="64">
-        <v>0.4379626865671642</v>
-      </c>
-      <c r="D18" s="64">
-        <v>0.5994563735514655</v>
-      </c>
-      <c r="E18" s="64">
-        <v>0.6924323308270676</v>
-      </c>
-      <c r="F18" s="64">
-        <v>0.7352164366373901</v>
-      </c>
-      <c r="G18" s="64">
-        <v>0.7566487758945386</v>
-      </c>
-      <c r="H18" s="66" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>360</v>
-      </c>
       <c r="C19" s="68">
-        <v>3</v>
+        <v>4890.583333333333</v>
       </c>
       <c r="D19" s="68">
-        <v>3</v>
+        <v>8234.405227272726</v>
       </c>
       <c r="E19" s="68">
-        <v>3</v>
+        <v>9770.199415000001</v>
       </c>
       <c r="F19" s="68">
-        <v>3</v>
+        <v>10671.708472875</v>
       </c>
       <c r="G19" s="68">
-        <v>3</v>
-      </c>
-      <c r="H19" s="66" t="s">
-        <v>361</v>
+        <v>11305.187310905127</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="C20" s="69" t="s">
-        <v>302</v>
-      </c>
-      <c r="D20" s="69" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="69" t="s">
-        <v>302</v>
-      </c>
-      <c r="F20" s="69" t="s">
-        <v>302</v>
-      </c>
-      <c r="G20" s="69" t="s">
-        <v>302</v>
+        <v>358</v>
+      </c>
+      <c r="C20" s="64">
+        <v>0.3851716417910448</v>
+      </c>
+      <c r="D20" s="64">
+        <v>0.26387014314928425</v>
+      </c>
+      <c r="E20" s="64">
+        <v>0.19403383458646614</v>
+      </c>
+      <c r="F20" s="64">
+        <v>0.1618977415307403</v>
+      </c>
+      <c r="G20" s="64">
+        <v>0.14579943502824858</v>
       </c>
       <c r="H20" s="66" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="C21" s="69">
+        <v>0.15402985074626865</v>
+      </c>
+      <c r="D21" s="64">
+        <v>0.08793456032719836</v>
+      </c>
+      <c r="E21" s="64">
+        <v>0.06466165413533834</v>
+      </c>
+      <c r="F21" s="64">
+        <v>0.053952321204516936</v>
+      </c>
+      <c r="G21" s="64">
+        <v>0.04858757062146892</v>
+      </c>
+      <c r="H21" s="66" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="C21" s="40" t="str">
+      <c r="C22" s="64">
+        <v>0.4379626865671642</v>
+      </c>
+      <c r="D22" s="64">
+        <v>0.5994563735514655</v>
+      </c>
+      <c r="E22" s="64">
+        <v>0.6924323308270676</v>
+      </c>
+      <c r="F22" s="64">
+        <v>0.7352164366373901</v>
+      </c>
+      <c r="G22" s="64">
+        <v>0.7566487758945386</v>
+      </c>
+      <c r="H22" s="66" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="C23" s="70">
+        <v>3</v>
+      </c>
+      <c r="D23" s="70">
+        <v>3</v>
+      </c>
+      <c r="E23" s="70">
+        <v>3</v>
+      </c>
+      <c r="F23" s="70">
+        <v>3</v>
+      </c>
+      <c r="G23" s="70">
+        <v>3</v>
+      </c>
+      <c r="H23" s="66" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C24" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="D24" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="E24" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="F24" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="G24" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="H24" s="66" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="C25" s="40" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="70" t="str">
+      <c r="D25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="70" t="str">
+      <c r="E25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="70" t="str">
+      <c r="F25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="70" t="str">
+      <c r="G25" s="72" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="66" t="s">
+      <c r="H25" s="66" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C22" s="71">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C26" s="73">
         <v>14</v>
       </c>
-      <c r="D22" s="68">
+      <c r="D26" s="70">
         <v>29</v>
       </c>
-      <c r="E22" s="68">
+      <c r="E26" s="70">
         <v>54</v>
       </c>
-      <c r="F22" s="72" t="s">
-        <v>364</v>
-      </c>
-      <c r="G22" s="72" t="s">
-        <v>364</v>
-      </c>
-      <c r="H22" s="66" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
-        <v>366</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="D24" s="19" t="s">
+      <c r="F26" s="74" t="s">
         <v>368</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19" t="s">
+      <c r="G26" s="74" t="s">
+        <v>368</v>
+      </c>
+      <c r="H26" s="66" t="s">
         <v>369</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="42" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C27" s="70">
+        <v>414</v>
+      </c>
+      <c r="D27" s="70">
+        <v>868</v>
+      </c>
+      <c r="E27" s="70">
+        <v>1629</v>
+      </c>
+      <c r="F27" s="70">
+        <v>2546</v>
+      </c>
+      <c r="G27" s="70">
+        <v>3557</v>
+      </c>
+      <c r="H27" s="66" t="s">
         <v>370</v>
       </c>
-      <c r="C25" s="40" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
         <v>371</v>
       </c>
-      <c r="D25" s="73" t="s">
+      <c r="C29" s="19" t="s">
         <v>372</v>
       </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74" t="s">
+      <c r="D29" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="42" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="C26" s="40" t="s">
-        <v>371</v>
-      </c>
-      <c r="D26" s="73" t="s">
-        <v>375</v>
-      </c>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74" t="s">
-        <v>376</v>
-      </c>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="42" t="s">
-        <v>377</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>371</v>
-      </c>
-      <c r="D27" s="73" t="s">
-        <v>378</v>
-      </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74" t="s">
-        <v>379</v>
-      </c>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="42" t="s">
-        <v>380</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>371</v>
-      </c>
-      <c r="D28" s="73" t="s">
-        <v>381</v>
-      </c>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74" t="s">
-        <v>382</v>
-      </c>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
-        <v>383</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>371</v>
-      </c>
-      <c r="D29" s="73" t="s">
-        <v>384</v>
-      </c>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74" t="s">
-        <v>385</v>
-      </c>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
+        <v>375</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>377</v>
+      </c>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
+        <v>378</v>
+      </c>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D31" s="75" t="s">
+        <v>380</v>
+      </c>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
+        <v>381</v>
+      </c>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="42" t="s">
+        <v>382</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D32" s="75" t="s">
+        <v>383</v>
+      </c>
+      <c r="E32" s="75"/>
+      <c r="F32" s="76" t="s">
+        <v>384</v>
+      </c>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="42" t="s">
+        <v>385</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D33" s="75" t="s">
         <v>386</v>
       </c>
-      <c r="C30" s="40" t="s">
-        <v>371</v>
-      </c>
-      <c r="D30" s="73" t="s">
+      <c r="E33" s="75"/>
+      <c r="F33" s="76" t="s">
         <v>387</v>
       </c>
-      <c r="E30" s="73"/>
-      <c r="F30" s="74" t="s">
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="42" t="s">
         <v>388</v>
       </c>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="42" t="s">
+      <c r="C34" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D34" s="75" t="s">
         <v>389</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="E34" s="75"/>
+      <c r="F34" s="76" t="s">
         <v>390</v>
       </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="75" t="s">
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="42" t="s">
         <v>391</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
+      <c r="C35" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="D35" s="75" t="s">
+        <v>392</v>
+      </c>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76" t="s">
+        <v>393</v>
+      </c>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="42" t="s">
+        <v>394</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="77" t="s">
+        <v>396</v>
+      </c>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -6834,37 +6961,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -26,13 +26,15 @@
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
+    <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
+    <sheet sheetId="24" name="Decision History" state="visible" r:id="rId27"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="440">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -40,7 +42,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · llc_single</t>
+    <t>Generated April 29, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -160,7 +162,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -310,6 +312,12 @@
     <t>Financial Health</t>
   </si>
   <si>
+    <t>23.</t>
+  </si>
+  <si>
+    <t>Budget Narrative</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -376,6 +384,9 @@
     <t>Escalation %</t>
   </si>
   <si>
+    <t>Timing</t>
+  </si>
+  <si>
     <t>Co-Op Tuition</t>
   </si>
   <si>
@@ -385,6 +396,9 @@
     <t>Per Student</t>
   </si>
   <si>
+    <t>Default</t>
+  </si>
+  <si>
     <t>Materials Fee</t>
   </si>
   <si>
@@ -460,6 +474,12 @@
     <t>Insurance</t>
   </si>
   <si>
+    <t>Compliance Contract</t>
+  </si>
+  <si>
+    <t>Administrative / General</t>
+  </si>
+  <si>
     <t>Curriculum &amp; Materials</t>
   </si>
   <si>
@@ -508,6 +528,48 @@
     <t>No</t>
   </si>
   <si>
+    <t>Enrollment Growth Rate</t>
+  </si>
+  <si>
+    <t>Rent Escalation Rate</t>
+  </si>
+  <si>
+    <t>Tuition Escalation Rate</t>
+  </si>
+  <si>
+    <t>Default Benefits Rate</t>
+  </si>
+  <si>
+    <t>Default Payroll Tax Rate</t>
+  </si>
+  <si>
+    <t>Student Retention Rate</t>
+  </si>
+  <si>
+    <t>REVENUE COLLECTION DEFAULTS</t>
+  </si>
+  <si>
+    <t>Default Billing Months</t>
+  </si>
+  <si>
+    <t>10 months (Aug-May)</t>
+  </si>
+  <si>
+    <t>Default Collection Method</t>
+  </si>
+  <si>
+    <t>Autopay</t>
+  </si>
+  <si>
+    <t>Default Collection Rate</t>
+  </si>
+  <si>
+    <t>Default Collection Delay</t>
+  </si>
+  <si>
+    <t>0 days</t>
+  </si>
+  <si>
     <t>WEIGHTED ENROLLMENT POPULATIONS</t>
   </si>
   <si>
@@ -577,9 +639,6 @@
     <t>Capacity Utilization</t>
   </si>
   <si>
-    <t>Enrollment Growth Rate</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -619,6 +678,9 @@
     <t>Loaded Cost</t>
   </si>
   <si>
+    <t>Rates</t>
+  </si>
+  <si>
     <t>5-YEAR TOTAL PERSONNEL COST</t>
   </si>
   <si>
@@ -658,6 +720,12 @@
     <t>Total Occupancy / Facility</t>
   </si>
   <si>
+    <t xml:space="preserve">  Compliance Contract</t>
+  </si>
+  <si>
+    <t>Total Administrative / General</t>
+  </si>
+  <si>
     <t>TOTAL OPERATING EXPENSES</t>
   </si>
   <si>
@@ -751,6 +819,9 @@
     <t xml:space="preserve">  Total Occupancy / Facility</t>
   </si>
   <si>
+    <t xml:space="preserve">    Compliance Contract</t>
+  </si>
+  <si>
     <t>Total Operating Expenses</t>
   </si>
   <si>
@@ -856,12 +927,24 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
+    <t>Cash Trough: July (Month 1)</t>
+  </si>
+  <si>
+    <t>Your lowest cash point is the month lenders focus on to ensure you won't run out of money before collections start. Plan reserves to cover this trough.</t>
+  </si>
+  <si>
     <t>Liberty Learning Co-Op - 5-Year Operating Statement</t>
   </si>
   <si>
+    <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
+  </si>
+  <si>
     <t>Capital &amp; Debt Service</t>
   </si>
   <si>
+    <t>Depreciation</t>
+  </si>
+  <si>
     <t>BOTTOM LINE</t>
   </si>
   <si>
@@ -895,7 +978,7 @@
     <t>Accounts Receivable</t>
   </si>
   <si>
-    <t>Fixed Assets</t>
+    <t>Fixed Assets (Net of Depreciation)</t>
   </si>
   <si>
     <t>Other Assets</t>
@@ -934,7 +1017,13 @@
     <t>Revenue</t>
   </si>
   <si>
-    <t>CFADS (Rev - Pers - OpEx)</t>
+    <t>Depreciation Add-Back</t>
+  </si>
+  <si>
+    <t>Debt Service (Loan)</t>
+  </si>
+  <si>
+    <t>CFADS (NI + Depr + DS)</t>
   </si>
   <si>
     <t>DSCR</t>
@@ -979,6 +1068,9 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>Current Ratio ≥ 1.1x</t>
+  </si>
+  <si>
     <t>Capacity ≥ 70%</t>
   </si>
   <si>
@@ -1060,7 +1152,7 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1210,7 +1302,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>117.0 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>111.5 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -1223,6 +1315,45 @@
   </si>
   <si>
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
+  </si>
+  <si>
+    <t>Enrollment Strategy</t>
+  </si>
+  <si>
+    <t>(Not provided)</t>
+  </si>
+  <si>
+    <t>Retention Plan</t>
+  </si>
+  <si>
+    <t>Risk Mitigation</t>
+  </si>
+  <si>
+    <t>Mission &amp; Vision</t>
+  </si>
+  <si>
+    <t>Revenue Assumptions</t>
+  </si>
+  <si>
+    <t>Staffing Philosophy</t>
+  </si>
+  <si>
+    <t>Expense Assumptions</t>
+  </si>
+  <si>
+    <t>Growth Strategy</t>
+  </si>
+  <si>
+    <t>Additional Context</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1367,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1327,6 +1458,18 @@
       <i/>
       <color rgb="FF808080"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1467,7 +1610,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1515,8 +1658,10 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1526,17 +1671,17 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1544,10 +1689,10 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1566,7 +1711,7 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1594,11 +1739,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2296,7 +2450,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2309,24 +2463,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B4" s="36">
         <v>15</v>
@@ -2346,7 +2500,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -2356,7 +2510,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B7" s="31">
         <v>90000</v>
@@ -2376,27 +2530,27 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B8" s="31">
         <v>3000</v>
       </c>
       <c r="C8" s="31">
-        <v>4532</v>
+        <v>4400</v>
       </c>
       <c r="D8" s="31">
-        <v>6365</v>
+        <v>6000</v>
       </c>
       <c r="E8" s="31">
-        <v>7868</v>
+        <v>7200</v>
       </c>
       <c r="F8" s="31">
-        <v>9004</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B9" s="31">
         <v>105000</v>
@@ -2416,7 +2570,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B10" s="31">
         <v>3000</v>
@@ -2436,7 +2590,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="B11" s="33">
         <f>SUM(B7:B10)</f>
@@ -2444,39 +2598,39 @@
       </c>
       <c r="C11" s="33">
         <f>SUM(C7:C10)</f>
-        <v>302202</v>
+        <v>302070</v>
       </c>
       <c r="D11" s="33">
         <f>SUM(D7:D10)</f>
-        <v>423299</v>
+        <v>422934</v>
       </c>
       <c r="E11" s="33">
         <f>SUM(E7:E10)</f>
-        <v>522542</v>
+        <v>521874</v>
       </c>
       <c r="F11" s="33">
         <f>SUM(F7:F10)</f>
-        <v>597645</v>
+        <v>596641</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B13" s="31">
         <v>13400</v>
       </c>
       <c r="C13" s="31">
-        <v>13736</v>
+        <v>13730</v>
       </c>
       <c r="D13" s="31">
-        <v>14110</v>
+        <v>14098</v>
       </c>
       <c r="E13" s="31">
-        <v>14515</v>
+        <v>14497</v>
       </c>
       <c r="F13" s="31">
-        <v>14941</v>
+        <v>14916</v>
       </c>
     </row>
   </sheetData>
@@ -2505,7 +2659,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2518,24 +2672,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2545,7 +2699,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B5" s="31">
         <v>13456</v>
@@ -2565,7 +2719,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="B6" s="32">
         <f>SUM(B5:B5)</f>
@@ -2590,7 +2744,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -2600,7 +2754,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="B8" s="31">
         <v>51060</v>
@@ -2620,7 +2774,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B8:B8)</f>
@@ -2645,7 +2799,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="B11" s="33">
         <f>B6+B9</f>
@@ -2685,7 +2839,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -2694,7 +2848,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2707,24 +2861,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2734,7 +2888,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B5" s="31">
         <v>75000</v>
@@ -2754,27 +2908,27 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="B6" s="31">
         <v>2500</v>
       </c>
       <c r="C6" s="31">
-        <v>4532</v>
+        <v>4400</v>
       </c>
       <c r="D6" s="31">
-        <v>6365</v>
+        <v>6000</v>
       </c>
       <c r="E6" s="31">
-        <v>7868</v>
+        <v>7200</v>
       </c>
       <c r="F6" s="31">
-        <v>9004</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="B7" s="31">
         <v>87500</v>
@@ -2794,7 +2948,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="B8" s="31">
         <v>2500</v>
@@ -2814,7 +2968,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
@@ -2822,24 +2976,24 @@
       </c>
       <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
-        <v>302202</v>
+        <v>302070</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
-        <v>423299</v>
+        <v>422934</v>
       </c>
       <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
-        <v>522542</v>
+        <v>521874</v>
       </c>
       <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
-        <v>597645</v>
+        <v>596641</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -2849,7 +3003,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="B12" s="31">
         <v>51060</v>
@@ -2869,7 +3023,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="B13" s="31">
         <v>13456</v>
@@ -2889,7 +3043,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="B14" s="32">
         <f>SUM(B12:B13)</f>
@@ -2914,7 +3068,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -2924,12 +3078,12 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="B18" s="31">
         <v>5000</v>
@@ -2949,12 +3103,12 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="B20" s="31">
         <v>3125</v>
@@ -2974,12 +3128,12 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="B22" s="31">
         <v>18000</v>
@@ -2999,7 +3153,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="B23" s="31">
         <v>2000</v>
@@ -3019,7 +3173,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="B24" s="31">
         <v>1500</v>
@@ -3039,7 +3193,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="B25" s="32">
         <f>SUM(B22:B24)</f>
@@ -3062,63 +3216,88 @@
         <v>29038</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="B26" s="32">
-        <f>B18+B20+B25</f>
-        <v>29625</v>
-      </c>
-      <c r="C26" s="32">
-        <f>C18+C20+C25</f>
-        <v>41303</v>
-      </c>
-      <c r="D26" s="32">
-        <f>D18+D20+D25</f>
-        <v>48059</v>
-      </c>
-      <c r="E26" s="32">
-        <f>E18+E20+E25</f>
-        <v>53762</v>
-      </c>
-      <c r="F26" s="32">
-        <f>F18+F20+F25</f>
-        <v>58301</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="B29" s="32" t="str">
-        <f>SUM(B29:B28)</f>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="37" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="B27" s="31">
+        <v>3750</v>
+      </c>
+      <c r="C27" s="31">
+        <v>4500</v>
+      </c>
+      <c r="D27" s="31">
+        <v>4500</v>
+      </c>
+      <c r="E27" s="31">
+        <v>4500</v>
+      </c>
+      <c r="F27" s="31">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" s="32">
+        <f>B18+B20+B25+B27</f>
+        <v>33375</v>
+      </c>
+      <c r="C28" s="32">
+        <f>C18+C20+C25+C27</f>
+        <v>45803</v>
+      </c>
+      <c r="D28" s="32">
+        <f>D18+D20+D25+D27</f>
+        <v>52559</v>
+      </c>
+      <c r="E28" s="32">
+        <f>E18+E20+E25+E27</f>
+        <v>58262</v>
+      </c>
+      <c r="F28" s="32">
+        <f>F18+F20+F25+F27</f>
+        <v>62801</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B31" s="32" t="str">
+        <f>SUM(B31:B30)</f>
         <v>0</v>
       </c>
-      <c r="C29" s="32" t="str">
-        <f>SUM(C29:C28)</f>
+      <c r="C31" s="32" t="str">
+        <f>SUM(C31:C30)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="32" t="str">
-        <f>SUM(D29:D28)</f>
+      <c r="D31" s="32" t="str">
+        <f>SUM(D31:D30)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="32" t="str">
-        <f>SUM(E29:E28)</f>
+      <c r="E31" s="32" t="str">
+        <f>SUM(E31:E30)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="32" t="str">
-        <f>SUM(F29:F28)</f>
+      <c r="F31" s="32" t="str">
+        <f>SUM(F31:F30)</f>
         <v>0</v>
       </c>
     </row>
@@ -3148,7 +3327,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3161,24 +3340,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="B4" s="34">
         <f>'Budget Detail'!B9</f>
@@ -3186,24 +3365,24 @@
       </c>
       <c r="C4" s="34">
         <f>'Budget Detail'!C9</f>
-        <v>302202</v>
+        <v>302070</v>
       </c>
       <c r="D4" s="34">
         <f>'Budget Detail'!D9</f>
-        <v>423299</v>
+        <v>422934</v>
       </c>
       <c r="E4" s="34">
         <f>'Budget Detail'!E9</f>
-        <v>522542</v>
+        <v>521874</v>
       </c>
       <c r="F4" s="34">
         <f>'Budget Detail'!F9</f>
-        <v>597645</v>
+        <v>596641</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="B5" s="34">
         <f>'Budget Detail'!B14</f>
@@ -3228,82 +3407,82 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="B6" s="34">
-        <f>'Budget Detail'!B26</f>
-        <v>29625</v>
+        <f>'Budget Detail'!B28</f>
+        <v>33375</v>
       </c>
       <c r="C6" s="34">
-        <f>'Budget Detail'!C26</f>
-        <v>41303</v>
+        <f>'Budget Detail'!C28</f>
+        <v>45803</v>
       </c>
       <c r="D6" s="34">
-        <f>'Budget Detail'!D26</f>
-        <v>48059</v>
+        <f>'Budget Detail'!D28</f>
+        <v>52559</v>
       </c>
       <c r="E6" s="34">
-        <f>'Budget Detail'!E26</f>
-        <v>53762</v>
+        <f>'Budget Detail'!E28</f>
+        <v>58262</v>
       </c>
       <c r="F6" s="34">
-        <f>'Budget Detail'!F26</f>
-        <v>58301</v>
+        <f>'Budget Detail'!F28</f>
+        <v>62801</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="B7" s="34" t="str">
-        <f>'Budget Detail'!B29</f>
+        <f>'Budget Detail'!B31</f>
         <v>0</v>
       </c>
       <c r="C7" s="34" t="str">
-        <f>'Budget Detail'!C29</f>
+        <f>'Budget Detail'!C31</f>
         <v>0</v>
       </c>
       <c r="D7" s="34" t="str">
-        <f>'Budget Detail'!D29</f>
+        <f>'Budget Detail'!D31</f>
         <v>0</v>
       </c>
       <c r="E7" s="34" t="str">
-        <f>'Budget Detail'!E29</f>
+        <f>'Budget Detail'!E31</f>
         <v>0</v>
       </c>
       <c r="F7" s="34" t="str">
-        <f>'Budget Detail'!F29</f>
+        <f>'Budget Detail'!F31</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
-        <v>94141</v>
+        <v>97891</v>
       </c>
       <c r="C8" s="32">
         <f>SUM(C5:C7)</f>
-        <v>121045</v>
+        <v>125545</v>
       </c>
       <c r="D8" s="32">
         <f>SUM(D5:D7)</f>
-        <v>130193</v>
+        <v>134693</v>
       </c>
       <c r="E8" s="32">
         <f>SUM(E5:E7)</f>
-        <v>138361</v>
+        <v>142861</v>
       </c>
       <c r="F8" s="32">
         <f>SUM(F5:F7)</f>
-        <v>145438</v>
+        <v>149938</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -3313,112 +3492,112 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="B11" s="33">
         <f>B4-B8</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C11" s="33">
         <f>C4-C8</f>
-        <v>181157</v>
+        <v>176525</v>
       </c>
       <c r="D11" s="33">
         <f>D4-D8</f>
-        <v>293106</v>
+        <v>288241</v>
       </c>
       <c r="E11" s="33">
         <f>E4-E8</f>
-        <v>384182</v>
+        <v>379014</v>
       </c>
       <c r="F11" s="33">
         <f>F4-F8</f>
-        <v>452207</v>
+        <v>446703</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
-        <v>0.43796269</v>
+        <v>0.41557463</v>
       </c>
       <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
-        <v>0.59945637</v>
+        <v>0.58438413</v>
       </c>
       <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
-        <v>0.69243233</v>
+        <v>0.68152664</v>
       </c>
       <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
-        <v>0.73521644</v>
+        <v>0.72625493</v>
       </c>
       <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
-        <v>0.75664878</v>
+        <v>0.74869702</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="B13" s="31">
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C13" s="31">
-        <v>254516</v>
+        <v>246134</v>
       </c>
       <c r="D13" s="31">
-        <v>547622</v>
+        <v>534374</v>
       </c>
       <c r="E13" s="31">
-        <v>931803</v>
+        <v>913388</v>
       </c>
       <c r="F13" s="31">
-        <v>1384011</v>
+        <v>1360092</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B14" s="31">
         <v>11167</v>
       </c>
       <c r="C14" s="31">
-        <v>13736</v>
+        <v>13730</v>
       </c>
       <c r="D14" s="31">
-        <v>14110</v>
+        <v>14098</v>
       </c>
       <c r="E14" s="31">
-        <v>14515</v>
+        <v>14497</v>
       </c>
       <c r="F14" s="31">
-        <v>14941</v>
+        <v>14916</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="B15" s="31">
-        <v>6276</v>
+        <v>6526</v>
       </c>
       <c r="C15" s="31">
-        <v>5502</v>
+        <v>5707</v>
       </c>
       <c r="D15" s="31">
-        <v>4340</v>
+        <v>4490</v>
       </c>
       <c r="E15" s="31">
-        <v>3843</v>
+        <v>3968</v>
       </c>
       <c r="F15" s="31">
-        <v>3636</v>
+        <v>3748</v>
       </c>
     </row>
   </sheetData>
@@ -3438,7 +3617,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3448,7 +3627,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3469,48 +3648,48 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -3528,7 +3707,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="B4" s="32">
         <v>11050</v>
@@ -3573,7 +3752,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -3591,7 +3770,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="B7" s="31">
         <v>6452</v>
@@ -3636,37 +3815,37 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="B8" s="31">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="C8" s="31">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="D8" s="31">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="E8" s="31">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="F8" s="31">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="G8" s="31">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="H8" s="31">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="I8" s="31">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="J8" s="31">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="K8" s="31">
-        <v>2963</v>
+        <v>3338</v>
       </c>
       <c r="L8" s="31">
         <v>0</v>
@@ -3676,12 +3855,12 @@
       </c>
       <c r="N8" s="31">
         <f>SUM(B8:M8)</f>
-        <v>29625</v>
+        <v>33375</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="B9" s="31">
         <v>0</v>
@@ -3726,7 +3905,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -3744,47 +3923,47 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="B12" s="34">
         <f>B7+B8+B9</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="C12" s="34">
         <f>C7+C8+C9</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="D12" s="34">
         <f>D7+D8+D9</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="E12" s="34">
         <f>E7+E8+E9</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="F12" s="34">
         <f>F7+F8+F9</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="G12" s="34">
         <f>G7+G8+G9</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="H12" s="34">
         <f>H7+H8+H9</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="I12" s="34">
         <f>I7+I8+I9</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="J12" s="34">
         <f>J7+J8+J9</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="K12" s="34">
         <f>K7+K8+K9</f>
-        <v>9415</v>
+        <v>9790</v>
       </c>
       <c r="L12" s="34" t="str">
         <f>L7+L8+L9</f>
@@ -3796,52 +3975,52 @@
       </c>
       <c r="N12" s="34">
         <f>SUM(B12:M12)</f>
-        <v>94150</v>
+        <v>97900</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="B13" s="34">
         <f>B4-B12</f>
-        <v>1635</v>
+        <v>1260</v>
       </c>
       <c r="C13" s="34">
         <f>C4-C12</f>
-        <v>10635</v>
+        <v>10260</v>
       </c>
       <c r="D13" s="34">
         <f>D4-D12</f>
-        <v>10635</v>
+        <v>10260</v>
       </c>
       <c r="E13" s="34">
         <f>E4-E12</f>
-        <v>10635</v>
+        <v>10260</v>
       </c>
       <c r="F13" s="34">
         <f>F4-F12</f>
-        <v>10635</v>
+        <v>10260</v>
       </c>
       <c r="G13" s="34">
         <f>G4-G12</f>
-        <v>10635</v>
+        <v>10260</v>
       </c>
       <c r="H13" s="34">
         <f>H4-H12</f>
-        <v>10635</v>
+        <v>10260</v>
       </c>
       <c r="I13" s="34">
         <f>I4-I12</f>
-        <v>10635</v>
+        <v>10260</v>
       </c>
       <c r="J13" s="34">
         <f>J4-J12</f>
-        <v>10635</v>
+        <v>10260</v>
       </c>
       <c r="K13" s="34">
         <f>K4-K12</f>
-        <v>10635</v>
+        <v>10260</v>
       </c>
       <c r="L13" s="34">
         <f>L4-L12</f>
@@ -3853,76 +4032,76 @@
       </c>
       <c r="N13" s="34">
         <f>SUM(B13:M13)</f>
-        <v>106850</v>
+        <v>103100</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="B14" s="38">
         <f>B17+B13</f>
-        <v>1635</v>
+        <v>1260</v>
       </c>
       <c r="C14" s="38">
         <f>B14+C13</f>
-        <v>12270</v>
+        <v>11520</v>
       </c>
       <c r="D14" s="38">
         <f>C14+D13</f>
-        <v>22905</v>
+        <v>21780</v>
       </c>
       <c r="E14" s="38">
         <f>D14+E13</f>
-        <v>33540</v>
+        <v>32040</v>
       </c>
       <c r="F14" s="38">
         <f>E14+F13</f>
-        <v>44175</v>
+        <v>42300</v>
       </c>
       <c r="G14" s="38">
         <f>F14+G13</f>
-        <v>54810</v>
+        <v>52560</v>
       </c>
       <c r="H14" s="38">
         <f>G14+H13</f>
-        <v>65445</v>
+        <v>62820</v>
       </c>
       <c r="I14" s="38">
         <f>H14+I13</f>
-        <v>76080</v>
+        <v>73080</v>
       </c>
       <c r="J14" s="38">
         <f>I14+J13</f>
-        <v>86715</v>
+        <v>83340</v>
       </c>
       <c r="K14" s="38">
         <f>J14+K13</f>
-        <v>97350</v>
+        <v>93600</v>
       </c>
       <c r="L14" s="38">
         <f>K14+L13</f>
-        <v>106600</v>
+        <v>102850</v>
       </c>
       <c r="M14" s="38">
         <f>L14+M13</f>
-        <v>106850</v>
+        <v>103100</v>
       </c>
       <c r="N14" s="33">
         <f>M14</f>
-        <v>106850</v>
+        <v>103100</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B17" s="23">
         <v>0</v>
@@ -3930,25 +4109,49 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="B18" s="38">
         <f>M14</f>
-        <v>106850</v>
+        <v>103100</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="B19" s="31">
         <f>MIN(B14:M14)</f>
-        <v>1635</v>
-      </c>
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="39" t="s">
+        <v>298</v>
+      </c>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:H21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -3963,7 +4166,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -3972,7 +4175,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3980,29 +4183,39 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>300</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+    </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4011,28 +4224,28 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
-        <v>229</v>
+      <c r="A5" s="41" t="s">
+        <v>251</v>
       </c>
       <c r="B5" s="32">
         <v>167500</v>
       </c>
       <c r="C5" s="32">
-        <v>302202</v>
+        <v>302070</v>
       </c>
       <c r="D5" s="32">
-        <v>423299</v>
+        <v>422934</v>
       </c>
       <c r="E5" s="32">
-        <v>522542</v>
+        <v>521874</v>
       </c>
       <c r="F5" s="32">
-        <v>597645</v>
+        <v>596641</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4042,7 +4255,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="B8" s="34">
         <v>64516</v>
@@ -4062,27 +4275,27 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="B9" s="34">
-        <v>29625</v>
+        <v>33375</v>
       </c>
       <c r="C9" s="34">
-        <v>41303</v>
+        <v>45803</v>
       </c>
       <c r="D9" s="34">
-        <v>48059</v>
+        <v>52559</v>
       </c>
       <c r="E9" s="34">
-        <v>53762</v>
+        <v>58262</v>
       </c>
       <c r="F9" s="34">
-        <v>58301</v>
+        <v>62801</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="B10" s="34">
         <v>0</v>
@@ -4101,138 +4314,159 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
-        <v>244</v>
-      </c>
-      <c r="B11" s="32">
-        <f>SUM(B8:B10)</f>
-        <v>94141</v>
-      </c>
-      <c r="C11" s="32">
-        <f>SUM(C8:C10)</f>
-        <v>121045</v>
-      </c>
-      <c r="D11" s="32">
-        <f>SUM(D8:D10)</f>
-        <v>130193</v>
-      </c>
-      <c r="E11" s="32">
-        <f>SUM(E8:E10)</f>
-        <v>138361</v>
-      </c>
-      <c r="F11" s="32">
-        <f>SUM(F8:F10)</f>
-        <v>145438</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="39" t="s">
-        <v>246</v>
-      </c>
-      <c r="B14" s="33">
-        <f>B5-B11</f>
-        <v>73359</v>
-      </c>
-      <c r="C14" s="33">
-        <f>C5-C11</f>
-        <v>181157</v>
-      </c>
-      <c r="D14" s="33">
-        <f>D5-D11</f>
-        <v>293106</v>
-      </c>
-      <c r="E14" s="33">
-        <f>E5-E11</f>
-        <v>384182</v>
-      </c>
-      <c r="F14" s="33">
-        <f>F5-F11</f>
-        <v>452207</v>
-      </c>
+      <c r="A11" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="B11" s="34">
+        <v>286</v>
+      </c>
+      <c r="C11" s="34">
+        <v>286</v>
+      </c>
+      <c r="D11" s="34">
+        <v>286</v>
+      </c>
+      <c r="E11" s="34">
+        <v>286</v>
+      </c>
+      <c r="F11" s="34">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="B12" s="32">
+        <f>SUM(B8:B11)</f>
+        <v>98177</v>
+      </c>
+      <c r="C12" s="32">
+        <f>SUM(C8:C11)</f>
+        <v>125831</v>
+      </c>
+      <c r="D12" s="32">
+        <f>SUM(D8:D11)</f>
+        <v>134979</v>
+      </c>
+      <c r="E12" s="32">
+        <f>SUM(E8:E11)</f>
+        <v>143146</v>
+      </c>
+      <c r="F12" s="32">
+        <f>SUM(F8:F11)</f>
+        <v>150223</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="B15" s="29">
-        <f>IF(B5=0,0,B14/B5)</f>
-        <v>0.43796269</v>
-      </c>
-      <c r="C15" s="29">
-        <f>IF(C5=0,0,C14/C5)</f>
-        <v>0.59945637</v>
-      </c>
-      <c r="D15" s="29">
-        <f>IF(D5=0,0,D14/D5)</f>
-        <v>0.69243233</v>
-      </c>
-      <c r="E15" s="29">
-        <f>IF(E5=0,0,E14/E5)</f>
-        <v>0.73521644</v>
-      </c>
-      <c r="F15" s="29">
-        <f>IF(F5=0,0,F14/F5)</f>
-        <v>0.75664878</v>
+      <c r="A15" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="B15" s="33">
+        <f>B5-B12</f>
+        <v>69323</v>
+      </c>
+      <c r="C15" s="33">
+        <f>C5-C12</f>
+        <v>176239</v>
+      </c>
+      <c r="D15" s="33">
+        <f>D5-D12</f>
+        <v>287955</v>
+      </c>
+      <c r="E15" s="33">
+        <f>E5-E12</f>
+        <v>378728</v>
+      </c>
+      <c r="F15" s="33">
+        <f>F5-F12</f>
+        <v>446418</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="B16" s="34">
-        <f>B14</f>
-        <v>73359</v>
-      </c>
-      <c r="C16" s="34">
-        <f>B16+C14</f>
-        <v>254516</v>
-      </c>
-      <c r="D16" s="34">
-        <f>C16+D14</f>
-        <v>547622</v>
-      </c>
-      <c r="E16" s="34">
-        <f>D16+E14</f>
-        <v>931803</v>
-      </c>
-      <c r="F16" s="34">
-        <f>E16+F14</f>
-        <v>1384011</v>
+      <c r="A16" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="B16" s="29">
+        <f>IF(B5=0,0,B15/B5)</f>
+        <v>0.41386887</v>
+      </c>
+      <c r="C16" s="29">
+        <f>IF(C5=0,0,C15/C5)</f>
+        <v>0.58343828</v>
+      </c>
+      <c r="D16" s="29">
+        <f>IF(D5=0,0,D15/D5)</f>
+        <v>0.68085108</v>
+      </c>
+      <c r="E16" s="29">
+        <f>IF(E5=0,0,E15/E5)</f>
+        <v>0.72570746</v>
+      </c>
+      <c r="F16" s="29">
+        <f>IF(F5=0,0,F15/F5)</f>
+        <v>0.74821815</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="B17" s="40" t="s">
-        <v>278</v>
-      </c>
-      <c r="C17" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="B17" s="34">
+        <f>B15</f>
+        <v>69323</v>
+      </c>
+      <c r="C17" s="34">
+        <f>B17+C15</f>
+        <v>245562</v>
+      </c>
+      <c r="D17" s="34">
+        <f>C17+D15</f>
+        <v>533517</v>
+      </c>
+      <c r="E17" s="34">
+        <f>D17+E15</f>
+        <v>912245</v>
+      </c>
+      <c r="F17" s="34">
+        <f>E17+F15</f>
+        <v>1358663</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>305</v>
+      </c>
+      <c r="C18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F18" s="43" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4269,24 +4503,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4295,20 +4529,20 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
-        <v>280</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>281</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>282</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>210</v>
+      <c r="A5" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -4337,7 +4571,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4350,24 +4584,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4377,72 +4611,72 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="B5" s="45">
+        <v>312</v>
+      </c>
+      <c r="B5" s="47">
         <f>'Monthly Cash Flow Y1'!M14</f>
-        <v>106850</v>
-      </c>
-      <c r="C5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14</f>
-        <v>288007</v>
-      </c>
-      <c r="D5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
-        <v>581113</v>
-      </c>
-      <c r="E5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
-        <v>965294</v>
-      </c>
-      <c r="F5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
-        <v>1417502</v>
+        <v>103100</v>
+      </c>
+      <c r="C5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15</f>
+        <v>279625</v>
+      </c>
+      <c r="D5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
+        <v>567865</v>
+      </c>
+      <c r="E5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
+        <v>946879</v>
+      </c>
+      <c r="F5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
+        <v>1393583</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="B6" s="31">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="C6" s="31">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="D6" s="31">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="E6" s="31">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="F6" s="31">
-        <v>0</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="B7" s="31">
-        <v>2000</v>
+        <v>1714</v>
       </c>
       <c r="C7" s="31">
-        <v>2000</v>
+        <v>1429</v>
       </c>
       <c r="D7" s="31">
-        <v>2000</v>
+        <v>1143</v>
       </c>
       <c r="E7" s="31">
-        <v>2000</v>
+        <v>857</v>
       </c>
       <c r="F7" s="31">
-        <v>2000</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="B8" s="31">
         <v>0</v>
@@ -4462,32 +4696,32 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
-        <v>108850</v>
+        <v>105324</v>
       </c>
       <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
-        <v>290007</v>
+        <v>281578</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
-        <v>583113</v>
+        <v>569548</v>
       </c>
       <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
-        <v>967294</v>
+        <v>948292</v>
       </c>
       <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
-        <v>1419502</v>
+        <v>1394726</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4497,7 +4731,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="B12" s="31">
         <v>0</v>
@@ -4517,7 +4751,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="B13" s="31">
         <v>0</v>
@@ -4537,7 +4771,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="B14" s="32" t="str">
         <f>SUM(B12:B13)</f>
@@ -4562,7 +4796,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4572,50 +4806,50 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="B17" s="33">
         <f>B9-B14</f>
-        <v>108850</v>
+        <v>105324</v>
       </c>
       <c r="C17" s="33">
         <f>C9-C14</f>
-        <v>290007</v>
+        <v>281578</v>
       </c>
       <c r="D17" s="33">
         <f>D9-D14</f>
-        <v>583113</v>
+        <v>569548</v>
       </c>
       <c r="E17" s="33">
         <f>E9-E14</f>
-        <v>967294</v>
+        <v>948292</v>
       </c>
       <c r="F17" s="33">
         <f>F9-F14</f>
-        <v>1419502</v>
+        <v>1394726</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="B19" s="46" t="str">
+        <v>323</v>
+      </c>
+      <c r="B19" s="48" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="46" t="str">
+      <c r="C19" s="48" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="46" t="str">
+      <c r="D19" s="48" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="46" t="str">
+      <c r="E19" s="48" t="str">
         <f>E9-E14-E17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="46" t="str">
+      <c r="F19" s="48" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -4637,7 +4871,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4646,7 +4880,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4659,24 +4893,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4686,27 +4920,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="B5" s="31">
         <v>167500</v>
       </c>
       <c r="C5" s="31">
-        <v>302202</v>
+        <v>302070</v>
       </c>
       <c r="D5" s="31">
-        <v>423299</v>
+        <v>422934</v>
       </c>
       <c r="E5" s="31">
-        <v>522542</v>
+        <v>521874</v>
       </c>
       <c r="F5" s="31">
-        <v>597645</v>
+        <v>596641</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="B6" s="31">
         <v>64516</v>
@@ -4726,387 +4960,447 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="B7" s="31">
-        <v>29625</v>
+        <v>33375</v>
       </c>
       <c r="C7" s="31">
-        <v>41303</v>
+        <v>45803</v>
       </c>
       <c r="D7" s="31">
-        <v>48059</v>
+        <v>52559</v>
       </c>
       <c r="E7" s="31">
-        <v>53762</v>
+        <v>58262</v>
       </c>
       <c r="F7" s="31">
-        <v>58301</v>
+        <v>62801</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="B8" s="34">
-        <f>B5-B6-B7</f>
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C8" s="34">
-        <f>C5-C6-C7</f>
-        <v>181157</v>
+        <v>176525</v>
       </c>
       <c r="D8" s="34">
-        <f>D5-D6-D7</f>
-        <v>293106</v>
+        <v>288241</v>
       </c>
       <c r="E8" s="34">
-        <f>E5-E6-E7</f>
-        <v>384182</v>
+        <v>379014</v>
       </c>
       <c r="F8" s="34">
-        <f>F5-F6-F7</f>
-        <v>452207</v>
+        <v>446703</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>267</v>
+        <v>327</v>
       </c>
       <c r="B9" s="31">
+        <v>286</v>
+      </c>
+      <c r="C9" s="31">
+        <v>286</v>
+      </c>
+      <c r="D9" s="31">
+        <v>286</v>
+      </c>
+      <c r="E9" s="31">
+        <v>286</v>
+      </c>
+      <c r="F9" s="31">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="B10" s="31">
         <v>0</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C10" s="31">
         <v>0</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D10" s="31">
         <v>0</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E10" s="31">
         <v>0</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F10" s="31">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>302</v>
-      </c>
-      <c r="F10" s="47" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="B13" s="31">
-        <v>106850</v>
-      </c>
-      <c r="C13" s="31">
-        <v>288007</v>
-      </c>
-      <c r="D13" s="31">
-        <v>581113</v>
-      </c>
-      <c r="E13" s="31">
-        <v>965294</v>
-      </c>
-      <c r="F13" s="31">
-        <v>1417502</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="B14" s="48">
-        <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
-        <v>414</v>
-      </c>
-      <c r="C14" s="48">
-        <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
-        <v>868</v>
-      </c>
-      <c r="D14" s="48">
-        <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
-        <v>1629</v>
-      </c>
-      <c r="E14" s="48">
-        <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
-        <v>2546</v>
-      </c>
-      <c r="F14" s="48">
-        <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
-        <v>3557</v>
-      </c>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="B11" s="34">
+        <f>B8+B9+B10</f>
+        <v>69894</v>
+      </c>
+      <c r="C11" s="34">
+        <f>C8+C9+C10</f>
+        <v>176811</v>
+      </c>
+      <c r="D11" s="34">
+        <f>D8+D9+D10</f>
+        <v>288526</v>
+      </c>
+      <c r="E11" s="34">
+        <f>E8+E9+E10</f>
+        <v>379300</v>
+      </c>
+      <c r="F11" s="34">
+        <f>F8+F9+F10</f>
+        <v>446989</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="B15" s="35">
-        <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
-        <v>13.6</v>
-      </c>
-      <c r="C15" s="35">
-        <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
-        <v>28.6</v>
-      </c>
-      <c r="D15" s="35">
-        <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
-        <v>53.6</v>
-      </c>
-      <c r="E15" s="35">
-        <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
-        <v>83.7</v>
-      </c>
-      <c r="F15" s="35">
-        <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
-        <v>117</v>
+        <v>333</v>
+      </c>
+      <c r="B15" s="31">
+        <v>103100</v>
+      </c>
+      <c r="C15" s="31">
+        <v>279625</v>
+      </c>
+      <c r="D15" s="31">
+        <v>567865</v>
+      </c>
+      <c r="E15" s="31">
+        <v>946879</v>
+      </c>
+      <c r="F15" s="31">
+        <v>1393583</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B16" s="29">
+        <v>334</v>
+      </c>
+      <c r="B16" s="50">
+        <f>IF((B5-B8)=0,0,(B15/(B5-B8))*365)</f>
+        <v>384</v>
+      </c>
+      <c r="C16" s="50">
+        <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
+        <v>813</v>
+      </c>
+      <c r="D16" s="50">
+        <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
+        <v>1539</v>
+      </c>
+      <c r="E16" s="50">
+        <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
+        <v>2419</v>
+      </c>
+      <c r="F16" s="50">
+        <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
+        <v>3392</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="B17" s="35">
+        <f>IF((B5-B8)=0,0,B15/((B5-B8)/12))</f>
+        <v>12.6</v>
+      </c>
+      <c r="C17" s="35">
+        <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
+        <v>26.7</v>
+      </c>
+      <c r="D17" s="35">
+        <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
+        <v>50.6</v>
+      </c>
+      <c r="E17" s="35">
+        <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
+        <v>79.5</v>
+      </c>
+      <c r="F17" s="35">
+        <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
+        <v>111.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B18" s="29">
         <v>0.375</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C18" s="29">
         <v>0.55</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D18" s="29">
         <v>0.75</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E18" s="29">
         <v>0.9</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F18" s="29">
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="B19" s="31">
-        <v>11167</v>
-      </c>
-      <c r="C19" s="31">
-        <v>13736</v>
-      </c>
-      <c r="D19" s="31">
-        <v>14110</v>
-      </c>
-      <c r="E19" s="31">
-        <v>14515</v>
-      </c>
-      <c r="F19" s="31">
-        <v>14941</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="B20" s="31">
-        <v>64516</v>
-      </c>
-      <c r="C20" s="31">
-        <v>79742</v>
-      </c>
-      <c r="D20" s="31">
-        <v>82134</v>
-      </c>
-      <c r="E20" s="31">
-        <v>84598</v>
-      </c>
-      <c r="F20" s="31">
-        <v>87136</v>
-      </c>
+    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>309</v>
+        <v>238</v>
       </c>
       <c r="B21" s="31">
-        <v>1975</v>
+        <v>11167</v>
       </c>
       <c r="C21" s="31">
-        <v>1877</v>
+        <v>13730</v>
       </c>
       <c r="D21" s="31">
-        <v>1602</v>
+        <v>14098</v>
       </c>
       <c r="E21" s="31">
-        <v>1493</v>
+        <v>14497</v>
       </c>
       <c r="F21" s="31">
-        <v>1458</v>
+        <v>14916</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="B22" s="49">
+      <c r="A22" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="B22" s="31">
+        <v>64516</v>
+      </c>
+      <c r="C22" s="31">
+        <v>79742</v>
+      </c>
+      <c r="D22" s="31">
+        <v>82134</v>
+      </c>
+      <c r="E22" s="31">
+        <v>84598</v>
+      </c>
+      <c r="F22" s="31">
+        <v>87136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="B23" s="31">
+        <v>2225</v>
+      </c>
+      <c r="C23" s="31">
+        <v>2082</v>
+      </c>
+      <c r="D23" s="31">
+        <v>1752</v>
+      </c>
+      <c r="E23" s="31">
+        <v>1618</v>
+      </c>
+      <c r="F23" s="31">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="B24" s="51">
         <v>8</v>
       </c>
-      <c r="C22" s="49">
+      <c r="C24" s="51">
         <v>7</v>
       </c>
-      <c r="D22" s="49">
+      <c r="D24" s="51">
         <v>7</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E24" s="51">
         <v>7</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F24" s="51">
         <v>7</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>302</v>
-      </c>
-      <c r="C25" s="50" t="s">
-        <v>302</v>
-      </c>
-      <c r="D25" s="50" t="s">
-        <v>302</v>
-      </c>
-      <c r="E25" s="50" t="s">
-        <v>302</v>
-      </c>
-      <c r="F25" s="50" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B26" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="D26" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="E26" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="F26" s="51" t="s">
-        <v>314</v>
-      </c>
+    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="C27" s="52" t="s">
-        <v>316</v>
-      </c>
-      <c r="D27" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="F27" s="51" t="s">
-        <v>314</v>
+        <v>331</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="E27" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="F27" s="52" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B28" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="D28" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="E28" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="F28" s="51" t="s">
-        <v>314</v>
+        <v>342</v>
+      </c>
+      <c r="B28" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="D28" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="F28" s="53" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="B29" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="E29" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="F29" s="51" t="s">
-        <v>314</v>
+        <v>344</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="F29" s="52" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>346</v>
+      </c>
+      <c r="C30" s="54" t="s">
+        <v>346</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="F32" s="53" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -5146,28 +5440,28 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
-        <v>319</v>
-      </c>
-      <c r="B3" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="53" t="s">
-        <v>320</v>
-      </c>
-      <c r="E3" s="53" t="s">
-        <v>112</v>
+      <c r="A3" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>350</v>
+      </c>
+      <c r="E3" s="55" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="B4" s="31">
         <v>12000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="E4" s="31">
         <v>12000</v>
@@ -5175,13 +5469,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="B6" s="33">
         <v>12000</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="E6" s="33">
         <v>12000</v>
@@ -5189,9 +5483,9 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="B7" s="46">
+        <v>355</v>
+      </c>
+      <c r="B7" s="48">
         <v>0</v>
       </c>
     </row>
@@ -5212,7 +5506,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C43"/>
+  <dimension ref="B3:C44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5478,18 +5772,26 @@
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="14" t="s">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="14"/>
+      <c r="C41" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Instructions'!A1"/>
@@ -5514,6 +5816,7 @@
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
     <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
     <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
+    <hyperlink ref="C41" r:id="rId23" location="#'Budget Narrative'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -5537,7 +5840,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5547,7 +5850,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -5557,7 +5860,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5565,144 +5868,144 @@
         <v>7</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="B6" s="31">
         <v>167500</v>
       </c>
       <c r="C6" s="31">
-        <v>302202</v>
+        <v>302070</v>
       </c>
       <c r="D6" s="31">
-        <v>423299</v>
+        <v>422934</v>
       </c>
       <c r="E6" s="31">
-        <v>522542</v>
+        <v>521874</v>
       </c>
       <c r="F6" s="31">
-        <v>597645</v>
+        <v>596641</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="B7" s="31">
-        <v>94141</v>
+        <v>97891</v>
       </c>
       <c r="C7" s="31">
-        <v>121045</v>
+        <v>125545</v>
       </c>
       <c r="D7" s="31">
-        <v>130193</v>
+        <v>134693</v>
       </c>
       <c r="E7" s="31">
-        <v>138361</v>
+        <v>142861</v>
       </c>
       <c r="F7" s="31">
-        <v>145438</v>
+        <v>149938</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="B8" s="33">
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="C8" s="33">
-        <v>181157</v>
+        <v>176525</v>
       </c>
       <c r="D8" s="33">
-        <v>293106</v>
+        <v>288241</v>
       </c>
       <c r="E8" s="33">
-        <v>384182</v>
+        <v>379014</v>
       </c>
       <c r="F8" s="33">
-        <v>452207</v>
+        <v>446703</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="B9" s="29">
-        <v>0.4379626865671642</v>
+        <v>0.41557462686567165</v>
       </c>
       <c r="C9" s="29">
-        <v>0.5994563735514655</v>
+        <v>0.5843841328168967</v>
       </c>
       <c r="D9" s="29">
-        <v>0.6924323308270677</v>
+        <v>0.6815266375084321</v>
       </c>
       <c r="E9" s="29">
-        <v>0.7352164366373901</v>
+        <v>0.7262549346685067</v>
       </c>
       <c r="F9" s="29">
-        <v>0.7566487758945386</v>
+        <v>0.7486970244652048</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="B10" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="C10" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="D10" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="E10" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>302</v>
+        <v>330</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="D10" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="E10" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="F10" s="56" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="B11" s="48">
+        <v>339</v>
+      </c>
+      <c r="B11" s="50">
         <v>8</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="50">
         <v>7</v>
       </c>
-      <c r="D11" s="48">
+      <c r="D11" s="50">
         <v>7</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="50">
         <v>7</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="50">
         <v>7</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -5712,7 +6015,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5720,138 +6023,138 @@
         <v>7</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="B16" s="31">
         <v>125625</v>
       </c>
       <c r="C16" s="31">
-        <v>226652</v>
+        <v>226553</v>
       </c>
       <c r="D16" s="31">
-        <v>317474</v>
+        <v>317200</v>
       </c>
       <c r="E16" s="31">
-        <v>391907</v>
+        <v>391406</v>
       </c>
       <c r="F16" s="31">
-        <v>448234</v>
+        <v>447481</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="B17" s="31">
-        <v>94141</v>
+        <v>97891</v>
       </c>
       <c r="C17" s="31">
-        <v>121045</v>
+        <v>125545</v>
       </c>
       <c r="D17" s="31">
-        <v>130193</v>
+        <v>134693</v>
       </c>
       <c r="E17" s="31">
-        <v>138361</v>
+        <v>142861</v>
       </c>
       <c r="F17" s="31">
-        <v>145438</v>
+        <v>149938</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="B18" s="33">
-        <v>31484</v>
+        <v>27734</v>
       </c>
       <c r="C18" s="33">
-        <v>105606</v>
+        <v>101007</v>
       </c>
       <c r="D18" s="33">
-        <v>187281</v>
+        <v>182507</v>
       </c>
       <c r="E18" s="33">
-        <v>253546</v>
+        <v>248545</v>
       </c>
       <c r="F18" s="33">
-        <v>302796</v>
+        <v>297543</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="B19" s="29">
-        <v>0.25061691542288556</v>
+        <v>0.22076616915422886</v>
       </c>
       <c r="C19" s="29">
-        <v>0.46594183140195405</v>
+        <v>0.44584551042252896</v>
       </c>
       <c r="D19" s="29">
-        <v>0.5899097744360902</v>
+        <v>0.5753688500112429</v>
       </c>
       <c r="E19" s="29">
-        <v>0.6469552488498536</v>
+        <v>0.635006579558009</v>
       </c>
       <c r="F19" s="29">
-        <v>0.6755317011927182</v>
+        <v>0.6649293659536065</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="C20" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="D20" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="F20" s="54" t="s">
-        <v>302</v>
+        <v>330</v>
+      </c>
+      <c r="B20" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="D20" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="E20" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="F20" s="56" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="B21" s="48">
+        <v>339</v>
+      </c>
+      <c r="B21" s="50">
         <v>8</v>
       </c>
-      <c r="C21" s="48">
+      <c r="C21" s="50">
         <v>8</v>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="50">
         <v>8</v>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="50">
         <v>7</v>
       </c>
-      <c r="F21" s="48">
+      <c r="F21" s="50">
         <v>7</v>
       </c>
     </row>
@@ -5883,7 +6186,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5895,7 +6198,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B3" s="19"/>
     </row>
@@ -5909,7 +6212,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -5917,7 +6220,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -5941,7 +6244,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -5949,7 +6252,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -5969,105 +6272,105 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="55" t="s">
+      <c r="D12" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="55" t="s">
+      <c r="E12" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="55" t="s">
+      <c r="F12" s="57" t="s">
         <v>106</v>
+      </c>
+      <c r="G12" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="D13" s="31">
         <v>167500</v>
       </c>
       <c r="E13" s="31">
-        <v>302202</v>
+        <v>302070</v>
       </c>
       <c r="F13" s="31">
-        <v>423299</v>
+        <v>422934</v>
       </c>
       <c r="G13" s="31">
-        <v>522542</v>
+        <v>521874</v>
       </c>
       <c r="H13" s="31">
-        <v>597645</v>
+        <v>596641</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="D14" s="31">
-        <v>94141</v>
+        <v>97891</v>
       </c>
       <c r="E14" s="31">
-        <v>121045</v>
+        <v>125545</v>
       </c>
       <c r="F14" s="31">
-        <v>130193</v>
+        <v>134693</v>
       </c>
       <c r="G14" s="31">
-        <v>138361</v>
+        <v>142861</v>
       </c>
       <c r="H14" s="31">
-        <v>145438</v>
+        <v>149938</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="D15" s="31">
-        <v>73359</v>
+        <v>69609</v>
       </c>
       <c r="E15" s="31">
-        <v>181157</v>
+        <v>176525</v>
       </c>
       <c r="F15" s="31">
-        <v>293106</v>
+        <v>288241</v>
       </c>
       <c r="G15" s="31">
-        <v>384182</v>
+        <v>379014</v>
       </c>
       <c r="H15" s="31">
-        <v>452207</v>
+        <v>446703</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="D16" s="31">
-        <v>106850</v>
+        <v>103100</v>
       </c>
       <c r="E16" s="31">
-        <v>288007</v>
+        <v>279625</v>
       </c>
       <c r="F16" s="31">
-        <v>581113</v>
+        <v>567865</v>
       </c>
       <c r="G16" s="31">
-        <v>965294</v>
+        <v>946879</v>
       </c>
       <c r="H16" s="31">
-        <v>1417502</v>
+        <v>1393583</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D17" s="31">
         <v>0</v>
@@ -6087,7 +6390,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -6107,65 +6410,65 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="55" t="s">
+      <c r="D20" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="55" t="s">
+      <c r="E20" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="H20" s="55" t="s">
+      <c r="F20" s="57" t="s">
         <v>106</v>
+      </c>
+      <c r="G20" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="57" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="D21" s="29">
-        <v>0.4379626865671642</v>
+        <v>0.41557462686567165</v>
       </c>
       <c r="E21" s="29">
-        <v>0.5994563735514655</v>
+        <v>0.5843841328168967</v>
       </c>
       <c r="F21" s="29">
-        <v>0.6924323308270677</v>
+        <v>0.6815266375084321</v>
       </c>
       <c r="G21" s="29">
-        <v>0.7352164366373902</v>
+        <v>0.7262549346685067</v>
       </c>
       <c r="H21" s="29">
-        <v>0.7566487758945385</v>
+        <v>0.7486970244652047</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D22" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="E22" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="F22" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="G22" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="H22" s="54" t="s">
-        <v>302</v>
+        <v>330</v>
+      </c>
+      <c r="D22" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="E22" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="F22" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="G22" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="H22" s="56" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D23" s="29">
         <v>0.375</v>
@@ -6185,27 +6488,27 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="D24" s="48">
+        <v>369</v>
+      </c>
+      <c r="D24" s="50">
         <v>15</v>
       </c>
-      <c r="E24" s="48">
+      <c r="E24" s="50">
         <v>22</v>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="50">
         <v>30</v>
       </c>
-      <c r="G24" s="48">
+      <c r="G24" s="50">
         <v>36</v>
       </c>
-      <c r="H24" s="48">
+      <c r="H24" s="50">
         <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -6246,7 +6549,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6256,645 +6559,645 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="56" t="s">
-        <v>342</v>
-      </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
+      <c r="B3" s="58" t="s">
+        <v>372</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="57" t="s">
-        <v>343</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>344</v>
-      </c>
-      <c r="F4" s="59" t="s">
-        <v>345</v>
+      <c r="B4" s="59" t="s">
+        <v>373</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>374</v>
+      </c>
+      <c r="F4" s="61" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="C6" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="D6" s="60" t="s">
-        <v>348</v>
-      </c>
-      <c r="E6" s="60" t="s">
-        <v>349</v>
-      </c>
-      <c r="F6" s="60" t="s">
-        <v>350</v>
-      </c>
-      <c r="G6" s="60" t="s">
-        <v>351</v>
-      </c>
-      <c r="H6" s="60" t="s">
-        <v>352</v>
+        <v>376</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>377</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>378</v>
+      </c>
+      <c r="E6" s="62" t="s">
+        <v>379</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>380</v>
+      </c>
+      <c r="G6" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="C7" s="61">
+        <v>369</v>
+      </c>
+      <c r="C7" s="63">
         <v>15</v>
       </c>
-      <c r="D7" s="61">
+      <c r="D7" s="63">
         <v>22</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="63">
         <v>30</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="63">
         <v>36</v>
       </c>
-      <c r="G7" s="61">
+      <c r="G7" s="63">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="C8" s="62">
+        <v>326</v>
+      </c>
+      <c r="C8" s="64">
         <v>167500</v>
       </c>
-      <c r="D8" s="62">
-        <v>302202</v>
-      </c>
-      <c r="E8" s="62">
-        <v>423299.1</v>
-      </c>
-      <c r="F8" s="62">
-        <v>522542.0514</v>
-      </c>
-      <c r="G8" s="62">
-        <v>597645.1781100001</v>
+      <c r="D8" s="64">
+        <v>302070</v>
+      </c>
+      <c r="E8" s="64">
+        <v>422933.7</v>
+      </c>
+      <c r="F8" s="64">
+        <v>521874.417</v>
+      </c>
+      <c r="G8" s="64">
+        <v>596641.1076300001</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="C9" s="62">
+        <v>288</v>
+      </c>
+      <c r="C9" s="64">
         <v>64516.25</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="64">
         <v>79742.085</v>
       </c>
-      <c r="E9" s="62">
+      <c r="E9" s="64">
         <v>82134.34754999999</v>
       </c>
-      <c r="F9" s="62">
+      <c r="F9" s="64">
         <v>84598.3779765</v>
       </c>
-      <c r="G9" s="62">
+      <c r="G9" s="64">
         <v>87136.32931579501</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="C10" s="62">
-        <v>29625</v>
-      </c>
-      <c r="D10" s="62">
-        <v>41303</v>
-      </c>
-      <c r="E10" s="62">
-        <v>48058.77</v>
-      </c>
-      <c r="F10" s="62">
-        <v>53762.168399999995</v>
-      </c>
-      <c r="G10" s="62">
-        <v>58301.35635800001</v>
+        <v>289</v>
+      </c>
+      <c r="C10" s="64">
+        <v>33375</v>
+      </c>
+      <c r="D10" s="64">
+        <v>45803</v>
+      </c>
+      <c r="E10" s="64">
+        <v>52558.77</v>
+      </c>
+      <c r="F10" s="64">
+        <v>58262.168399999995</v>
+      </c>
+      <c r="G10" s="64">
+        <v>62801.35635800001</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="C11" s="62">
+        <v>290</v>
+      </c>
+      <c r="C11" s="64">
         <v>0</v>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="64">
         <v>0</v>
       </c>
-      <c r="E11" s="62">
+      <c r="E11" s="64">
         <v>0</v>
       </c>
-      <c r="F11" s="62">
+      <c r="F11" s="64">
         <v>0</v>
       </c>
-      <c r="G11" s="62">
+      <c r="G11" s="64">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="C12" s="63">
-        <v>73358.75</v>
-      </c>
-      <c r="D12" s="63">
-        <v>181156.91499999998</v>
-      </c>
-      <c r="E12" s="63">
-        <v>293105.98245</v>
-      </c>
-      <c r="F12" s="63">
-        <v>384181.5050235</v>
-      </c>
-      <c r="G12" s="63">
-        <v>452207.49243620504</v>
+        <v>269</v>
+      </c>
+      <c r="C12" s="65">
+        <v>69608.75</v>
+      </c>
+      <c r="D12" s="65">
+        <v>176524.91499999998</v>
+      </c>
+      <c r="E12" s="65">
+        <v>288240.58245</v>
+      </c>
+      <c r="F12" s="65">
+        <v>379013.8706235</v>
+      </c>
+      <c r="G12" s="65">
+        <v>446703.42195620504</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="C13" s="63">
-        <v>106850</v>
-      </c>
-      <c r="D13" s="63">
-        <v>288006.915</v>
-      </c>
-      <c r="E13" s="63">
-        <v>581112.89745</v>
-      </c>
-      <c r="F13" s="63">
-        <v>965294.4024735</v>
-      </c>
-      <c r="G13" s="63">
-        <v>1417501.894909705</v>
+        <v>333</v>
+      </c>
+      <c r="C13" s="65">
+        <v>103100</v>
+      </c>
+      <c r="D13" s="65">
+        <v>279624.915</v>
+      </c>
+      <c r="E13" s="65">
+        <v>567865.4974499999</v>
+      </c>
+      <c r="F13" s="65">
+        <v>946879.3680735</v>
+      </c>
+      <c r="G13" s="65">
+        <v>1393582.790029705</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="C14" s="64">
-        <v>0.4379626865671642</v>
-      </c>
-      <c r="D14" s="64">
-        <v>0.5994563735514655</v>
-      </c>
-      <c r="E14" s="64">
-        <v>0.6924323308270677</v>
-      </c>
-      <c r="F14" s="64">
-        <v>0.7352164366373902</v>
-      </c>
-      <c r="G14" s="64">
-        <v>0.7566487758945385</v>
+        <v>368</v>
+      </c>
+      <c r="C14" s="66">
+        <v>0.41557462686567165</v>
+      </c>
+      <c r="D14" s="66">
+        <v>0.5843841328168967</v>
+      </c>
+      <c r="E14" s="66">
+        <v>0.6815266375084321</v>
+      </c>
+      <c r="F14" s="66">
+        <v>0.7262549346685067</v>
+      </c>
+      <c r="G14" s="66">
+        <v>0.7486970244652047</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="C15" s="65">
+        <v>238</v>
+      </c>
+      <c r="C15" s="67">
         <v>11166.666666666666</v>
       </c>
-      <c r="D15" s="65">
-        <v>13736.454545454546</v>
-      </c>
-      <c r="E15" s="65">
-        <v>14109.97</v>
-      </c>
-      <c r="F15" s="65">
-        <v>14515.056983333334</v>
-      </c>
-      <c r="G15" s="65">
-        <v>14941.129452750003</v>
-      </c>
-      <c r="H15" s="66" t="s">
-        <v>353</v>
+      <c r="D15" s="67">
+        <v>13730.454545454546</v>
+      </c>
+      <c r="E15" s="67">
+        <v>14097.79</v>
+      </c>
+      <c r="F15" s="67">
+        <v>14496.511583333333</v>
+      </c>
+      <c r="G15" s="67">
+        <v>14916.027690750003</v>
+      </c>
+      <c r="H15" s="68" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="C16" s="67">
-        <v>6276.083333333333</v>
-      </c>
-      <c r="D16" s="67">
-        <v>5502.049318181818</v>
-      </c>
-      <c r="E16" s="67">
-        <v>4339.770585</v>
-      </c>
-      <c r="F16" s="67">
-        <v>3843.348510458333</v>
-      </c>
-      <c r="G16" s="67">
-        <v>3635.9421418448756</v>
+        <v>272</v>
+      </c>
+      <c r="C16" s="69">
+        <v>6526.083333333333</v>
+      </c>
+      <c r="D16" s="69">
+        <v>5706.594772727273</v>
+      </c>
+      <c r="E16" s="69">
+        <v>4489.770585</v>
+      </c>
+      <c r="F16" s="69">
+        <v>3968.348510458333</v>
+      </c>
+      <c r="G16" s="69">
+        <v>3748.4421418448756</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="C17" s="62">
+        <v>384</v>
+      </c>
+      <c r="C17" s="64">
         <v>400</v>
       </c>
-      <c r="D17" s="62">
+      <c r="D17" s="64">
         <v>412</v>
       </c>
-      <c r="E17" s="62">
+      <c r="E17" s="64">
         <v>424.35999999999996</v>
       </c>
-      <c r="F17" s="62">
+      <c r="F17" s="64">
         <v>437.0908</v>
       </c>
-      <c r="G17" s="62">
+      <c r="G17" s="64">
         <v>450.20352400000013</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="C18" s="65">
+        <v>385</v>
+      </c>
+      <c r="C18" s="67">
         <v>1720</v>
       </c>
-      <c r="D18" s="65">
+      <c r="D18" s="67">
         <v>1207.909090909091</v>
       </c>
-      <c r="E18" s="65">
+      <c r="E18" s="67">
         <v>912.3739999999999</v>
       </c>
-      <c r="F18" s="65">
+      <c r="F18" s="67">
         <v>783.1210166666666</v>
       </c>
-      <c r="G18" s="65">
+      <c r="G18" s="67">
         <v>725.9531824500001</v>
       </c>
-      <c r="H18" s="66" t="s">
-        <v>356</v>
+      <c r="H18" s="68" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="C19" s="68">
-        <v>4890.583333333333</v>
-      </c>
-      <c r="D19" s="68">
-        <v>8234.405227272726</v>
-      </c>
-      <c r="E19" s="68">
-        <v>9770.199415000001</v>
-      </c>
-      <c r="F19" s="68">
-        <v>10671.708472875</v>
-      </c>
-      <c r="G19" s="68">
-        <v>11305.187310905127</v>
+        <v>387</v>
+      </c>
+      <c r="C19" s="70">
+        <v>4640.583333333333</v>
+      </c>
+      <c r="D19" s="70">
+        <v>8023.859772727272</v>
+      </c>
+      <c r="E19" s="70">
+        <v>9608.019414999999</v>
+      </c>
+      <c r="F19" s="70">
+        <v>10528.163072875</v>
+      </c>
+      <c r="G19" s="70">
+        <v>11167.585548905126</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="C20" s="64">
+        <v>388</v>
+      </c>
+      <c r="C20" s="66">
         <v>0.3851716417910448</v>
       </c>
-      <c r="D20" s="64">
-        <v>0.26387014314928425</v>
-      </c>
-      <c r="E20" s="64">
-        <v>0.19403383458646614</v>
-      </c>
-      <c r="F20" s="64">
-        <v>0.1618977415307403</v>
-      </c>
-      <c r="G20" s="64">
-        <v>0.14579943502824858</v>
-      </c>
-      <c r="H20" s="66" t="s">
-        <v>359</v>
+      <c r="D20" s="66">
+        <v>0.2639854503922932</v>
+      </c>
+      <c r="E20" s="66">
+        <v>0.1942014730677645</v>
+      </c>
+      <c r="F20" s="66">
+        <v>0.16210485745366593</v>
+      </c>
+      <c r="G20" s="66">
+        <v>0.14604479678230883</v>
+      </c>
+      <c r="H20" s="68" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="C21" s="69">
+        <v>390</v>
+      </c>
+      <c r="C21" s="71">
         <v>0.15402985074626865</v>
       </c>
-      <c r="D21" s="64">
-        <v>0.08793456032719836</v>
-      </c>
-      <c r="E21" s="64">
-        <v>0.06466165413533834</v>
-      </c>
-      <c r="F21" s="64">
-        <v>0.053952321204516936</v>
-      </c>
-      <c r="G21" s="64">
-        <v>0.04858757062146892</v>
-      </c>
-      <c r="H21" s="66" t="s">
-        <v>361</v>
+      <c r="D21" s="66">
+        <v>0.08797298639388221</v>
+      </c>
+      <c r="E21" s="66">
+        <v>0.06471751955448335</v>
+      </c>
+      <c r="F21" s="66">
+        <v>0.05402134245641706</v>
+      </c>
+      <c r="G21" s="66">
+        <v>0.048669337272697025</v>
+      </c>
+      <c r="H21" s="68" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="C22" s="64">
-        <v>0.4379626865671642</v>
-      </c>
-      <c r="D22" s="64">
-        <v>0.5994563735514655</v>
-      </c>
-      <c r="E22" s="64">
-        <v>0.6924323308270676</v>
-      </c>
-      <c r="F22" s="64">
-        <v>0.7352164366373901</v>
-      </c>
-      <c r="G22" s="64">
-        <v>0.7566487758945386</v>
-      </c>
-      <c r="H22" s="66" t="s">
-        <v>363</v>
+        <v>392</v>
+      </c>
+      <c r="C22" s="66">
+        <v>0.41557462686567165</v>
+      </c>
+      <c r="D22" s="66">
+        <v>0.5843841328168967</v>
+      </c>
+      <c r="E22" s="66">
+        <v>0.6815266375084321</v>
+      </c>
+      <c r="F22" s="66">
+        <v>0.7262549346685065</v>
+      </c>
+      <c r="G22" s="66">
+        <v>0.7486970244652048</v>
+      </c>
+      <c r="H22" s="68" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="C23" s="70">
+        <v>394</v>
+      </c>
+      <c r="C23" s="72">
         <v>3</v>
       </c>
-      <c r="D23" s="70">
+      <c r="D23" s="72">
         <v>3</v>
       </c>
-      <c r="E23" s="70">
+      <c r="E23" s="72">
         <v>3</v>
       </c>
-      <c r="F23" s="70">
+      <c r="F23" s="72">
         <v>3</v>
       </c>
-      <c r="G23" s="70">
+      <c r="G23" s="72">
         <v>3</v>
       </c>
-      <c r="H23" s="66" t="s">
-        <v>365</v>
+      <c r="H23" s="68" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="C24" s="71" t="s">
-        <v>302</v>
-      </c>
-      <c r="D24" s="71" t="s">
-        <v>302</v>
-      </c>
-      <c r="E24" s="71" t="s">
-        <v>302</v>
-      </c>
-      <c r="F24" s="71" t="s">
-        <v>302</v>
-      </c>
-      <c r="G24" s="71" t="s">
-        <v>302</v>
-      </c>
-      <c r="H24" s="66" t="s">
-        <v>302</v>
+        <v>330</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>331</v>
+      </c>
+      <c r="D24" s="73" t="s">
+        <v>331</v>
+      </c>
+      <c r="E24" s="73" t="s">
+        <v>331</v>
+      </c>
+      <c r="F24" s="73" t="s">
+        <v>331</v>
+      </c>
+      <c r="G24" s="73" t="s">
+        <v>331</v>
+      </c>
+      <c r="H24" s="68" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="C25" s="40" t="str">
-        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>396</v>
+      </c>
+      <c r="C25" s="42" t="str">
+        <f>IF('5-Year Operating Stmt'!B17&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
+      <c r="D25" s="74" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!C17&gt;=0,'5-Year Operating Stmt'!B17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
+      <c r="E25" s="74" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!D17&gt;=0,'5-Year Operating Stmt'!C17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
+      <c r="F25" s="74" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!E17&gt;=0,'5-Year Operating Stmt'!D17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="72" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
+      <c r="G25" s="74" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!F17&gt;=0,'5-Year Operating Stmt'!E17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="66" t="s">
-        <v>347</v>
+      <c r="H25" s="68" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="C26" s="73">
-        <v>14</v>
-      </c>
-      <c r="D26" s="70">
-        <v>29</v>
-      </c>
-      <c r="E26" s="70">
-        <v>54</v>
-      </c>
-      <c r="F26" s="74" t="s">
-        <v>368</v>
-      </c>
-      <c r="G26" s="74" t="s">
-        <v>368</v>
-      </c>
-      <c r="H26" s="66" t="s">
-        <v>369</v>
+        <v>397</v>
+      </c>
+      <c r="C26" s="75">
+        <v>13</v>
+      </c>
+      <c r="D26" s="72">
+        <v>27</v>
+      </c>
+      <c r="E26" s="72">
+        <v>51</v>
+      </c>
+      <c r="F26" s="76" t="s">
+        <v>398</v>
+      </c>
+      <c r="G26" s="76" t="s">
+        <v>398</v>
+      </c>
+      <c r="H26" s="68" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="C27" s="70">
-        <v>414</v>
-      </c>
-      <c r="D27" s="70">
-        <v>868</v>
-      </c>
-      <c r="E27" s="70">
-        <v>1629</v>
-      </c>
-      <c r="F27" s="70">
-        <v>2546</v>
-      </c>
-      <c r="G27" s="70">
-        <v>3557</v>
-      </c>
-      <c r="H27" s="66" t="s">
-        <v>370</v>
+        <v>334</v>
+      </c>
+      <c r="C27" s="72">
+        <v>384</v>
+      </c>
+      <c r="D27" s="72">
+        <v>813</v>
+      </c>
+      <c r="E27" s="72">
+        <v>1539</v>
+      </c>
+      <c r="F27" s="72">
+        <v>2419</v>
+      </c>
+      <c r="G27" s="72">
+        <v>3392</v>
+      </c>
+      <c r="H27" s="68" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="42" t="s">
-        <v>375</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>377</v>
-      </c>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76" t="s">
-        <v>378</v>
-      </c>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
+      <c r="B30" s="44" t="s">
+        <v>405</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="D30" s="77" t="s">
+        <v>407</v>
+      </c>
+      <c r="E30" s="77"/>
+      <c r="F30" s="78" t="s">
+        <v>408</v>
+      </c>
+      <c r="G30" s="78"/>
+      <c r="H30" s="78"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="42" t="s">
-        <v>379</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D31" s="75" t="s">
-        <v>380</v>
-      </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76" t="s">
-        <v>381</v>
-      </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
+      <c r="B31" s="44" t="s">
+        <v>409</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="D31" s="77" t="s">
+        <v>410</v>
+      </c>
+      <c r="E31" s="77"/>
+      <c r="F31" s="78" t="s">
+        <v>411</v>
+      </c>
+      <c r="G31" s="78"/>
+      <c r="H31" s="78"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="42" t="s">
-        <v>382</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D32" s="75" t="s">
-        <v>383</v>
-      </c>
-      <c r="E32" s="75"/>
-      <c r="F32" s="76" t="s">
-        <v>384</v>
-      </c>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
+      <c r="B32" s="44" t="s">
+        <v>412</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="D32" s="77" t="s">
+        <v>413</v>
+      </c>
+      <c r="E32" s="77"/>
+      <c r="F32" s="78" t="s">
+        <v>414</v>
+      </c>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="42" t="s">
-        <v>385</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D33" s="75" t="s">
-        <v>386</v>
-      </c>
-      <c r="E33" s="75"/>
-      <c r="F33" s="76" t="s">
-        <v>387</v>
-      </c>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
+      <c r="B33" s="44" t="s">
+        <v>415</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="D33" s="77" t="s">
+        <v>416</v>
+      </c>
+      <c r="E33" s="77"/>
+      <c r="F33" s="78" t="s">
+        <v>417</v>
+      </c>
+      <c r="G33" s="78"/>
+      <c r="H33" s="78"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="42" t="s">
-        <v>388</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D34" s="75" t="s">
-        <v>389</v>
-      </c>
-      <c r="E34" s="75"/>
-      <c r="F34" s="76" t="s">
-        <v>390</v>
-      </c>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
+      <c r="B34" s="44" t="s">
+        <v>418</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="D34" s="77" t="s">
+        <v>419</v>
+      </c>
+      <c r="E34" s="77"/>
+      <c r="F34" s="78" t="s">
+        <v>420</v>
+      </c>
+      <c r="G34" s="78"/>
+      <c r="H34" s="78"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="42" t="s">
-        <v>391</v>
-      </c>
-      <c r="C35" s="40" t="s">
-        <v>376</v>
-      </c>
-      <c r="D35" s="75" t="s">
-        <v>392</v>
-      </c>
-      <c r="E35" s="75"/>
-      <c r="F35" s="76" t="s">
-        <v>393</v>
-      </c>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
+      <c r="B35" s="44" t="s">
+        <v>421</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="D35" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="E35" s="77"/>
+      <c r="F35" s="78" t="s">
+        <v>423</v>
+      </c>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="42" t="s">
-        <v>394</v>
+      <c r="B37" s="44" t="s">
+        <v>424</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="77" t="s">
-        <v>396</v>
-      </c>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
+      <c r="B39" s="79" t="s">
+        <v>426</v>
+      </c>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="79"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -7002,12 +7305,225 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="21"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>427</v>
+      </c>
+      <c r="B3" s="19"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B4" s="80"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" s="19"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B7" s="80"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="B9" s="19"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B10" s="80"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="B12" s="19"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B13" s="80"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="B15" s="19"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B16" s="80"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="B18" s="19"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B19" s="80"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="B21" s="19"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B22" s="80"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="B24" s="19"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B25" s="80"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="B27" s="19"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B28" s="80"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A28:B28"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="81" t="s">
+        <v>438</v>
+      </c>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="82" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -7017,7 +7533,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7031,18 +7547,18 @@
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -7085,10 +7601,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7109,7 +7625,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B12" s="20">
         <v>7</v>
@@ -7117,7 +7633,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="20">
         <v>40</v>
@@ -7125,7 +7641,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -7139,24 +7655,24 @@
         <v>7</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B17" s="22">
         <v>15</v>
@@ -7176,7 +7692,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7185,32 +7701,35 @@
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
     </row>
-    <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D21" s="23">
         <v>6000</v>
@@ -7218,16 +7737,19 @@
       <c r="E21" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D22" s="23">
         <v>200</v>
@@ -7235,16 +7757,19 @@
       <c r="E22" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>116</v>
       </c>
       <c r="D23" s="23">
         <v>7000</v>
@@ -7252,16 +7777,19 @@
       <c r="E23" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D24" s="23">
         <v>3000</v>
@@ -7269,10 +7797,13 @@
       <c r="E24" s="24">
         <v>0</v>
       </c>
+      <c r="F24" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -7283,36 +7814,36 @@
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D28" s="25">
         <v>1</v>
@@ -7329,13 +7860,13 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D29" s="25">
         <v>0.5</v>
@@ -7352,7 +7883,7 @@
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B31" s="19"/>
       <c r="C31" s="19"/>
@@ -7363,30 +7894,30 @@
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D33" s="23">
         <v>1800</v>
@@ -7397,13 +7928,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D34" s="23">
         <v>200</v>
@@ -7414,13 +7945,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D35" s="23">
         <v>1800</v>
@@ -7431,16 +7962,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D36" s="23">
-        <v>400</v>
+        <v>4500</v>
       </c>
       <c r="E36" s="24">
         <v>0</v>
@@ -7448,194 +7979,302 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D37" s="23">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E37" s="24">
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-    </row>
-    <row r="40" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B43" s="24">
-        <v>0.03</v>
-      </c>
-      <c r="C43" s="26" t="s">
+      <c r="B38" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="23">
+        <v>250</v>
+      </c>
+      <c r="E38" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
         <v>151</v>
       </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+    </row>
+    <row r="41" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B44" s="24">
         <v>0.03</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B45" s="25">
-        <v>0.8333333333333334</v>
+        <v>158</v>
+      </c>
+      <c r="B45" s="24">
+        <v>0.03</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="B46" s="23">
-        <v>0</v>
+        <v>160</v>
+      </c>
+      <c r="B46" s="25">
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="49" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-    </row>
-    <row r="50" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B49" s="24">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B50" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B52" s="24">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B53" s="24">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B54" s="24">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19"/>
+    </row>
+    <row r="63" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B63" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="E50" s="21" t="s">
+      <c r="C63" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F50" s="21" t="s">
+      <c r="D63" s="21" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B51" s="22">
+      <c r="E63" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="B64" s="22">
         <v>3</v>
       </c>
-      <c r="C51" s="22">
+      <c r="C64" s="22">
         <v>4</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D64" s="22">
         <v>5</v>
       </c>
-      <c r="E51" s="22">
+      <c r="E64" s="22">
         <v>6</v>
       </c>
-      <c r="F51" s="22">
+      <c r="F64" s="22">
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B52" s="22">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B65" s="22">
         <v>2</v>
       </c>
-      <c r="C52" s="22">
+      <c r="C65" s="22">
         <v>3</v>
       </c>
-      <c r="D52" s="22">
+      <c r="D65" s="22">
         <v>4</v>
       </c>
-      <c r="E52" s="22">
+      <c r="E65" s="22">
         <v>5</v>
       </c>
-      <c r="F52" s="22">
+      <c r="F65" s="22">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B53" s="22">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B66" s="22">
         <v>5</v>
       </c>
-      <c r="C53" s="22">
+      <c r="C66" s="22">
         <v>7</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D66" s="22">
         <v>9</v>
       </c>
-      <c r="E53" s="22">
+      <c r="E66" s="22">
         <v>10</v>
       </c>
-      <c r="F53" s="22">
+      <c r="F66" s="22">
         <v>12</v>
       </c>
     </row>
@@ -7671,10 +8310,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7695,10 +8334,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7711,7 +8350,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -7719,66 +8358,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -7821,24 +8460,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -7848,7 +8487,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B6" s="27">
         <v>15</v>
@@ -7868,7 +8507,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="22">
         <v>40</v>
@@ -7876,7 +8515,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="B8" s="28">
         <f>B6/$B$7</f>
@@ -7901,10 +8540,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C10" s="29">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
@@ -7925,7 +8564,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -7935,82 +8574,82 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B14" s="30">
-        <f>Assumptions!B51</f>
+        <f>Assumptions!B64</f>
         <v>3</v>
       </c>
       <c r="C14" s="30">
-        <f>Assumptions!C51</f>
+        <f>Assumptions!C64</f>
         <v>4</v>
       </c>
       <c r="D14" s="30">
-        <f>Assumptions!D51</f>
+        <f>Assumptions!D64</f>
         <v>5</v>
       </c>
       <c r="E14" s="30">
-        <f>Assumptions!E51</f>
+        <f>Assumptions!E64</f>
         <v>6</v>
       </c>
       <c r="F14" s="30">
-        <f>Assumptions!F51</f>
+        <f>Assumptions!F64</f>
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="B15" s="30">
-        <f>Assumptions!B52</f>
+        <f>Assumptions!B65</f>
         <v>2</v>
       </c>
       <c r="C15" s="30">
-        <f>Assumptions!C52</f>
+        <f>Assumptions!C65</f>
         <v>3</v>
       </c>
       <c r="D15" s="30">
-        <f>Assumptions!D52</f>
+        <f>Assumptions!D65</f>
         <v>4</v>
       </c>
       <c r="E15" s="30">
-        <f>Assumptions!E52</f>
+        <f>Assumptions!E65</f>
         <v>5</v>
       </c>
       <c r="F15" s="30">
-        <f>Assumptions!F52</f>
+        <f>Assumptions!F65</f>
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B16" s="30">
-        <f>Assumptions!B53</f>
+        <f>Assumptions!B66</f>
         <v>5</v>
       </c>
       <c r="C16" s="30">
-        <f>Assumptions!C53</f>
+        <f>Assumptions!C66</f>
         <v>7</v>
       </c>
       <c r="D16" s="30">
-        <f>Assumptions!D53</f>
+        <f>Assumptions!D66</f>
         <v>9</v>
       </c>
       <c r="E16" s="30">
-        <f>Assumptions!E53</f>
+        <f>Assumptions!E66</f>
         <v>10</v>
       </c>
       <c r="F16" s="30">
-        <f>Assumptions!F53</f>
+        <f>Assumptions!F66</f>
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="B17" s="27">
         <f>B14+B15+B16</f>
@@ -8035,7 +8674,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="B18" s="28">
         <f>IF(B6=0,0,B17/B6)</f>
@@ -8084,7 +8723,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8097,24 +8736,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -8124,7 +8763,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B5" s="31">
         <v>90000</v>
@@ -8144,27 +8783,27 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B6" s="31">
         <v>3000</v>
       </c>
       <c r="C6" s="31">
-        <v>4532</v>
+        <v>4400</v>
       </c>
       <c r="D6" s="31">
-        <v>6365</v>
+        <v>6000</v>
       </c>
       <c r="E6" s="31">
-        <v>7868</v>
+        <v>7200</v>
       </c>
       <c r="F6" s="31">
-        <v>9004</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="B7" s="32">
         <f>SUM(B5,B6)</f>
@@ -8172,24 +8811,24 @@
       </c>
       <c r="C7" s="32">
         <f>SUM(C5,C6)</f>
-        <v>140492</v>
+        <v>140360</v>
       </c>
       <c r="D7" s="32">
         <f>SUM(D5,D6)</f>
-        <v>197327</v>
+        <v>196962</v>
       </c>
       <c r="E7" s="32">
         <f>SUM(E5,E6)</f>
-        <v>243897</v>
+        <v>243229</v>
       </c>
       <c r="F7" s="32">
         <f>SUM(F5,F6)</f>
-        <v>279126</v>
+        <v>278122</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -8199,7 +8838,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B9" s="31">
         <v>105000</v>
@@ -8219,7 +8858,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="B10" s="32">
         <f>SUM(B9)</f>
@@ -8244,7 +8883,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -8254,7 +8893,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B12" s="23">
         <v>3000</v>
@@ -8274,7 +8913,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B13" s="32">
         <f>SUM(B12)</f>
@@ -8299,7 +8938,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="B15" s="33">
         <f>SUM(B7,B10,B13)</f>
@@ -8307,19 +8946,19 @@
       </c>
       <c r="C15" s="33">
         <f>SUM(C7,C10,C13)</f>
-        <v>302202</v>
+        <v>302070</v>
       </c>
       <c r="D15" s="33">
         <f>SUM(D7,D10,D13)</f>
-        <v>423299</v>
+        <v>422934</v>
       </c>
       <c r="E15" s="33">
         <f>SUM(E7,E10,E13)</f>
-        <v>522542</v>
+        <v>521874</v>
       </c>
       <c r="F15" s="33">
         <f>SUM(F7,F10,F13)</f>
-        <v>597645</v>
+        <v>596641</v>
       </c>
     </row>
   </sheetData>
@@ -8339,7 +8978,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -8348,9 +8987,10 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>61</v>
       </c>
@@ -8360,36 +9000,40 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C4" s="25">
         <v>1</v>
@@ -8406,13 +9050,16 @@
       <c r="G4" s="34">
         <v>61272</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C5" s="25">
         <v>0.5</v>
@@ -8429,10 +9076,13 @@
       <c r="G5" s="34">
         <v>16148</v>
       </c>
+      <c r="H5" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -8446,24 +9096,24 @@
         <v>7</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="B9" s="33">
         <v>64516</v>
@@ -8483,27 +9133,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="B10" s="29">
         <v>0.320976368159204</v>
       </c>
       <c r="C10" s="29">
-        <v>0.26387014314928425</v>
+        <v>0.2639854503922932</v>
       </c>
       <c r="D10" s="29">
-        <v>0.19403383458646614</v>
+        <v>0.1942014730677645</v>
       </c>
       <c r="E10" s="29">
-        <v>0.1618977415307403</v>
+        <v>0.16210485745366593</v>
       </c>
       <c r="F10" s="29">
-        <v>0.14579943502824858</v>
+        <v>0.14604479678230883</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B11" s="35">
         <v>10</v>
@@ -8523,7 +9173,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -8538,7 +9188,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -8547,7 +9197,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8560,24 +9210,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -8587,7 +9237,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B5" s="31">
         <v>6000</v>
@@ -8607,7 +9257,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="B6" s="32">
         <f>SUM(B5:B5)</f>
@@ -8632,7 +9282,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -8642,7 +9292,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="B8" s="31">
         <v>3750</v>
@@ -8662,7 +9312,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B8:B8)</f>
@@ -8687,7 +9337,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -8697,7 +9347,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="B11" s="31">
         <v>21600</v>
@@ -8717,7 +9367,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="B12" s="31">
         <v>2400</v>
@@ -8737,7 +9387,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="B13" s="31">
         <v>1800</v>
@@ -8757,7 +9407,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="B14" s="32">
         <f>SUM(B11:B13)</f>
@@ -8780,29 +9430,84 @@
         <v>29038</v>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="B16" s="33">
-        <f>B6+B9+B14</f>
-        <v>35550</v>
-      </c>
-      <c r="C16" s="33">
-        <f>C6+C9+C14</f>
-        <v>41303</v>
-      </c>
-      <c r="D16" s="33">
-        <f>D6+D9+D14</f>
-        <v>48059</v>
-      </c>
-      <c r="E16" s="33">
-        <f>E6+E9+E14</f>
-        <v>53762</v>
-      </c>
-      <c r="F16" s="33">
-        <f>F6+F9+F14</f>
-        <v>58301</v>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B16" s="31">
+        <v>4500</v>
+      </c>
+      <c r="C16" s="31">
+        <v>4500</v>
+      </c>
+      <c r="D16" s="31">
+        <v>4500</v>
+      </c>
+      <c r="E16" s="31">
+        <v>4500</v>
+      </c>
+      <c r="F16" s="31">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="B17" s="32">
+        <f>SUM(B16:B16)</f>
+        <v>4500</v>
+      </c>
+      <c r="C17" s="32">
+        <f>SUM(C16:C16)</f>
+        <v>4500</v>
+      </c>
+      <c r="D17" s="32">
+        <f>SUM(D16:D16)</f>
+        <v>4500</v>
+      </c>
+      <c r="E17" s="32">
+        <f>SUM(E16:E16)</f>
+        <v>4500</v>
+      </c>
+      <c r="F17" s="32">
+        <f>SUM(F16:F16)</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" s="33">
+        <f>B6+B9+B14+B17</f>
+        <v>40050</v>
+      </c>
+      <c r="C19" s="33">
+        <f>C6+C9+C14+C17</f>
+        <v>45803</v>
+      </c>
+      <c r="D19" s="33">
+        <f>D6+D9+D14+D17</f>
+        <v>52559</v>
+      </c>
+      <c r="E19" s="33">
+        <f>E6+E9+E14+E17</f>
+        <v>58262</v>
+      </c>
+      <c r="F19" s="33">
+        <f>F6+F9+F14+F17</f>
+        <v>62801</v>
       </c>
     </row>
   </sheetData>
@@ -8832,7 +9537,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8842,27 +9547,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="F5" s="33">
         <v>0</v>
@@ -8870,7 +9575,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="F6" s="32">
         <v>0</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -27,14 +27,15 @@
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
-    <sheet sheetId="24" name="Decision History" state="visible" r:id="rId27"/>
+    <sheet sheetId="24" name="Assumptions Memo" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="Decision History" state="visible" r:id="rId28"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="443">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -42,7 +43,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · llc_single</t>
+    <t>Generated May 1, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -162,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1152,7 +1153,7 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1345,6 +1346,15 @@
   </si>
   <si>
     <t>Additional Context</t>
+  </si>
+  <si>
+    <t>Assumptions Memo</t>
+  </si>
+  <si>
+    <t>Founder-supplied reasoning for each assumption captured during the wizard. Empty when no rationale was entered for that area.</t>
+  </si>
+  <si>
+    <t>No founder rationale captured.</t>
   </si>
   <si>
     <t>Decision History</t>
@@ -1367,7 +1377,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1520,6 +1530,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1610,7 +1625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1748,6 +1763,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -7455,6 +7474,54 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>437</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="81" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
+        <v>439</v>
+      </c>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7473,7 +7540,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="15" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -7483,26 +7550,26 @@
       <c r="H1" s="15"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="81" t="s">
-        <v>438</v>
-      </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
+      <c r="B2" s="83" t="s">
+        <v>441</v>
+      </c>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="82" t="s">
-        <v>439</v>
-      </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
+      <c r="B4" s="84" t="s">
+        <v>442</v>
+      </c>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -43,7 +43,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · llc_single</t>
+    <t>Generated May 7, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -163,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -589,7 +589,7 @@
     <t>School Model</t>
   </si>
   <si>
-    <t>microschool</t>
+    <t>homeschool co-op</t>
   </si>
   <si>
     <t>Financial Label Convention</t>
@@ -1153,7 +1153,7 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1261,7 +1261,7 @@
     <t>The model reaches profit early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -1303,7 +1303,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>111.5 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>112.0 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -2995,19 +2995,19 @@
       </c>
       <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
-        <v>302070</v>
+        <v>302980</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
-        <v>422934</v>
+        <v>424730</v>
       </c>
       <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
-        <v>521874</v>
+        <v>523580</v>
       </c>
       <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
-        <v>596641</v>
+        <v>598240</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3384,19 +3384,19 @@
       </c>
       <c r="C4" s="34">
         <f>'Budget Detail'!C9</f>
-        <v>302070</v>
+        <v>302980</v>
       </c>
       <c r="D4" s="34">
         <f>'Budget Detail'!D9</f>
-        <v>422934</v>
+        <v>424730</v>
       </c>
       <c r="E4" s="34">
         <f>'Budget Detail'!E9</f>
-        <v>521874</v>
+        <v>523580</v>
       </c>
       <c r="F4" s="34">
         <f>'Budget Detail'!F9</f>
-        <v>596641</v>
+        <v>598240</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3519,19 +3519,19 @@
       </c>
       <c r="C11" s="33">
         <f>C4-C8</f>
-        <v>176525</v>
+        <v>177435</v>
       </c>
       <c r="D11" s="33">
         <f>D4-D8</f>
-        <v>288241</v>
+        <v>290037</v>
       </c>
       <c r="E11" s="33">
         <f>E4-E8</f>
-        <v>379014</v>
+        <v>380719</v>
       </c>
       <c r="F11" s="33">
         <f>F4-F8</f>
-        <v>446703</v>
+        <v>448302</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3544,19 +3544,19 @@
       </c>
       <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
-        <v>0.58438413</v>
+        <v>0.58563243</v>
       </c>
       <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
-        <v>0.68152664</v>
+        <v>0.68287355</v>
       </c>
       <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
-        <v>0.72625493</v>
+        <v>0.72714667</v>
       </c>
       <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
-        <v>0.74869702</v>
+        <v>0.74936867</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3567,16 +3567,16 @@
         <v>69609</v>
       </c>
       <c r="C13" s="31">
-        <v>246134</v>
+        <v>247044</v>
       </c>
       <c r="D13" s="31">
-        <v>534374</v>
+        <v>537081</v>
       </c>
       <c r="E13" s="31">
-        <v>913388</v>
+        <v>917800</v>
       </c>
       <c r="F13" s="31">
-        <v>1360092</v>
+        <v>1366102</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3587,16 +3587,16 @@
         <v>11167</v>
       </c>
       <c r="C14" s="31">
-        <v>13730</v>
+        <v>13772</v>
       </c>
       <c r="D14" s="31">
-        <v>14098</v>
+        <v>14158</v>
       </c>
       <c r="E14" s="31">
-        <v>14497</v>
+        <v>14544</v>
       </c>
       <c r="F14" s="31">
-        <v>14916</v>
+        <v>14956</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4250,16 +4250,16 @@
         <v>167500</v>
       </c>
       <c r="C5" s="32">
-        <v>302070</v>
+        <v>302980</v>
       </c>
       <c r="D5" s="32">
-        <v>422934</v>
+        <v>424730</v>
       </c>
       <c r="E5" s="32">
-        <v>521874</v>
+        <v>523580</v>
       </c>
       <c r="F5" s="32">
-        <v>596641</v>
+        <v>598240</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4397,19 +4397,19 @@
       </c>
       <c r="C15" s="33">
         <f>C5-C12</f>
-        <v>176239</v>
+        <v>177149</v>
       </c>
       <c r="D15" s="33">
         <f>D5-D12</f>
-        <v>287955</v>
+        <v>289751</v>
       </c>
       <c r="E15" s="33">
         <f>E5-E12</f>
-        <v>378728</v>
+        <v>380434</v>
       </c>
       <c r="F15" s="33">
         <f>F5-F12</f>
-        <v>446418</v>
+        <v>448017</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4422,19 +4422,19 @@
       </c>
       <c r="C16" s="29">
         <f>IF(C5=0,0,C15/C5)</f>
-        <v>0.58343828</v>
+        <v>0.58468942</v>
       </c>
       <c r="D16" s="29">
         <f>IF(D5=0,0,D15/D5)</f>
-        <v>0.68085108</v>
+        <v>0.68220085</v>
       </c>
       <c r="E16" s="29">
         <f>IF(E5=0,0,E15/E5)</f>
-        <v>0.72570746</v>
+        <v>0.72660098</v>
       </c>
       <c r="F16" s="29">
         <f>IF(F5=0,0,F15/F5)</f>
-        <v>0.74821815</v>
+        <v>0.74889108</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4447,19 +4447,19 @@
       </c>
       <c r="C17" s="34">
         <f>B17+C15</f>
-        <v>245562</v>
+        <v>246472</v>
       </c>
       <c r="D17" s="34">
         <f>C17+D15</f>
-        <v>533517</v>
+        <v>536223</v>
       </c>
       <c r="E17" s="34">
         <f>D17+E15</f>
-        <v>912245</v>
+        <v>916657</v>
       </c>
       <c r="F17" s="34">
         <f>E17+F15</f>
-        <v>1358663</v>
+        <v>1364674</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4638,19 +4638,19 @@
       </c>
       <c r="C5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15</f>
-        <v>279625</v>
+        <v>280535</v>
       </c>
       <c r="D5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
-        <v>567865</v>
+        <v>570572</v>
       </c>
       <c r="E5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
-        <v>946879</v>
+        <v>951291</v>
       </c>
       <c r="F5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
-        <v>1393583</v>
+        <v>1399594</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4723,19 +4723,19 @@
       </c>
       <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
-        <v>281578</v>
+        <v>282488</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
-        <v>569548</v>
+        <v>572254</v>
       </c>
       <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
-        <v>948292</v>
+        <v>952704</v>
       </c>
       <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
-        <v>1394726</v>
+        <v>1400736</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4833,19 +4833,19 @@
       </c>
       <c r="C17" s="33">
         <f>C9-C14</f>
-        <v>281578</v>
+        <v>282488</v>
       </c>
       <c r="D17" s="33">
         <f>D9-D14</f>
-        <v>569548</v>
+        <v>572254</v>
       </c>
       <c r="E17" s="33">
         <f>E9-E14</f>
-        <v>948292</v>
+        <v>952704</v>
       </c>
       <c r="F17" s="33">
         <f>F9-F14</f>
-        <v>1394726</v>
+        <v>1400736</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4945,16 +4945,16 @@
         <v>167500</v>
       </c>
       <c r="C5" s="31">
-        <v>302070</v>
+        <v>302980</v>
       </c>
       <c r="D5" s="31">
-        <v>422934</v>
+        <v>424730</v>
       </c>
       <c r="E5" s="31">
-        <v>521874</v>
+        <v>523580</v>
       </c>
       <c r="F5" s="31">
-        <v>596641</v>
+        <v>598240</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5005,16 +5005,16 @@
         <v>69609</v>
       </c>
       <c r="C8" s="34">
-        <v>176525</v>
+        <v>177435</v>
       </c>
       <c r="D8" s="34">
-        <v>288241</v>
+        <v>290037</v>
       </c>
       <c r="E8" s="34">
-        <v>379014</v>
+        <v>380719</v>
       </c>
       <c r="F8" s="34">
-        <v>446703</v>
+        <v>448302</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5067,19 +5067,19 @@
       </c>
       <c r="C11" s="34">
         <f>C8+C9+C10</f>
-        <v>176811</v>
+        <v>177721</v>
       </c>
       <c r="D11" s="34">
         <f>D8+D9+D10</f>
-        <v>288526</v>
+        <v>290323</v>
       </c>
       <c r="E11" s="34">
         <f>E8+E9+E10</f>
-        <v>379300</v>
+        <v>381005</v>
       </c>
       <c r="F11" s="34">
         <f>F8+F9+F10</f>
-        <v>446989</v>
+        <v>448588</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5120,16 +5120,16 @@
         <v>103100</v>
       </c>
       <c r="C15" s="31">
-        <v>279625</v>
+        <v>280535</v>
       </c>
       <c r="D15" s="31">
-        <v>567865</v>
+        <v>570572</v>
       </c>
       <c r="E15" s="31">
-        <v>946879</v>
+        <v>951291</v>
       </c>
       <c r="F15" s="31">
-        <v>1393583</v>
+        <v>1399594</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5142,19 +5142,19 @@
       </c>
       <c r="C16" s="50">
         <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="D16" s="50">
         <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
-        <v>1539</v>
+        <v>1546</v>
       </c>
       <c r="E16" s="50">
         <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
-        <v>2419</v>
+        <v>2430</v>
       </c>
       <c r="F16" s="50">
         <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
-        <v>3392</v>
+        <v>3407</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5167,19 +5167,19 @@
       </c>
       <c r="C17" s="35">
         <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="D17" s="35">
         <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="E17" s="35">
         <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
-        <v>79.5</v>
+        <v>79.9</v>
       </c>
       <c r="F17" s="35">
         <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
-        <v>111.5</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5220,16 +5220,16 @@
         <v>11167</v>
       </c>
       <c r="C21" s="31">
-        <v>13730</v>
+        <v>13772</v>
       </c>
       <c r="D21" s="31">
-        <v>14098</v>
+        <v>14158</v>
       </c>
       <c r="E21" s="31">
-        <v>14497</v>
+        <v>14544</v>
       </c>
       <c r="F21" s="31">
-        <v>14916</v>
+        <v>14956</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -5910,16 +5910,16 @@
         <v>167500</v>
       </c>
       <c r="C6" s="31">
-        <v>302070</v>
+        <v>302980</v>
       </c>
       <c r="D6" s="31">
-        <v>422934</v>
+        <v>424730</v>
       </c>
       <c r="E6" s="31">
-        <v>521874</v>
+        <v>523580</v>
       </c>
       <c r="F6" s="31">
-        <v>596641</v>
+        <v>598240</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5950,16 +5950,16 @@
         <v>69609</v>
       </c>
       <c r="C8" s="33">
-        <v>176525</v>
+        <v>177435</v>
       </c>
       <c r="D8" s="33">
-        <v>288241</v>
+        <v>290037</v>
       </c>
       <c r="E8" s="33">
-        <v>379014</v>
+        <v>380719</v>
       </c>
       <c r="F8" s="33">
-        <v>446703</v>
+        <v>448302</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5970,16 +5970,16 @@
         <v>0.41557462686567165</v>
       </c>
       <c r="C9" s="29">
-        <v>0.5843841328168967</v>
+        <v>0.5856324344841243</v>
       </c>
       <c r="D9" s="29">
-        <v>0.6815266375084321</v>
+        <v>0.6828735489605162</v>
       </c>
       <c r="E9" s="29">
-        <v>0.7262549346685067</v>
+        <v>0.7271466702767485</v>
       </c>
       <c r="F9" s="29">
-        <v>0.7486970244652048</v>
+        <v>0.7493686719814874</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6065,16 +6065,16 @@
         <v>125625</v>
       </c>
       <c r="C16" s="31">
-        <v>226553</v>
+        <v>227235</v>
       </c>
       <c r="D16" s="31">
-        <v>317200</v>
+        <v>318548</v>
       </c>
       <c r="E16" s="31">
-        <v>391406</v>
+        <v>392685</v>
       </c>
       <c r="F16" s="31">
-        <v>447481</v>
+        <v>448680</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6105,16 +6105,16 @@
         <v>27734</v>
       </c>
       <c r="C18" s="33">
-        <v>101007</v>
+        <v>101690</v>
       </c>
       <c r="D18" s="33">
-        <v>182507</v>
+        <v>183854</v>
       </c>
       <c r="E18" s="33">
-        <v>248545</v>
+        <v>249824</v>
       </c>
       <c r="F18" s="33">
-        <v>297543</v>
+        <v>298742</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6125,16 +6125,16 @@
         <v>0.22076616915422886</v>
       </c>
       <c r="C19" s="29">
-        <v>0.44584551042252896</v>
+        <v>0.4475099126454991</v>
       </c>
       <c r="D19" s="29">
-        <v>0.5753688500112429</v>
+        <v>0.5771647319473548</v>
       </c>
       <c r="E19" s="29">
-        <v>0.635006579558009</v>
+        <v>0.636195560368998</v>
       </c>
       <c r="F19" s="29">
-        <v>0.6649293659536065</v>
+        <v>0.6658248959753165</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6315,16 +6315,16 @@
         <v>167500</v>
       </c>
       <c r="E13" s="31">
-        <v>302070</v>
+        <v>302980</v>
       </c>
       <c r="F13" s="31">
-        <v>422934</v>
+        <v>424730</v>
       </c>
       <c r="G13" s="31">
-        <v>521874</v>
+        <v>523580</v>
       </c>
       <c r="H13" s="31">
-        <v>596641</v>
+        <v>598240</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -6355,16 +6355,16 @@
         <v>69609</v>
       </c>
       <c r="E15" s="31">
-        <v>176525</v>
+        <v>177435</v>
       </c>
       <c r="F15" s="31">
-        <v>288241</v>
+        <v>290037</v>
       </c>
       <c r="G15" s="31">
-        <v>379014</v>
+        <v>380719</v>
       </c>
       <c r="H15" s="31">
-        <v>446703</v>
+        <v>448302</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -6375,16 +6375,16 @@
         <v>103100</v>
       </c>
       <c r="E16" s="31">
-        <v>279625</v>
+        <v>280535</v>
       </c>
       <c r="F16" s="31">
-        <v>567865</v>
+        <v>570572</v>
       </c>
       <c r="G16" s="31">
-        <v>946879</v>
+        <v>951291</v>
       </c>
       <c r="H16" s="31">
-        <v>1393583</v>
+        <v>1399594</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -6453,16 +6453,16 @@
         <v>0.41557462686567165</v>
       </c>
       <c r="E21" s="29">
-        <v>0.5843841328168967</v>
+        <v>0.5856324344841243</v>
       </c>
       <c r="F21" s="29">
-        <v>0.6815266375084321</v>
+        <v>0.6828735489605162</v>
       </c>
       <c r="G21" s="29">
-        <v>0.7262549346685067</v>
+        <v>0.7271466702767485</v>
       </c>
       <c r="H21" s="29">
-        <v>0.7486970244652047</v>
+        <v>0.7493686719814874</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -6556,7 +6556,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:I39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6566,7 +6566,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>371</v>
       </c>
@@ -6576,8 +6576,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
         <v>372</v>
       </c>
@@ -6587,6 +6588,7 @@
       <c r="F3" s="58"/>
       <c r="G3" s="58"/>
       <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="59" t="s">
@@ -6650,16 +6652,16 @@
         <v>167500</v>
       </c>
       <c r="D8" s="64">
-        <v>302070</v>
+        <v>302980</v>
       </c>
       <c r="E8" s="64">
-        <v>422933.7</v>
+        <v>424730</v>
       </c>
       <c r="F8" s="64">
-        <v>521874.417</v>
+        <v>523580</v>
       </c>
       <c r="G8" s="64">
-        <v>596641.1076300001</v>
+        <v>598240</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -6699,7 +6701,7 @@
         <v>58262.168399999995</v>
       </c>
       <c r="G10" s="64">
-        <v>62801.35635800001</v>
+        <v>62801.356358000005</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
@@ -6730,16 +6732,16 @@
         <v>69608.75</v>
       </c>
       <c r="D12" s="65">
-        <v>176524.91499999998</v>
+        <v>177434.91499999998</v>
       </c>
       <c r="E12" s="65">
-        <v>288240.58245</v>
+        <v>290036.88245000003</v>
       </c>
       <c r="F12" s="65">
-        <v>379013.8706235</v>
+        <v>380719.4536235</v>
       </c>
       <c r="G12" s="65">
-        <v>446703.42195620504</v>
+        <v>448302.314326205</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -6750,16 +6752,16 @@
         <v>103100</v>
       </c>
       <c r="D13" s="65">
-        <v>279624.915</v>
+        <v>280534.915</v>
       </c>
       <c r="E13" s="65">
-        <v>567865.4974499999</v>
+        <v>570571.79745</v>
       </c>
       <c r="F13" s="65">
-        <v>946879.3680735</v>
+        <v>951291.2510735</v>
       </c>
       <c r="G13" s="65">
-        <v>1393582.790029705</v>
+        <v>1399593.565399705</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -6770,16 +6772,16 @@
         <v>0.41557462686567165</v>
       </c>
       <c r="D14" s="66">
-        <v>0.5843841328168967</v>
+        <v>0.5856324344841243</v>
       </c>
       <c r="E14" s="66">
-        <v>0.6815266375084321</v>
+        <v>0.6828735489605162</v>
       </c>
       <c r="F14" s="66">
-        <v>0.7262549346685067</v>
+        <v>0.7271466702767485</v>
       </c>
       <c r="G14" s="66">
-        <v>0.7486970244652047</v>
+        <v>0.7493686719814874</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
@@ -6790,16 +6792,16 @@
         <v>11166.666666666666</v>
       </c>
       <c r="D15" s="67">
-        <v>13730.454545454546</v>
+        <v>13771.818181818182</v>
       </c>
       <c r="E15" s="67">
-        <v>14097.79</v>
+        <v>14157.666666666666</v>
       </c>
       <c r="F15" s="67">
-        <v>14496.511583333333</v>
+        <v>14543.888888888889</v>
       </c>
       <c r="G15" s="67">
-        <v>14916.027690750003</v>
+        <v>14956</v>
       </c>
       <c r="H15" s="68" t="s">
         <v>383</v>
@@ -6822,7 +6824,7 @@
         <v>3968.348510458333</v>
       </c>
       <c r="G16" s="69">
-        <v>3748.4421418448756</v>
+        <v>3748.442141844875</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -6876,16 +6878,16 @@
         <v>4640.583333333333</v>
       </c>
       <c r="D19" s="70">
-        <v>8023.859772727272</v>
+        <v>8065.223409090908</v>
       </c>
       <c r="E19" s="70">
-        <v>9608.019414999999</v>
+        <v>9667.896081666668</v>
       </c>
       <c r="F19" s="70">
-        <v>10528.163072875</v>
+        <v>10575.540378430556</v>
       </c>
       <c r="G19" s="70">
-        <v>11167.585548905126</v>
+        <v>11207.557858155125</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
@@ -6896,16 +6898,16 @@
         <v>0.3851716417910448</v>
       </c>
       <c r="D20" s="66">
-        <v>0.2639854503922932</v>
+        <v>0.2631925704666975</v>
       </c>
       <c r="E20" s="66">
-        <v>0.1942014730677645</v>
+        <v>0.19338014161938172</v>
       </c>
       <c r="F20" s="66">
-        <v>0.16210485745366593</v>
+        <v>0.16157679433228925</v>
       </c>
       <c r="G20" s="66">
-        <v>0.14604479678230883</v>
+        <v>0.14565446863431902</v>
       </c>
       <c r="H20" s="68" t="s">
         <v>389</v>
@@ -6919,16 +6921,16 @@
         <v>0.15402985074626865</v>
       </c>
       <c r="D21" s="66">
-        <v>0.08797298639388221</v>
+        <v>0.08770875965410257</v>
       </c>
       <c r="E21" s="66">
-        <v>0.06471751955448335</v>
+        <v>0.06444381136251265</v>
       </c>
       <c r="F21" s="66">
-        <v>0.05402134245641706</v>
+        <v>0.0538453657511746</v>
       </c>
       <c r="G21" s="66">
-        <v>0.048669337272697025</v>
+        <v>0.04853926066127307</v>
       </c>
       <c r="H21" s="68" t="s">
         <v>391</v>
@@ -6942,16 +6944,16 @@
         <v>0.41557462686567165</v>
       </c>
       <c r="D22" s="66">
-        <v>0.5843841328168967</v>
+        <v>0.5856324344841243</v>
       </c>
       <c r="E22" s="66">
-        <v>0.6815266375084321</v>
+        <v>0.682873548960516</v>
       </c>
       <c r="F22" s="66">
-        <v>0.7262549346685065</v>
+        <v>0.7271466702767484</v>
       </c>
       <c r="G22" s="66">
-        <v>0.7486970244652048</v>
+        <v>0.7493686719814874</v>
       </c>
       <c r="H22" s="68" t="s">
         <v>393</v>
@@ -7062,22 +7064,22 @@
         <v>384</v>
       </c>
       <c r="D27" s="72">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="E27" s="72">
-        <v>1539</v>
+        <v>1546</v>
       </c>
       <c r="F27" s="72">
-        <v>2419</v>
+        <v>2430</v>
       </c>
       <c r="G27" s="72">
-        <v>3392</v>
+        <v>3407</v>
       </c>
       <c r="H27" s="68" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
         <v>401</v>
       </c>
@@ -7093,8 +7095,9 @@
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="44" t="s">
         <v>405</v>
       </c>
@@ -7110,8 +7113,9 @@
       </c>
       <c r="G30" s="78"/>
       <c r="H30" s="78"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="78"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="44" t="s">
         <v>409</v>
       </c>
@@ -7127,8 +7131,9 @@
       </c>
       <c r="G31" s="78"/>
       <c r="H31" s="78"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="78"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="44" t="s">
         <v>412</v>
       </c>
@@ -7144,8 +7149,9 @@
       </c>
       <c r="G32" s="78"/>
       <c r="H32" s="78"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="78"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="44" t="s">
         <v>415</v>
       </c>
@@ -7161,8 +7167,9 @@
       </c>
       <c r="G33" s="78"/>
       <c r="H33" s="78"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="78"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="44" t="s">
         <v>418</v>
       </c>
@@ -7178,8 +7185,9 @@
       </c>
       <c r="G34" s="78"/>
       <c r="H34" s="78"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="78"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="44" t="s">
         <v>421</v>
       </c>
@@ -7195,6 +7203,7 @@
       </c>
       <c r="G35" s="78"/>
       <c r="H35" s="78"/>
+      <c r="I35" s="78"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="44" t="s">
@@ -7207,7 +7216,7 @@
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="79" t="s">
         <v>426</v>
       </c>
@@ -7217,27 +7226,28 @@
       <c r="F39" s="79"/>
       <c r="G39" s="79"/>
       <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B39:I39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7706,7 +7716,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>103</v>
       </c>
@@ -7715,7 +7725,6 @@
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -8254,7 +8263,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
         <v>178</v>
       </c>
@@ -8263,7 +8272,6 @@
       <c r="D62" s="19"/>
       <c r="E62" s="19"/>
       <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
     </row>
     <row r="63" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="21" t="s">
@@ -8785,7 +8793,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9147,7 +9155,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>215</v>
       </c>
@@ -9156,7 +9164,6 @@
       <c r="D7" s="19"/>
       <c r="E7" s="19"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
@@ -9259,7 +9266,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Homeschool_Co-Op_Mixed.xlsx
@@ -24,18 +24,19 @@
     <sheet sheetId="18" name="DSCR &amp; Covenants" state="visible" r:id="rId21"/>
     <sheet sheetId="19" name="Sources &amp; Uses" state="visible" r:id="rId22"/>
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
-    <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
+    <sheet sheetId="21" name="Lender Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
-    <sheet sheetId="24" name="Assumptions Memo" state="visible" r:id="rId27"/>
-    <sheet sheetId="25" name="Decision History" state="visible" r:id="rId28"/>
+    <sheet sheetId="24" name="Assumptions Confidence" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="Assumptions Memo" state="visible" r:id="rId28"/>
+    <sheet sheetId="26" name="Decision History" state="visible" r:id="rId29"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="466">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -43,7 +44,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · llc_single</t>
+    <t>Generated May 9, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -130,7 +131,7 @@
     <t>SchoolStack Budget</t>
   </si>
   <si>
-    <t>5-Year Financial Model &amp; Underwriting Workbook</t>
+    <t>5-Year Financial Model — Founder Planning Workbook</t>
   </si>
   <si>
     <t>School Name</t>
@@ -163,7 +164,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>May 7, 2026</t>
+    <t>May 9, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -304,7 +305,7 @@
     <t>21.</t>
   </si>
   <si>
-    <t>Underwriting Snapshot</t>
+    <t>Lender Snapshot</t>
   </si>
   <si>
     <t>22.</t>
@@ -319,6 +320,12 @@
     <t>Budget Narrative</t>
   </si>
   <si>
+    <t>24.</t>
+  </si>
+  <si>
+    <t>Assumptions Confidence</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -418,6 +425,39 @@
     <t>Annual Fixed</t>
   </si>
   <si>
+    <t>REVENUE QUALITY</t>
+  </si>
+  <si>
+    <t>Bucket</t>
+  </si>
+  <si>
+    <t>Contracted</t>
+  </si>
+  <si>
+    <t>Projected</t>
+  </si>
+  <si>
+    <t>Donor-dependent</t>
+  </si>
+  <si>
+    <t>Policy-dependent</t>
+  </si>
+  <si>
+    <t>Contracted %</t>
+  </si>
+  <si>
+    <t>Projected %</t>
+  </si>
+  <si>
+    <t>Donor-dependent %</t>
+  </si>
+  <si>
+    <t>Policy-dependent %</t>
+  </si>
+  <si>
+    <t>Hard Rev Coverage (Contracted ÷ Fixed + Debt)</t>
+  </si>
+  <si>
     <t>STAFFING</t>
   </si>
   <si>
@@ -928,7 +968,7 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
-    <t>Cash Trough: July (Month 1)</t>
+    <t>Cash Trough: September (Month 3)</t>
   </si>
   <si>
     <t>Your lowest cash point is the month lenders focus on to ensure you won't run out of money before collections start. Plan reserves to cover this trough.</t>
@@ -940,7 +980,10 @@
     <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
   </si>
   <si>
-    <t>Capital &amp; Debt Service</t>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Principal &amp; Capital Outlays</t>
   </si>
   <si>
     <t>Depreciation</t>
@@ -1039,6 +1082,9 @@
     <t>Ending Cash</t>
   </si>
   <si>
+    <t>Working-Capital Cash (basis for runway/days)</t>
+  </si>
+  <si>
     <t>Days Cash on Hand</t>
   </si>
   <si>
@@ -1120,7 +1166,7 @@
     <t>Enrollment: -25%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
-    <t>Underwriting Snapshot - Loan Committee Summary</t>
+    <t>Lender Conversation Snapshot - Summary</t>
   </si>
   <si>
     <t>Entity</t>
@@ -1147,13 +1193,34 @@
     <t>Enrollment</t>
   </si>
   <si>
+    <t>BREAK-EVEN &amp; DOWNSIDE</t>
+  </si>
+  <si>
+    <t>Break-Even Students</t>
+  </si>
+  <si>
+    <t>Break-Even Utilization %</t>
+  </si>
+  <si>
+    <t>-10% Enrollment: DSCR</t>
+  </si>
+  <si>
+    <t>-10% Enrollment: Ending Cash</t>
+  </si>
+  <si>
+    <t>-20% Enrollment: DSCR</t>
+  </si>
+  <si>
+    <t>-20% Enrollment: Ending Cash</t>
+  </si>
+  <si>
     <t>Prepared by SchoolStack Budget - budget.schoolstack.ai</t>
   </si>
   <si>
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1346,6 +1413,9 @@
   </si>
   <si>
     <t>Additional Context</t>
+  </si>
+  <si>
+    <t>No assumptions tagged yet — open the wizard and tag each major assumption (Actuals, Signed agreement, Written quote, Research, Estimate) with a one-line evidence note. The tags surface here, in the lender PDF, and on share links.</t>
   </si>
   <si>
     <t>Assumptions Memo</t>
@@ -1370,12 +1440,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0;#,##0;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.00x"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;×&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.00x"/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
@@ -1625,7 +1696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1659,17 +1730,18 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1687,7 +1759,7 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1700,7 +1772,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2469,7 +2541,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2482,44 +2554,44 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="36">
+        <v>111</v>
+      </c>
+      <c r="B4" s="37">
         <v>15</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="37">
         <v>22</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="37">
         <v>30</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="37">
         <v>36</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="37">
         <v>40</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -2529,126 +2601,126 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="31">
+        <v>119</v>
+      </c>
+      <c r="B7" s="25">
         <v>90000</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="25">
         <v>135960</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="25">
         <v>190962</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="25">
         <v>236029</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="25">
         <v>270122</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="31">
+        <v>123</v>
+      </c>
+      <c r="B8" s="25">
         <v>3000</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="25">
         <v>4400</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="25">
         <v>6000</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="25">
         <v>7200</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="25">
         <v>8000</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="31">
+        <v>124</v>
+      </c>
+      <c r="B9" s="25">
         <v>105000</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="25">
         <v>158620</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="25">
         <v>222789</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="25">
         <v>275367</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="25">
         <v>315142</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="31">
+        <v>126</v>
+      </c>
+      <c r="B10" s="25">
         <v>3000</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="25">
         <v>3090</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="25">
         <v>3183</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="25">
         <v>3278</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="25">
         <v>3377</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="B11" s="33">
+        <v>250</v>
+      </c>
+      <c r="B11" s="34">
         <f>SUM(B7:B10)</f>
         <v>201000</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="34">
         <f>SUM(C7:C10)</f>
         <v>302070</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="34">
         <f>SUM(D7:D10)</f>
         <v>422934</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="34">
         <f>SUM(E7:E10)</f>
         <v>521874</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="34">
         <f>SUM(F7:F10)</f>
         <v>596641</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B13" s="31">
+        <v>251</v>
+      </c>
+      <c r="B13" s="25">
         <v>13400</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="25">
         <v>13730</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="25">
         <v>14098</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="25">
         <v>14497</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="25">
         <v>14916</v>
       </c>
     </row>
@@ -2678,7 +2750,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2691,24 +2763,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2718,52 +2790,52 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B5" s="31">
+        <v>253</v>
+      </c>
+      <c r="B5" s="25">
         <v>13456</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="25">
         <v>16632</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="25">
         <v>17131</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="25">
         <v>17645</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="25">
         <v>18174</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="B6" s="32">
+        <v>254</v>
+      </c>
+      <c r="B6" s="33">
         <f>SUM(B5:B5)</f>
         <v>13456</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="33">
         <f>SUM(C5:C5)</f>
         <v>16632</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="33">
         <f>SUM(D5:D5)</f>
         <v>17131</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="33">
         <f>SUM(E5:E5)</f>
         <v>17645</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="33">
         <f>SUM(F5:F5)</f>
         <v>18174</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -2773,70 +2845,70 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B8" s="31">
+        <v>255</v>
+      </c>
+      <c r="B8" s="25">
         <v>51060</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="25">
         <v>63110</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="25">
         <v>65003</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="25">
         <v>66954</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="25">
         <v>68962</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="B9" s="32">
+        <v>256</v>
+      </c>
+      <c r="B9" s="33">
         <f>SUM(B8:B8)</f>
         <v>51060</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>SUM(C8:C8)</f>
         <v>63110</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <f>SUM(D8:D8)</f>
         <v>65003</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <f>SUM(E8:E8)</f>
         <v>66954</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>SUM(F8:F8)</f>
         <v>68962</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="B11" s="33">
+        <v>257</v>
+      </c>
+      <c r="B11" s="34">
         <f>B6+B9</f>
         <v>64516</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="34">
         <f>C6+C9</f>
         <v>79742</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="34">
         <f>D6+D9</f>
         <v>82134</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="34">
         <f>E6+E9</f>
         <v>84598</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="34">
         <f>F6+F9</f>
         <v>87136</v>
       </c>
@@ -2867,7 +2939,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2880,24 +2952,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2907,112 +2979,112 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="B5" s="31">
+        <v>260</v>
+      </c>
+      <c r="B5" s="25">
         <v>75000</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="25">
         <v>135960</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="25">
         <v>190962</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="25">
         <v>236029</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="25">
         <v>270122</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="B6" s="31">
+        <v>261</v>
+      </c>
+      <c r="B6" s="25">
         <v>2500</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="25">
         <v>4400</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="25">
         <v>6000</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="25">
         <v>7200</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="25">
         <v>8000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B7" s="31">
+        <v>262</v>
+      </c>
+      <c r="B7" s="25">
         <v>87500</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="25">
         <v>158620</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="25">
         <v>222789</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="25">
         <v>275367</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="25">
         <v>315142</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B8" s="31">
+        <v>263</v>
+      </c>
+      <c r="B8" s="25">
         <v>2500</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="25">
         <v>3090</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="25">
         <v>3183</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="25">
         <v>3278</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="25">
         <v>3377</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B9" s="32">
+        <v>264</v>
+      </c>
+      <c r="B9" s="33">
         <f>SUM(B5:B8)</f>
         <v>167500</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>SUM(C5:C8)</f>
         <v>302980</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <f>SUM(D5:D8)</f>
         <v>424730</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <f>SUM(E5:E8)</f>
         <v>523580</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>SUM(F5:F8)</f>
         <v>598240</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -3022,72 +3094,72 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="B12" s="31">
+        <v>266</v>
+      </c>
+      <c r="B12" s="25">
         <v>51060</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="25">
         <v>63110</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="25">
         <v>65003</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="25">
         <v>66954</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="25">
         <v>68962</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="B13" s="31">
+        <v>267</v>
+      </c>
+      <c r="B13" s="25">
         <v>13456</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="25">
         <v>16632</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="25">
         <v>17131</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="25">
         <v>17645</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="25">
         <v>18174</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="B14" s="32">
+        <v>229</v>
+      </c>
+      <c r="B14" s="33">
         <f>SUM(B12:B13)</f>
         <v>64516</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>SUM(C12:C13)</f>
         <v>79742</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <f>SUM(D12:D13)</f>
         <v>82134</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>SUM(E12:E13)</f>
         <v>84598</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>SUM(F12:F13)</f>
         <v>87136</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -3096,198 +3168,198 @@
       <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
-        <v>149</v>
+      <c r="A17" s="38" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B18" s="31">
+        <v>268</v>
+      </c>
+      <c r="B18" s="25">
         <v>5000</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="25">
         <v>9064</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="25">
         <v>12731</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="25">
         <v>15735</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="25">
         <v>18008</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
-        <v>150</v>
+      <c r="A19" s="38" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B20" s="31">
+        <v>269</v>
+      </c>
+      <c r="B20" s="25">
         <v>3125</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="25">
         <v>5665</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="25">
         <v>7957</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="25">
         <v>9835</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="25">
         <v>11255</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
-        <v>142</v>
+      <c r="A21" s="38" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B22" s="31">
+        <v>270</v>
+      </c>
+      <c r="B22" s="25">
         <v>18000</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="25">
         <v>22248</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="25">
         <v>22915</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="25">
         <v>23603</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="25">
         <v>24311</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B23" s="31">
+        <v>271</v>
+      </c>
+      <c r="B23" s="25">
         <v>2000</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="25">
         <v>2472</v>
       </c>
-      <c r="D23" s="31">
+      <c r="D23" s="25">
         <v>2546</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E23" s="25">
         <v>2623</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="25">
         <v>2701</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B24" s="31">
+        <v>272</v>
+      </c>
+      <c r="B24" s="25">
         <v>1500</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="25">
         <v>1854</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="25">
         <v>1910</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="25">
         <v>1967</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="25">
         <v>2026</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="B25" s="32">
+        <v>273</v>
+      </c>
+      <c r="B25" s="33">
         <f>SUM(B22:B24)</f>
         <v>21500</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <f>SUM(C22:C24)</f>
         <v>26574</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="33">
         <f>SUM(D22:D24)</f>
         <v>27371</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="33">
         <f>SUM(E22:E24)</f>
         <v>28192</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="33">
         <f>SUM(F22:F24)</f>
         <v>29038</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="37" t="s">
-        <v>147</v>
+      <c r="A26" s="38" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="B27" s="31">
+        <v>274</v>
+      </c>
+      <c r="B27" s="25">
         <v>3750</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="25">
         <v>4500</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="25">
         <v>4500</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="25">
         <v>4500</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="25">
         <v>4500</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="B28" s="32">
+        <v>275</v>
+      </c>
+      <c r="B28" s="33">
         <f>B18+B20+B25+B27</f>
         <v>33375</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <f>C18+C20+C25+C27</f>
         <v>45803</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <f>D18+D20+D25+D27</f>
         <v>52559</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="33">
         <f>E18+E20+E25+E27</f>
         <v>58262</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <f>F18+F20+F25+F27</f>
         <v>62801</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
@@ -3297,25 +3369,25 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="B31" s="32" t="str">
+        <v>277</v>
+      </c>
+      <c r="B31" s="33" t="str">
         <f>SUM(B31:B30)</f>
         <v>0</v>
       </c>
-      <c r="C31" s="32" t="str">
+      <c r="C31" s="33" t="str">
         <f>SUM(C31:C30)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="32" t="str">
+      <c r="D31" s="33" t="str">
         <f>SUM(D31:D30)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="32" t="str">
+      <c r="E31" s="33" t="str">
         <f>SUM(E31:E30)</f>
         <v>0</v>
       </c>
-      <c r="F31" s="32" t="str">
+      <c r="F31" s="33" t="str">
         <f>SUM(F31:F30)</f>
         <v>0</v>
       </c>
@@ -3346,7 +3418,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3359,149 +3431,149 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B4" s="34">
+        <v>264</v>
+      </c>
+      <c r="B4" s="35">
         <f>'Budget Detail'!B9</f>
         <v>167500</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="35">
         <f>'Budget Detail'!C9</f>
         <v>302980</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="35">
         <f>'Budget Detail'!D9</f>
         <v>424730</v>
       </c>
-      <c r="E4" s="34">
+      <c r="E4" s="35">
         <f>'Budget Detail'!E9</f>
         <v>523580</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="35">
         <f>'Budget Detail'!F9</f>
         <v>598240</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="34">
+        <v>229</v>
+      </c>
+      <c r="B5" s="35">
         <f>'Budget Detail'!B14</f>
         <v>64516</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="35">
         <f>'Budget Detail'!C14</f>
         <v>79742</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="35">
         <f>'Budget Detail'!D14</f>
         <v>82134</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="35">
         <f>'Budget Detail'!E14</f>
         <v>84598</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="35">
         <f>'Budget Detail'!F14</f>
         <v>87136</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="B6" s="34">
+        <v>275</v>
+      </c>
+      <c r="B6" s="35">
         <f>'Budget Detail'!B28</f>
         <v>33375</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="35">
         <f>'Budget Detail'!C28</f>
         <v>45803</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="35">
         <f>'Budget Detail'!D28</f>
         <v>52559</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="35">
         <f>'Budget Detail'!E28</f>
         <v>58262</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="35">
         <f>'Budget Detail'!F28</f>
         <v>62801</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="34" t="str">
+        <v>279</v>
+      </c>
+      <c r="B7" s="35" t="str">
         <f>'Budget Detail'!B31</f>
         <v>0</v>
       </c>
-      <c r="C7" s="34" t="str">
+      <c r="C7" s="35" t="str">
         <f>'Budget Detail'!C31</f>
         <v>0</v>
       </c>
-      <c r="D7" s="34" t="str">
+      <c r="D7" s="35" t="str">
         <f>'Budget Detail'!D31</f>
         <v>0</v>
       </c>
-      <c r="E7" s="34" t="str">
+      <c r="E7" s="35" t="str">
         <f>'Budget Detail'!E31</f>
         <v>0</v>
       </c>
-      <c r="F7" s="34" t="str">
+      <c r="F7" s="35" t="str">
         <f>'Budget Detail'!F31</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="B8" s="32">
+        <v>280</v>
+      </c>
+      <c r="B8" s="33">
         <f>SUM(B5:B7)</f>
         <v>97891</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <f>SUM(C5:C7)</f>
         <v>125545</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="33">
         <f>SUM(D5:D7)</f>
         <v>134693</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="33">
         <f>SUM(E5:E7)</f>
         <v>142861</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="33">
         <f>SUM(F5:F7)</f>
         <v>149938</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -3511,111 +3583,111 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="B11" s="33">
+        <v>282</v>
+      </c>
+      <c r="B11" s="34">
         <f>B4-B8</f>
         <v>69609</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="34">
         <f>C4-C8</f>
         <v>177435</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="34">
         <f>D4-D8</f>
         <v>290037</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="34">
         <f>E4-E8</f>
         <v>380719</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="34">
         <f>F4-F8</f>
         <v>448302</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B12" s="29">
+        <v>283</v>
+      </c>
+      <c r="B12" s="26">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.41557463</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="26">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.58563243</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="26">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.68287355</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="26">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.72714667</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="26">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.74936867</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B13" s="31">
+        <v>284</v>
+      </c>
+      <c r="B13" s="25">
         <v>69609</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="25">
         <v>247044</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="25">
         <v>537081</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="25">
         <v>917800</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="25">
         <v>1366102</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B14" s="31">
+        <v>251</v>
+      </c>
+      <c r="B14" s="25">
         <v>11167</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="25">
         <v>13772</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="25">
         <v>14158</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="25">
         <v>14544</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="25">
         <v>14956</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B15" s="31">
+        <v>285</v>
+      </c>
+      <c r="B15" s="25">
         <v>6526</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="25">
         <v>5707</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="25">
         <v>4490</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="25">
         <v>3968</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="25">
         <v>3748</v>
       </c>
     </row>
@@ -3646,7 +3718,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3667,48 +3739,48 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -3726,52 +3798,52 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B4" s="32">
-        <v>11050</v>
-      </c>
-      <c r="C4" s="32">
-        <v>20050</v>
-      </c>
-      <c r="D4" s="32">
-        <v>20050</v>
-      </c>
-      <c r="E4" s="32">
-        <v>20050</v>
-      </c>
-      <c r="F4" s="32">
-        <v>20050</v>
-      </c>
-      <c r="G4" s="32">
-        <v>20050</v>
-      </c>
-      <c r="H4" s="32">
-        <v>20050</v>
-      </c>
-      <c r="I4" s="32">
-        <v>20050</v>
-      </c>
-      <c r="J4" s="32">
-        <v>20050</v>
-      </c>
-      <c r="K4" s="32">
-        <v>20050</v>
-      </c>
-      <c r="L4" s="32">
+        <v>264</v>
+      </c>
+      <c r="B4" s="33">
+        <v>29500</v>
+      </c>
+      <c r="C4" s="33">
         <v>9250</v>
       </c>
-      <c r="M4" s="32">
+      <c r="D4" s="33">
+        <v>9250</v>
+      </c>
+      <c r="E4" s="33">
+        <v>35500</v>
+      </c>
+      <c r="F4" s="33">
+        <v>9250</v>
+      </c>
+      <c r="G4" s="33">
+        <v>9250</v>
+      </c>
+      <c r="H4" s="33">
+        <v>35500</v>
+      </c>
+      <c r="I4" s="33">
+        <v>9250</v>
+      </c>
+      <c r="J4" s="33">
+        <v>9250</v>
+      </c>
+      <c r="K4" s="33">
+        <v>35500</v>
+      </c>
+      <c r="L4" s="33">
+        <v>9250</v>
+      </c>
+      <c r="M4" s="33">
         <v>250</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="33">
         <f>SUM(B4:M4)</f>
         <v>201000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -3789,142 +3861,142 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B7" s="31">
+        <v>301</v>
+      </c>
+      <c r="B7" s="25">
         <v>6452</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="25">
         <v>6452</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="25">
         <v>6452</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="25">
         <v>6452</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="25">
         <v>6452</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="25">
         <v>6452</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="25">
         <v>6452</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="25">
         <v>6452</v>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="25">
         <v>6452</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="25">
         <v>6452</v>
       </c>
-      <c r="L7" s="31">
-        <v>0</v>
-      </c>
-      <c r="M7" s="31">
-        <v>0</v>
-      </c>
-      <c r="N7" s="31">
+      <c r="L7" s="25">
+        <v>0</v>
+      </c>
+      <c r="M7" s="25">
+        <v>0</v>
+      </c>
+      <c r="N7" s="25">
         <f>SUM(B7:M7)</f>
         <v>64516</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="B8" s="31">
+        <v>302</v>
+      </c>
+      <c r="B8" s="25">
         <v>3338</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="25">
         <v>3338</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="25">
         <v>3338</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="25">
         <v>3338</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="25">
         <v>3338</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="25">
         <v>3338</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="25">
         <v>3338</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="25">
         <v>3338</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="25">
         <v>3338</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="25">
         <v>3338</v>
       </c>
-      <c r="L8" s="31">
-        <v>0</v>
-      </c>
-      <c r="M8" s="31">
-        <v>0</v>
-      </c>
-      <c r="N8" s="31">
+      <c r="L8" s="25">
+        <v>0</v>
+      </c>
+      <c r="M8" s="25">
+        <v>0</v>
+      </c>
+      <c r="N8" s="25">
         <f>SUM(B8:M8)</f>
         <v>33375</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="B9" s="31">
-        <v>0</v>
-      </c>
-      <c r="C9" s="31">
-        <v>0</v>
-      </c>
-      <c r="D9" s="31">
-        <v>0</v>
-      </c>
-      <c r="E9" s="31">
-        <v>0</v>
-      </c>
-      <c r="F9" s="31">
-        <v>0</v>
-      </c>
-      <c r="G9" s="31">
-        <v>0</v>
-      </c>
-      <c r="H9" s="31">
-        <v>0</v>
-      </c>
-      <c r="I9" s="31">
-        <v>0</v>
-      </c>
-      <c r="J9" s="31">
-        <v>0</v>
-      </c>
-      <c r="K9" s="31">
-        <v>0</v>
-      </c>
-      <c r="L9" s="31">
-        <v>0</v>
-      </c>
-      <c r="M9" s="31">
-        <v>0</v>
-      </c>
-      <c r="N9" s="31" t="str">
+        <v>303</v>
+      </c>
+      <c r="B9" s="25">
+        <v>0</v>
+      </c>
+      <c r="C9" s="25">
+        <v>0</v>
+      </c>
+      <c r="D9" s="25">
+        <v>0</v>
+      </c>
+      <c r="E9" s="25">
+        <v>0</v>
+      </c>
+      <c r="F9" s="25">
+        <v>0</v>
+      </c>
+      <c r="G9" s="25">
+        <v>0</v>
+      </c>
+      <c r="H9" s="25">
+        <v>0</v>
+      </c>
+      <c r="I9" s="25">
+        <v>0</v>
+      </c>
+      <c r="J9" s="25">
+        <v>0</v>
+      </c>
+      <c r="K9" s="25">
+        <v>0</v>
+      </c>
+      <c r="L9" s="25">
+        <v>0</v>
+      </c>
+      <c r="M9" s="25">
+        <v>0</v>
+      </c>
+      <c r="N9" s="25" t="str">
         <f>SUM(B9:M9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -3942,185 +4014,185 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="B12" s="34">
+        <v>280</v>
+      </c>
+      <c r="B12" s="35">
         <f>B7+B8+B9</f>
         <v>9790</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="35">
         <f>C7+C8+C9</f>
         <v>9790</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="35">
         <f>D7+D8+D9</f>
         <v>9790</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="35">
         <f>E7+E8+E9</f>
         <v>9790</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="35">
         <f>F7+F8+F9</f>
         <v>9790</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="35">
         <f>G7+G8+G9</f>
         <v>9790</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="35">
         <f>H7+H8+H9</f>
         <v>9790</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="35">
         <f>I7+I8+I9</f>
         <v>9790</v>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="35">
         <f>J7+J8+J9</f>
         <v>9790</v>
       </c>
-      <c r="K12" s="34">
+      <c r="K12" s="35">
         <f>K7+K8+K9</f>
         <v>9790</v>
       </c>
-      <c r="L12" s="34" t="str">
+      <c r="L12" s="35" t="str">
         <f>L7+L8+L9</f>
         <v>0</v>
       </c>
-      <c r="M12" s="34" t="str">
+      <c r="M12" s="35" t="str">
         <f>M7+M8+M9</f>
         <v>0</v>
       </c>
-      <c r="N12" s="34">
+      <c r="N12" s="35">
         <f>SUM(B12:M12)</f>
         <v>97900</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="B13" s="34">
+        <v>305</v>
+      </c>
+      <c r="B13" s="35">
         <f>B4-B12</f>
-        <v>1260</v>
-      </c>
-      <c r="C13" s="34">
+        <v>19710</v>
+      </c>
+      <c r="C13" s="35">
         <f>C4-C12</f>
-        <v>10260</v>
-      </c>
-      <c r="D13" s="34">
+        <v>-540</v>
+      </c>
+      <c r="D13" s="35">
         <f>D4-D12</f>
-        <v>10260</v>
-      </c>
-      <c r="E13" s="34">
+        <v>-540</v>
+      </c>
+      <c r="E13" s="35">
         <f>E4-E12</f>
-        <v>10260</v>
-      </c>
-      <c r="F13" s="34">
+        <v>25710</v>
+      </c>
+      <c r="F13" s="35">
         <f>F4-F12</f>
-        <v>10260</v>
-      </c>
-      <c r="G13" s="34">
+        <v>-540</v>
+      </c>
+      <c r="G13" s="35">
         <f>G4-G12</f>
-        <v>10260</v>
-      </c>
-      <c r="H13" s="34">
+        <v>-540</v>
+      </c>
+      <c r="H13" s="35">
         <f>H4-H12</f>
-        <v>10260</v>
-      </c>
-      <c r="I13" s="34">
+        <v>25710</v>
+      </c>
+      <c r="I13" s="35">
         <f>I4-I12</f>
-        <v>10260</v>
-      </c>
-      <c r="J13" s="34">
+        <v>-540</v>
+      </c>
+      <c r="J13" s="35">
         <f>J4-J12</f>
-        <v>10260</v>
-      </c>
-      <c r="K13" s="34">
+        <v>-540</v>
+      </c>
+      <c r="K13" s="35">
         <f>K4-K12</f>
-        <v>10260</v>
-      </c>
-      <c r="L13" s="34">
+        <v>25710</v>
+      </c>
+      <c r="L13" s="35">
         <f>L4-L12</f>
         <v>9250</v>
       </c>
-      <c r="M13" s="34">
+      <c r="M13" s="35">
         <f>M4-M12</f>
         <v>250</v>
       </c>
-      <c r="N13" s="34">
+      <c r="N13" s="35">
         <f>SUM(B13:M13)</f>
         <v>103100</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="B14" s="38">
+        <v>306</v>
+      </c>
+      <c r="B14" s="39">
         <f>B17+B13</f>
-        <v>1260</v>
-      </c>
-      <c r="C14" s="38">
+        <v>19710</v>
+      </c>
+      <c r="C14" s="39">
         <f>B14+C13</f>
-        <v>11520</v>
-      </c>
-      <c r="D14" s="38">
+        <v>19170</v>
+      </c>
+      <c r="D14" s="39">
         <f>C14+D13</f>
-        <v>21780</v>
-      </c>
-      <c r="E14" s="38">
+        <v>18630</v>
+      </c>
+      <c r="E14" s="39">
         <f>D14+E13</f>
-        <v>32040</v>
-      </c>
-      <c r="F14" s="38">
+        <v>44340</v>
+      </c>
+      <c r="F14" s="39">
         <f>E14+F13</f>
-        <v>42300</v>
-      </c>
-      <c r="G14" s="38">
+        <v>43800</v>
+      </c>
+      <c r="G14" s="39">
         <f>F14+G13</f>
-        <v>52560</v>
-      </c>
-      <c r="H14" s="38">
+        <v>43260</v>
+      </c>
+      <c r="H14" s="39">
         <f>G14+H13</f>
-        <v>62820</v>
-      </c>
-      <c r="I14" s="38">
+        <v>68970</v>
+      </c>
+      <c r="I14" s="39">
         <f>H14+I13</f>
-        <v>73080</v>
-      </c>
-      <c r="J14" s="38">
+        <v>68430</v>
+      </c>
+      <c r="J14" s="39">
         <f>I14+J13</f>
-        <v>83340</v>
-      </c>
-      <c r="K14" s="38">
+        <v>67890</v>
+      </c>
+      <c r="K14" s="39">
         <f>J14+K13</f>
         <v>93600</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14" s="39">
         <f>K14+L13</f>
         <v>102850</v>
       </c>
-      <c r="M14" s="38">
+      <c r="M14" s="39">
         <f>L14+M13</f>
         <v>103100</v>
       </c>
-      <c r="N14" s="33">
+      <c r="N14" s="34">
         <f>M14</f>
         <v>103100</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B17" s="23">
         <v>0</v>
@@ -4128,25 +4200,25 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="B18" s="38">
+        <v>308</v>
+      </c>
+      <c r="B18" s="39">
         <f>M14</f>
         <v>103100</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="B19" s="31">
+        <v>309</v>
+      </c>
+      <c r="B19" s="25">
         <f>MIN(B14:M14)</f>
-        <v>1260</v>
+        <v>18630</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -4155,16 +4227,16 @@
       <c r="F20" s="3"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
-        <v>298</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
+      <c r="A21" s="40" t="s">
+        <v>311</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4185,7 +4257,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4194,7 +4266,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4203,38 +4275,38 @@
       <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
-        <v>300</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
+      <c r="A2" s="41" t="s">
+        <v>313</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4243,28 +4315,28 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
-        <v>251</v>
-      </c>
-      <c r="B5" s="32">
+      <c r="A5" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="33">
         <v>167500</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="33">
         <v>302980</v>
       </c>
-      <c r="D5" s="32">
+      <c r="D5" s="33">
         <v>424730</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="33">
         <v>523580</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="33">
         <v>598240</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4274,211 +4346,231 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="B8" s="34">
+        <v>301</v>
+      </c>
+      <c r="B8" s="35">
         <v>64516</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="35">
         <v>79742</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="35">
         <v>82134</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="35">
         <v>84598</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="35">
         <v>87136</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="34">
+        <v>302</v>
+      </c>
+      <c r="B9" s="35">
         <v>33375</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="35">
         <v>45803</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="35">
         <v>52559</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="35">
         <v>58262</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <v>62801</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="B10" s="34">
-        <v>0</v>
-      </c>
-      <c r="C10" s="34">
-        <v>0</v>
-      </c>
-      <c r="D10" s="34">
-        <v>0</v>
-      </c>
-      <c r="E10" s="34">
-        <v>0</v>
-      </c>
-      <c r="F10" s="34">
+        <v>314</v>
+      </c>
+      <c r="B10" s="35">
+        <v>0</v>
+      </c>
+      <c r="C10" s="35">
+        <v>0</v>
+      </c>
+      <c r="D10" s="35">
+        <v>0</v>
+      </c>
+      <c r="E10" s="35">
+        <v>0</v>
+      </c>
+      <c r="F10" s="35">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="B11" s="34">
+        <v>315</v>
+      </c>
+      <c r="B11" s="35">
+        <v>0</v>
+      </c>
+      <c r="C11" s="35">
+        <v>0</v>
+      </c>
+      <c r="D11" s="35">
+        <v>0</v>
+      </c>
+      <c r="E11" s="35">
+        <v>0</v>
+      </c>
+      <c r="F11" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B12" s="35">
         <v>286</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C12" s="35">
         <v>286</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D12" s="35">
         <v>286</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E12" s="35">
         <v>286</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F12" s="35">
         <v>286</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="B12" s="32">
-        <f>SUM(B8:B11)</f>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="B13" s="33">
+        <f>SUM(B8:B12)</f>
         <v>98177</v>
       </c>
-      <c r="C12" s="32">
-        <f>SUM(C8:C11)</f>
+      <c r="C13" s="33">
+        <f>SUM(C8:C12)</f>
         <v>125831</v>
       </c>
-      <c r="D12" s="32">
-        <f>SUM(D8:D11)</f>
+      <c r="D13" s="33">
+        <f>SUM(D8:D12)</f>
         <v>134979</v>
       </c>
-      <c r="E12" s="32">
-        <f>SUM(E8:E11)</f>
+      <c r="E13" s="33">
+        <f>SUM(E8:E12)</f>
         <v>143146</v>
       </c>
-      <c r="F12" s="32">
-        <f>SUM(F8:F11)</f>
+      <c r="F13" s="33">
+        <f>SUM(F8:F12)</f>
         <v>150223</v>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="B15" s="33">
-        <f>B5-B12</f>
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="B16" s="34">
+        <f>B5-B13</f>
         <v>69323</v>
       </c>
-      <c r="C15" s="33">
-        <f>C5-C12</f>
+      <c r="C16" s="34">
+        <f>C5-C13</f>
         <v>177149</v>
       </c>
-      <c r="D15" s="33">
-        <f>D5-D12</f>
+      <c r="D16" s="34">
+        <f>D5-D13</f>
         <v>289751</v>
       </c>
-      <c r="E15" s="33">
-        <f>E5-E12</f>
+      <c r="E16" s="34">
+        <f>E5-E13</f>
         <v>380434</v>
       </c>
-      <c r="F15" s="33">
-        <f>F5-F12</f>
+      <c r="F16" s="34">
+        <f>F5-F13</f>
         <v>448017</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B16" s="29">
-        <f>IF(B5=0,0,B15/B5)</f>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="B17" s="26">
+        <f>IF(B5=0,0,B16/B5)</f>
         <v>0.41386887</v>
       </c>
-      <c r="C16" s="29">
-        <f>IF(C5=0,0,C15/C5)</f>
+      <c r="C17" s="26">
+        <f>IF(C5=0,0,C16/C5)</f>
         <v>0.58468942</v>
       </c>
-      <c r="D16" s="29">
-        <f>IF(D5=0,0,D15/D5)</f>
+      <c r="D17" s="26">
+        <f>IF(D5=0,0,D16/D5)</f>
         <v>0.68220085</v>
       </c>
-      <c r="E16" s="29">
-        <f>IF(E5=0,0,E15/E5)</f>
+      <c r="E17" s="26">
+        <f>IF(E5=0,0,E16/E5)</f>
         <v>0.72660098</v>
       </c>
-      <c r="F16" s="29">
-        <f>IF(F5=0,0,F15/F5)</f>
+      <c r="F17" s="26">
+        <f>IF(F5=0,0,F16/F5)</f>
         <v>0.74889108</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B17" s="34">
-        <f>B15</f>
-        <v>69323</v>
-      </c>
-      <c r="C17" s="34">
-        <f>B17+C15</f>
-        <v>246472</v>
-      </c>
-      <c r="D17" s="34">
-        <f>C17+D15</f>
-        <v>536223</v>
-      </c>
-      <c r="E17" s="34">
-        <f>D17+E15</f>
-        <v>916657</v>
-      </c>
-      <c r="F17" s="34">
-        <f>E17+F15</f>
-        <v>1364674</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>305</v>
-      </c>
-      <c r="C18" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="B18" s="35">
+        <f>B16</f>
+        <v>69323</v>
+      </c>
+      <c r="C18" s="35">
+        <f>B18+C16</f>
+        <v>246472</v>
+      </c>
+      <c r="D18" s="35">
+        <f>C18+D16</f>
+        <v>536223</v>
+      </c>
+      <c r="E18" s="35">
+        <f>D18+E16</f>
+        <v>916657</v>
+      </c>
+      <c r="F18" s="35">
+        <f>E18+F16</f>
+        <v>1364674</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>319</v>
+      </c>
+      <c r="C19" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="D19" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E19" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="43" t="s">
+      <c r="F19" s="44" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4522,24 +4614,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4548,20 +4640,20 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="B5" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>309</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>232</v>
+      <c r="A5" s="45" t="s">
+        <v>321</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>322</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>323</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -4590,7 +4682,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4603,24 +4695,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4630,117 +4722,117 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="B5" s="47">
+        <v>326</v>
+      </c>
+      <c r="B5" s="48">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>103100</v>
       </c>
-      <c r="C5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15</f>
+      <c r="C5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C16</f>
         <v>280535</v>
       </c>
-      <c r="D5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
+      <c r="D5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C16+'5-Year Operating Stmt'!D16</f>
         <v>570572</v>
       </c>
-      <c r="E5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
+      <c r="E5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C16+'5-Year Operating Stmt'!D16+'5-Year Operating Stmt'!E16</f>
         <v>951291</v>
       </c>
-      <c r="F5" s="47">
-        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
+      <c r="F5" s="48">
+        <f>B5+'5-Year Operating Stmt'!C16+'5-Year Operating Stmt'!D16+'5-Year Operating Stmt'!E16+'5-Year Operating Stmt'!F16</f>
         <v>1399594</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="B6" s="31">
+        <v>327</v>
+      </c>
+      <c r="B6" s="25">
         <v>510</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="25">
         <v>524</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="25">
         <v>540</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="25">
         <v>555</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="25">
         <v>571</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="B7" s="31">
+        <v>328</v>
+      </c>
+      <c r="B7" s="25">
         <v>1714</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="25">
         <v>1429</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="25">
         <v>1143</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="25">
         <v>857</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="25">
         <v>571</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="B8" s="31">
-        <v>0</v>
-      </c>
-      <c r="C8" s="31">
-        <v>0</v>
-      </c>
-      <c r="D8" s="31">
-        <v>0</v>
-      </c>
-      <c r="E8" s="31">
-        <v>0</v>
-      </c>
-      <c r="F8" s="31">
+        <v>329</v>
+      </c>
+      <c r="B8" s="25">
+        <v>0</v>
+      </c>
+      <c r="C8" s="25">
+        <v>0</v>
+      </c>
+      <c r="D8" s="25">
+        <v>0</v>
+      </c>
+      <c r="E8" s="25">
+        <v>0</v>
+      </c>
+      <c r="F8" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="B9" s="32">
+        <v>330</v>
+      </c>
+      <c r="B9" s="33">
         <f>SUM(B5:B8)</f>
         <v>105324</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>SUM(C5:C8)</f>
         <v>282488</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <f>SUM(D5:D8)</f>
         <v>572254</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <f>SUM(E5:E8)</f>
         <v>952704</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>SUM(F5:F8)</f>
         <v>1400736</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4750,72 +4842,72 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="B12" s="31">
-        <v>0</v>
-      </c>
-      <c r="C12" s="31">
-        <v>0</v>
-      </c>
-      <c r="D12" s="31">
-        <v>0</v>
-      </c>
-      <c r="E12" s="31">
-        <v>0</v>
-      </c>
-      <c r="F12" s="31">
+        <v>332</v>
+      </c>
+      <c r="B12" s="25">
+        <v>0</v>
+      </c>
+      <c r="C12" s="25">
+        <v>0</v>
+      </c>
+      <c r="D12" s="25">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25">
+        <v>0</v>
+      </c>
+      <c r="F12" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="B13" s="31">
-        <v>0</v>
-      </c>
-      <c r="C13" s="31">
-        <v>0</v>
-      </c>
-      <c r="D13" s="31">
-        <v>0</v>
-      </c>
-      <c r="E13" s="31">
-        <v>0</v>
-      </c>
-      <c r="F13" s="31">
+        <v>333</v>
+      </c>
+      <c r="B13" s="25">
+        <v>0</v>
+      </c>
+      <c r="C13" s="25">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <v>0</v>
+      </c>
+      <c r="E13" s="25">
+        <v>0</v>
+      </c>
+      <c r="F13" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="B14" s="32" t="str">
+        <v>334</v>
+      </c>
+      <c r="B14" s="33" t="str">
         <f>SUM(B12:B13)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="32" t="str">
+      <c r="C14" s="33" t="str">
         <f>SUM(C12:C13)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="32" t="str">
+      <c r="D14" s="33" t="str">
         <f>SUM(D12:D13)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="32" t="str">
+      <c r="E14" s="33" t="str">
         <f>SUM(E12:E13)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="32" t="str">
+      <c r="F14" s="33" t="str">
         <f>SUM(F12:F13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4825,50 +4917,50 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="B17" s="33">
+        <v>336</v>
+      </c>
+      <c r="B17" s="34">
         <f>B9-B14</f>
         <v>105324</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="34">
         <f>C9-C14</f>
         <v>282488</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="34">
         <f>D9-D14</f>
         <v>572254</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="34">
         <f>E9-E14</f>
         <v>952704</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="34">
         <f>F9-F14</f>
         <v>1400736</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="B19" s="48" t="str">
+        <v>337</v>
+      </c>
+      <c r="B19" s="49" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="48" t="str">
+      <c r="C19" s="49" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="48" t="str">
+      <c r="D19" s="49" t="str">
         <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="48" t="str">
+      <c r="E19" s="49" t="str">
         <f>E9-E14-E17</f>
         <v>0</v>
       </c>
-      <c r="F19" s="48" t="str">
+      <c r="F19" s="49" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -4890,7 +4982,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4899,7 +4991,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4912,24 +5004,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4939,172 +5031,172 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="B5" s="31">
+        <v>340</v>
+      </c>
+      <c r="B5" s="25">
         <v>167500</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="25">
         <v>302980</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="25">
         <v>424730</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="25">
         <v>523580</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="25">
         <v>598240</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B6" s="31">
+        <v>301</v>
+      </c>
+      <c r="B6" s="25">
         <v>64516</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="25">
         <v>79742</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="25">
         <v>82134</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="25">
         <v>84598</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="25">
         <v>87136</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="B7" s="31">
+        <v>302</v>
+      </c>
+      <c r="B7" s="25">
         <v>33375</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="25">
         <v>45803</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="25">
         <v>52559</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="25">
         <v>58262</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="25">
         <v>62801</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="B8" s="34">
+        <v>282</v>
+      </c>
+      <c r="B8" s="35">
         <v>69609</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="35">
         <v>177435</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="35">
         <v>290037</v>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="35">
         <v>380719</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="35">
         <v>448302</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="B9" s="31">
+        <v>341</v>
+      </c>
+      <c r="B9" s="25">
         <v>286</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="25">
         <v>286</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="25">
         <v>286</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="25">
         <v>286</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="25">
         <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="B10" s="31">
-        <v>0</v>
-      </c>
-      <c r="C10" s="31">
-        <v>0</v>
-      </c>
-      <c r="D10" s="31">
-        <v>0</v>
-      </c>
-      <c r="E10" s="31">
-        <v>0</v>
-      </c>
-      <c r="F10" s="31">
+        <v>342</v>
+      </c>
+      <c r="B10" s="25">
+        <v>0</v>
+      </c>
+      <c r="C10" s="25">
+        <v>0</v>
+      </c>
+      <c r="D10" s="25">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25">
+        <v>0</v>
+      </c>
+      <c r="F10" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="B11" s="34">
+        <v>343</v>
+      </c>
+      <c r="B11" s="35">
         <f>B8+B9+B10</f>
         <v>69894</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="35">
         <f>C8+C9+C10</f>
         <v>177721</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="35">
         <f>D8+D9+D10</f>
         <v>290323</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="35">
         <f>E8+E9+E10</f>
         <v>381005</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="35">
         <f>F8+F9+F10</f>
         <v>448588</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>331</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>331</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>331</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>331</v>
-      </c>
-      <c r="F12" s="49" t="s">
-        <v>331</v>
+        <v>344</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -5114,312 +5206,332 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="B15" s="31">
+        <v>347</v>
+      </c>
+      <c r="B15" s="25">
+        <v>79609</v>
+      </c>
+      <c r="C15" s="25">
+        <v>257044</v>
+      </c>
+      <c r="D15" s="25">
+        <v>547081</v>
+      </c>
+      <c r="E15" s="25">
+        <v>927800</v>
+      </c>
+      <c r="F15" s="25">
+        <v>1376102</v>
+      </c>
+    </row>
+    <row r="16" hidden="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="B16" s="25">
         <v>103100</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C16" s="25">
         <v>280535</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D16" s="25">
         <v>570572</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E16" s="25">
         <v>951291</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F16" s="25">
         <v>1399594</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="B16" s="50">
-        <f>IF((B5-B8)=0,0,(B15/(B5-B8))*365)</f>
-        <v>384</v>
-      </c>
-      <c r="C16" s="50">
-        <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
-        <v>816</v>
-      </c>
-      <c r="D16" s="50">
-        <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
-        <v>1546</v>
-      </c>
-      <c r="E16" s="50">
-        <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
-        <v>2430</v>
-      </c>
-      <c r="F16" s="50">
-        <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
-        <v>3407</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="B17" s="35">
-        <f>IF((B5-B8)=0,0,B15/((B5-B8)/12))</f>
-        <v>12.6</v>
-      </c>
-      <c r="C17" s="35">
-        <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
-        <v>26.8</v>
-      </c>
-      <c r="D17" s="35">
-        <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
-        <v>50.8</v>
-      </c>
-      <c r="E17" s="35">
-        <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
-        <v>79.9</v>
-      </c>
-      <c r="F17" s="35">
-        <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
-        <v>112</v>
+        <v>349</v>
+      </c>
+      <c r="B17" s="51">
+        <f>IF((B5-B8)=0,0,(B16/(B5-B8))*365)</f>
+        <v>384</v>
+      </c>
+      <c r="C17" s="51">
+        <f>IF((C5-C8)=0,0,(C16/(C5-C8))*365)</f>
+        <v>816</v>
+      </c>
+      <c r="D17" s="51">
+        <f>IF((D5-D8)=0,0,(D16/(D5-D8))*365)</f>
+        <v>1546</v>
+      </c>
+      <c r="E17" s="51">
+        <f>IF((E5-E8)=0,0,(E16/(E5-E8))*365)</f>
+        <v>2430</v>
+      </c>
+      <c r="F17" s="51">
+        <f>IF((F5-F8)=0,0,(F16/(F5-F8))*365)</f>
+        <v>3407</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B18" s="29">
+        <v>350</v>
+      </c>
+      <c r="B18" s="36">
+        <f>IF((B5-B8)=0,0,B16/((B5-B8)/12))</f>
+        <v>12.6</v>
+      </c>
+      <c r="C18" s="36">
+        <f>IF((C5-C8)=0,0,C16/((C5-C8)/12))</f>
+        <v>26.8</v>
+      </c>
+      <c r="D18" s="36">
+        <f>IF((D5-D8)=0,0,D16/((D5-D8)/12))</f>
+        <v>50.8</v>
+      </c>
+      <c r="E18" s="36">
+        <f>IF((E5-E8)=0,0,E16/((E5-E8)/12))</f>
+        <v>79.9</v>
+      </c>
+      <c r="F18" s="36">
+        <f>IF((F5-F8)=0,0,F16/((F5-F8)/12))</f>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="B19" s="26">
         <v>0.375</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="26">
         <v>0.55</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D19" s="26">
         <v>0.75</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E19" s="26">
         <v>0.9</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F19" s="26">
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>336</v>
-      </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B21" s="31">
-        <v>11167</v>
-      </c>
-      <c r="C21" s="31">
-        <v>13772</v>
-      </c>
-      <c r="D21" s="31">
-        <v>14158</v>
-      </c>
-      <c r="E21" s="31">
-        <v>14544</v>
-      </c>
-      <c r="F21" s="31">
-        <v>14956</v>
-      </c>
+    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="B22" s="31">
-        <v>64516</v>
-      </c>
-      <c r="C22" s="31">
-        <v>79742</v>
-      </c>
-      <c r="D22" s="31">
-        <v>82134</v>
-      </c>
-      <c r="E22" s="31">
-        <v>84598</v>
-      </c>
-      <c r="F22" s="31">
-        <v>87136</v>
+        <v>251</v>
+      </c>
+      <c r="B22" s="25">
+        <v>11167</v>
+      </c>
+      <c r="C22" s="25">
+        <v>13772</v>
+      </c>
+      <c r="D22" s="25">
+        <v>14158</v>
+      </c>
+      <c r="E22" s="25">
+        <v>14544</v>
+      </c>
+      <c r="F22" s="25">
+        <v>14956</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="B23" s="31">
+        <v>352</v>
+      </c>
+      <c r="B23" s="25">
+        <v>64516</v>
+      </c>
+      <c r="C23" s="25">
+        <v>79742</v>
+      </c>
+      <c r="D23" s="25">
+        <v>82134</v>
+      </c>
+      <c r="E23" s="25">
+        <v>84598</v>
+      </c>
+      <c r="F23" s="25">
+        <v>87136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="B24" s="25">
         <v>2225</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C24" s="25">
         <v>2082</v>
       </c>
-      <c r="D23" s="31">
+      <c r="D24" s="25">
         <v>1752</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E24" s="25">
         <v>1618</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F24" s="25">
         <v>1570</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="B24" s="51">
-        <v>8</v>
-      </c>
-      <c r="C24" s="51">
-        <v>7</v>
-      </c>
-      <c r="D24" s="51">
-        <v>7</v>
-      </c>
-      <c r="E24" s="51">
-        <v>7</v>
-      </c>
-      <c r="F24" s="51">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="B27" s="52" t="s">
-        <v>331</v>
-      </c>
-      <c r="C27" s="52" t="s">
-        <v>331</v>
-      </c>
-      <c r="D27" s="52" t="s">
-        <v>331</v>
-      </c>
-      <c r="E27" s="52" t="s">
-        <v>331</v>
-      </c>
-      <c r="F27" s="52" t="s">
-        <v>331</v>
-      </c>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="B25" s="52">
+        <v>9</v>
+      </c>
+      <c r="C25" s="52">
+        <v>9</v>
+      </c>
+      <c r="D25" s="52">
+        <v>9</v>
+      </c>
+      <c r="E25" s="52">
+        <v>9</v>
+      </c>
+      <c r="F25" s="52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D28" s="53" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E28" s="53" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F28" s="53" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="B29" s="52" t="s">
-        <v>331</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>331</v>
-      </c>
-      <c r="D29" s="52" t="s">
-        <v>331</v>
-      </c>
-      <c r="E29" s="52" t="s">
-        <v>331</v>
-      </c>
-      <c r="F29" s="52" t="s">
-        <v>331</v>
+        <v>357</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="E29" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="F29" s="54" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B30" s="53" t="s">
         <v>345</v>
       </c>
-      <c r="B30" s="54" t="s">
-        <v>346</v>
-      </c>
-      <c r="C30" s="54" t="s">
-        <v>346</v>
+      <c r="C30" s="53" t="s">
+        <v>345</v>
       </c>
       <c r="D30" s="53" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E30" s="53" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F30" s="53" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>343</v>
-      </c>
-      <c r="C31" s="53" t="s">
-        <v>343</v>
-      </c>
-      <c r="D31" s="53" t="s">
-        <v>343</v>
-      </c>
-      <c r="E31" s="53" t="s">
-        <v>343</v>
-      </c>
-      <c r="F31" s="53" t="s">
-        <v>343</v>
+        <v>360</v>
+      </c>
+      <c r="B31" s="55" t="s">
+        <v>361</v>
+      </c>
+      <c r="C31" s="55" t="s">
+        <v>361</v>
+      </c>
+      <c r="D31" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="E31" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="F31" s="54" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="B32" s="53" t="s">
-        <v>343</v>
-      </c>
-      <c r="C32" s="53" t="s">
-        <v>343</v>
-      </c>
-      <c r="D32" s="53" t="s">
-        <v>343</v>
-      </c>
-      <c r="E32" s="53" t="s">
-        <v>343</v>
-      </c>
-      <c r="F32" s="53" t="s">
-        <v>343</v>
+        <v>362</v>
+      </c>
+      <c r="B32" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="D32" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="E32" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="F32" s="54" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B33" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="D33" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="E33" s="54" t="s">
+        <v>358</v>
+      </c>
+      <c r="F33" s="54" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -5459,52 +5571,52 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
-        <v>349</v>
-      </c>
-      <c r="B3" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="55" t="s">
-        <v>350</v>
-      </c>
-      <c r="E3" s="55" t="s">
-        <v>114</v>
+      <c r="A3" s="56" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="56" t="s">
+        <v>365</v>
+      </c>
+      <c r="E3" s="56" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="B4" s="31">
+        <v>366</v>
+      </c>
+      <c r="B4" s="25">
         <v>12000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="E4" s="31">
+        <v>367</v>
+      </c>
+      <c r="E4" s="25">
         <v>12000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="B6" s="33">
+        <v>368</v>
+      </c>
+      <c r="B6" s="34">
         <v>12000</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="E6" s="33">
+        <v>369</v>
+      </c>
+      <c r="E6" s="34">
         <v>12000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="B7" s="48">
+        <v>370</v>
+      </c>
+      <c r="B7" s="49">
         <v>0</v>
       </c>
     </row>
@@ -5525,7 +5637,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C44"/>
+  <dimension ref="B3:C45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5799,18 +5911,26 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="14" t="s">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="14"/>
+      <c r="C42" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Instructions'!A1"/>
@@ -5833,9 +5953,10 @@
     <hyperlink ref="C36" r:id="rId18" location="#'DSCR &amp; Covenants'!A1"/>
     <hyperlink ref="C37" r:id="rId19" location="#'Sources &amp; Uses'!A1"/>
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
-    <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
+    <hyperlink ref="C39" r:id="rId21" location="#'Lender Snapshot'!A1"/>
     <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
     <hyperlink ref="C41" r:id="rId23" location="#'Budget Narrative'!A1"/>
+    <hyperlink ref="C42" r:id="rId24" location="#'Assumptions Confidence'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -5859,7 +5980,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5869,7 +5990,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -5879,7 +6000,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5887,144 +6008,144 @@
         <v>7</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="B6" s="31">
+        <v>340</v>
+      </c>
+      <c r="B6" s="25">
         <v>167500</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="25">
         <v>302980</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="25">
         <v>424730</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="25">
         <v>523580</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="25">
         <v>598240</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B7" s="31">
+        <v>280</v>
+      </c>
+      <c r="B7" s="25">
         <v>97891</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="25">
         <v>125545</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="25">
         <v>134693</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="25">
         <v>142861</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="25">
         <v>149938</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="B8" s="33">
+        <v>282</v>
+      </c>
+      <c r="B8" s="34">
         <v>69609</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <v>177435</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="34">
         <v>290037</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <v>380719</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <v>448302</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B9" s="29">
+        <v>283</v>
+      </c>
+      <c r="B9" s="26">
         <v>0.41557462686567165</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="26">
         <v>0.5856324344841243</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="26">
         <v>0.6828735489605162</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="26">
         <v>0.7271466702767485</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="26">
         <v>0.7493686719814874</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="C10" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="D10" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="E10" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="F10" s="56" t="s">
-        <v>331</v>
+        <v>344</v>
+      </c>
+      <c r="B10" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="D10" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="B11" s="50">
+        <v>354</v>
+      </c>
+      <c r="B11" s="51">
         <v>8</v>
       </c>
-      <c r="C11" s="50">
+      <c r="C11" s="51">
         <v>7</v>
       </c>
-      <c r="D11" s="50">
+      <c r="D11" s="51">
         <v>7</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="51">
         <v>7</v>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="51">
         <v>7</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6034,7 +6155,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6042,138 +6163,138 @@
         <v>7</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="B16" s="31">
+        <v>340</v>
+      </c>
+      <c r="B16" s="25">
         <v>125625</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="25">
         <v>227235</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="25">
         <v>318548</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="25">
         <v>392685</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="25">
         <v>448680</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B17" s="31">
+        <v>280</v>
+      </c>
+      <c r="B17" s="25">
         <v>97891</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="25">
         <v>125545</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="25">
         <v>134693</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="25">
         <v>142861</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="25">
         <v>149938</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="B18" s="33">
+        <v>282</v>
+      </c>
+      <c r="B18" s="34">
         <v>27734</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="34">
         <v>101690</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="34">
         <v>183854</v>
       </c>
-      <c r="E18" s="33">
+      <c r="E18" s="34">
         <v>249824</v>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="34">
         <v>298742</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B19" s="29">
+        <v>283</v>
+      </c>
+      <c r="B19" s="26">
         <v>0.22076616915422886</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="26">
         <v>0.4475099126454991</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="26">
         <v>0.5771647319473548</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="26">
         <v>0.636195560368998</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="26">
         <v>0.6658248959753165</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B20" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="C20" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="D20" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="E20" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="F20" s="56" t="s">
-        <v>331</v>
+        <v>344</v>
+      </c>
+      <c r="B20" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="C20" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="D20" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="E20" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="F20" s="57" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="B21" s="50">
+        <v>354</v>
+      </c>
+      <c r="B21" s="51">
         <v>8</v>
       </c>
-      <c r="C21" s="50">
+      <c r="C21" s="51">
         <v>8</v>
       </c>
-      <c r="D21" s="50">
+      <c r="D21" s="51">
         <v>8</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="51">
         <v>7</v>
       </c>
-      <c r="F21" s="50">
+      <c r="F21" s="51">
         <v>7</v>
       </c>
     </row>
@@ -6194,7 +6315,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -6205,7 +6326,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6217,7 +6338,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B3" s="19"/>
     </row>
@@ -6231,7 +6352,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -6239,7 +6360,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6263,7 +6384,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -6271,7 +6392,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -6291,125 +6412,125 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="57" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="F12" s="57" t="s">
+      <c r="D12" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="57" t="s">
+      <c r="E12" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="57" t="s">
+      <c r="F12" s="58" t="s">
         <v>108</v>
+      </c>
+      <c r="G12" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="D13" s="31">
+        <v>340</v>
+      </c>
+      <c r="D13" s="25">
         <v>167500</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="25">
         <v>302980</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="25">
         <v>424730</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="25">
         <v>523580</v>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="25">
         <v>598240</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D14" s="31">
+        <v>280</v>
+      </c>
+      <c r="D14" s="25">
         <v>97891</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="25">
         <v>125545</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="25">
         <v>134693</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="25">
         <v>142861</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="25">
         <v>149938</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="D15" s="31">
+        <v>282</v>
+      </c>
+      <c r="D15" s="25">
         <v>69609</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="25">
         <v>177435</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="25">
         <v>290037</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="25">
         <v>380719</v>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="25">
         <v>448302</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="D16" s="31">
+        <v>380</v>
+      </c>
+      <c r="D16" s="25">
         <v>103100</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="25">
         <v>280535</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="25">
         <v>570572</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="25">
         <v>951291</v>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="25">
         <v>1399594</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="D17" s="31">
-        <v>0</v>
-      </c>
-      <c r="E17" s="31">
-        <v>0</v>
-      </c>
-      <c r="F17" s="31">
-        <v>0</v>
-      </c>
-      <c r="G17" s="31">
-        <v>0</v>
-      </c>
-      <c r="H17" s="31">
+        <v>381</v>
+      </c>
+      <c r="D17" s="25">
+        <v>0</v>
+      </c>
+      <c r="E17" s="25">
+        <v>0</v>
+      </c>
+      <c r="F17" s="25">
+        <v>0</v>
+      </c>
+      <c r="G17" s="25">
+        <v>0</v>
+      </c>
+      <c r="H17" s="25">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -6429,118 +6550,276 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="57" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" s="57" t="s">
+      <c r="D20" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="G20" s="57" t="s">
+      <c r="E20" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="H20" s="57" t="s">
+      <c r="F20" s="58" t="s">
         <v>108</v>
+      </c>
+      <c r="G20" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="H20" s="58" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="D21" s="29">
+        <v>383</v>
+      </c>
+      <c r="D21" s="26">
         <v>0.41557462686567165</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="26">
         <v>0.5856324344841243</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="26">
         <v>0.6828735489605162</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="26">
         <v>0.7271466702767485</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="26">
         <v>0.7493686719814874</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="D22" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="E22" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="F22" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="G22" s="56" t="s">
-        <v>331</v>
-      </c>
-      <c r="H22" s="56" t="s">
-        <v>331</v>
+        <v>344</v>
+      </c>
+      <c r="D22" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="E22" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="F22" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="G22" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="H22" s="57" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="D23" s="29">
+        <v>213</v>
+      </c>
+      <c r="D23" s="26">
         <v>0.375</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="26">
         <v>0.55</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="26">
         <v>0.75</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="26">
         <v>0.9</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="26">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="D24" s="50">
+        <v>384</v>
+      </c>
+      <c r="D24" s="51">
         <v>15</v>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="51">
         <v>22</v>
       </c>
-      <c r="F24" s="50">
+      <c r="F24" s="51">
         <v>30</v>
       </c>
-      <c r="G24" s="50">
+      <c r="G24" s="51">
         <v>36</v>
       </c>
-      <c r="H24" s="50">
+      <c r="H24" s="51">
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
+    <row r="26" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="G27" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="58" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="D28" s="51">
+        <v>9</v>
+      </c>
+      <c r="E28" s="51">
+        <v>9</v>
+      </c>
+      <c r="F28" s="51">
+        <v>9</v>
+      </c>
+      <c r="G28" s="51">
+        <v>9</v>
+      </c>
+      <c r="H28" s="51">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="D29" s="26">
+        <v>0.225</v>
+      </c>
+      <c r="E29" s="26">
+        <v>0.225</v>
+      </c>
+      <c r="F29" s="26">
+        <v>0.225</v>
+      </c>
+      <c r="G29" s="26">
+        <v>0.225</v>
+      </c>
+      <c r="H29" s="26">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="D30" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="E30" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="F30" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="G30" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="H30" s="57" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="D31" s="25">
+        <v>69150</v>
+      </c>
+      <c r="E31" s="25">
+        <v>220830</v>
+      </c>
+      <c r="F31" s="25">
+        <v>471186</v>
+      </c>
+      <c r="G31" s="25">
+        <v>797523</v>
+      </c>
+      <c r="H31" s="25">
+        <v>1190026</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="D32" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="E32" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="F32" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="G32" s="57" t="s">
+        <v>345</v>
+      </c>
+      <c r="H32" s="57" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D33" s="25">
+        <v>48234</v>
+      </c>
+      <c r="E33" s="25">
+        <v>174066</v>
+      </c>
+      <c r="F33" s="25">
+        <v>384498</v>
+      </c>
+      <c r="G33" s="25">
+        <v>669719</v>
+      </c>
+      <c r="H33" s="25">
+        <v>1005769</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A35:H35"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6568,7 +6847,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -6579,654 +6858,654 @@
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="58" t="s">
-        <v>372</v>
-      </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
+      <c r="B3" s="59" t="s">
+        <v>394</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="59" t="s">
-        <v>373</v>
-      </c>
-      <c r="D4" s="60" t="s">
-        <v>374</v>
-      </c>
-      <c r="F4" s="61" t="s">
-        <v>375</v>
+      <c r="B4" s="60" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" s="61" t="s">
+        <v>396</v>
+      </c>
+      <c r="F4" s="62" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="C6" s="62" t="s">
-        <v>377</v>
-      </c>
-      <c r="D6" s="62" t="s">
-        <v>378</v>
-      </c>
-      <c r="E6" s="62" t="s">
-        <v>379</v>
-      </c>
-      <c r="F6" s="62" t="s">
-        <v>380</v>
-      </c>
-      <c r="G6" s="62" t="s">
-        <v>381</v>
-      </c>
-      <c r="H6" s="62" t="s">
-        <v>382</v>
+        <v>398</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>399</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>400</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>401</v>
+      </c>
+      <c r="F6" s="63" t="s">
+        <v>402</v>
+      </c>
+      <c r="G6" s="63" t="s">
+        <v>403</v>
+      </c>
+      <c r="H6" s="63" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="C7" s="63">
+        <v>384</v>
+      </c>
+      <c r="C7" s="64">
         <v>15</v>
       </c>
-      <c r="D7" s="63">
+      <c r="D7" s="64">
         <v>22</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="64">
         <v>30</v>
       </c>
-      <c r="F7" s="63">
+      <c r="F7" s="64">
         <v>36</v>
       </c>
-      <c r="G7" s="63">
+      <c r="G7" s="64">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="C8" s="64">
+        <v>340</v>
+      </c>
+      <c r="C8" s="65">
         <v>167500</v>
       </c>
-      <c r="D8" s="64">
+      <c r="D8" s="65">
         <v>302980</v>
       </c>
-      <c r="E8" s="64">
+      <c r="E8" s="65">
         <v>424730</v>
       </c>
-      <c r="F8" s="64">
+      <c r="F8" s="65">
         <v>523580</v>
       </c>
-      <c r="G8" s="64">
+      <c r="G8" s="65">
         <v>598240</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="C9" s="64">
+        <v>301</v>
+      </c>
+      <c r="C9" s="65">
         <v>64516.25</v>
       </c>
-      <c r="D9" s="64">
+      <c r="D9" s="65">
         <v>79742.085</v>
       </c>
-      <c r="E9" s="64">
+      <c r="E9" s="65">
         <v>82134.34754999999</v>
       </c>
-      <c r="F9" s="64">
+      <c r="F9" s="65">
         <v>84598.3779765</v>
       </c>
-      <c r="G9" s="64">
+      <c r="G9" s="65">
         <v>87136.32931579501</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="C10" s="64">
+        <v>302</v>
+      </c>
+      <c r="C10" s="65">
         <v>33375</v>
       </c>
-      <c r="D10" s="64">
+      <c r="D10" s="65">
         <v>45803</v>
       </c>
-      <c r="E10" s="64">
+      <c r="E10" s="65">
         <v>52558.77</v>
       </c>
-      <c r="F10" s="64">
+      <c r="F10" s="65">
         <v>58262.168399999995</v>
       </c>
-      <c r="G10" s="64">
+      <c r="G10" s="65">
         <v>62801.356358000005</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="C11" s="64">
-        <v>0</v>
-      </c>
-      <c r="D11" s="64">
-        <v>0</v>
-      </c>
-      <c r="E11" s="64">
-        <v>0</v>
-      </c>
-      <c r="F11" s="64">
-        <v>0</v>
-      </c>
-      <c r="G11" s="64">
+        <v>303</v>
+      </c>
+      <c r="C11" s="65">
+        <v>0</v>
+      </c>
+      <c r="D11" s="65">
+        <v>0</v>
+      </c>
+      <c r="E11" s="65">
+        <v>0</v>
+      </c>
+      <c r="F11" s="65">
+        <v>0</v>
+      </c>
+      <c r="G11" s="65">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="C12" s="65">
+        <v>282</v>
+      </c>
+      <c r="C12" s="66">
         <v>69608.75</v>
       </c>
-      <c r="D12" s="65">
+      <c r="D12" s="66">
         <v>177434.91499999998</v>
       </c>
-      <c r="E12" s="65">
+      <c r="E12" s="66">
         <v>290036.88245000003</v>
       </c>
-      <c r="F12" s="65">
+      <c r="F12" s="66">
         <v>380719.4536235</v>
       </c>
-      <c r="G12" s="65">
+      <c r="G12" s="66">
         <v>448302.314326205</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="C13" s="65">
+        <v>347</v>
+      </c>
+      <c r="C13" s="66">
         <v>103100</v>
       </c>
-      <c r="D13" s="65">
+      <c r="D13" s="66">
         <v>280534.915</v>
       </c>
-      <c r="E13" s="65">
+      <c r="E13" s="66">
         <v>570571.79745</v>
       </c>
-      <c r="F13" s="65">
+      <c r="F13" s="66">
         <v>951291.2510735</v>
       </c>
-      <c r="G13" s="65">
+      <c r="G13" s="66">
         <v>1399593.565399705</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="C14" s="66">
+        <v>383</v>
+      </c>
+      <c r="C14" s="67">
         <v>0.41557462686567165</v>
       </c>
-      <c r="D14" s="66">
+      <c r="D14" s="67">
         <v>0.5856324344841243</v>
       </c>
-      <c r="E14" s="66">
+      <c r="E14" s="67">
         <v>0.6828735489605162</v>
       </c>
-      <c r="F14" s="66">
+      <c r="F14" s="67">
         <v>0.7271466702767485</v>
       </c>
-      <c r="G14" s="66">
+      <c r="G14" s="67">
         <v>0.7493686719814874</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="C15" s="67">
+        <v>251</v>
+      </c>
+      <c r="C15" s="68">
         <v>11166.666666666666</v>
       </c>
-      <c r="D15" s="67">
+      <c r="D15" s="68">
         <v>13771.818181818182</v>
       </c>
-      <c r="E15" s="67">
+      <c r="E15" s="68">
         <v>14157.666666666666</v>
       </c>
-      <c r="F15" s="67">
+      <c r="F15" s="68">
         <v>14543.888888888889</v>
       </c>
-      <c r="G15" s="67">
+      <c r="G15" s="68">
         <v>14956</v>
       </c>
-      <c r="H15" s="68" t="s">
-        <v>383</v>
+      <c r="H15" s="69" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="C16" s="69">
+        <v>285</v>
+      </c>
+      <c r="C16" s="70">
         <v>6526.083333333333</v>
       </c>
-      <c r="D16" s="69">
+      <c r="D16" s="70">
         <v>5706.594772727273</v>
       </c>
-      <c r="E16" s="69">
+      <c r="E16" s="70">
         <v>4489.770585</v>
       </c>
-      <c r="F16" s="69">
+      <c r="F16" s="70">
         <v>3968.348510458333</v>
       </c>
-      <c r="G16" s="69">
+      <c r="G16" s="70">
         <v>3748.442141844875</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="C17" s="64">
+        <v>406</v>
+      </c>
+      <c r="C17" s="65">
         <v>400</v>
       </c>
-      <c r="D17" s="64">
+      <c r="D17" s="65">
         <v>412</v>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="65">
         <v>424.35999999999996</v>
       </c>
-      <c r="F17" s="64">
+      <c r="F17" s="65">
         <v>437.0908</v>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="65">
         <v>450.20352400000013</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>385</v>
-      </c>
-      <c r="C18" s="67">
+        <v>407</v>
+      </c>
+      <c r="C18" s="68">
         <v>1720</v>
       </c>
-      <c r="D18" s="67">
+      <c r="D18" s="68">
         <v>1207.909090909091</v>
       </c>
-      <c r="E18" s="67">
+      <c r="E18" s="68">
         <v>912.3739999999999</v>
       </c>
-      <c r="F18" s="67">
+      <c r="F18" s="68">
         <v>783.1210166666666</v>
       </c>
-      <c r="G18" s="67">
+      <c r="G18" s="68">
         <v>725.9531824500001</v>
       </c>
-      <c r="H18" s="68" t="s">
-        <v>386</v>
+      <c r="H18" s="69" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="C19" s="70">
+        <v>409</v>
+      </c>
+      <c r="C19" s="71">
         <v>4640.583333333333</v>
       </c>
-      <c r="D19" s="70">
+      <c r="D19" s="71">
         <v>8065.223409090908</v>
       </c>
-      <c r="E19" s="70">
+      <c r="E19" s="71">
         <v>9667.896081666668</v>
       </c>
-      <c r="F19" s="70">
+      <c r="F19" s="71">
         <v>10575.540378430556</v>
       </c>
-      <c r="G19" s="70">
+      <c r="G19" s="71">
         <v>11207.557858155125</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="C20" s="66">
+        <v>410</v>
+      </c>
+      <c r="C20" s="67">
         <v>0.3851716417910448</v>
       </c>
-      <c r="D20" s="66">
+      <c r="D20" s="67">
         <v>0.2631925704666975</v>
       </c>
-      <c r="E20" s="66">
+      <c r="E20" s="67">
         <v>0.19338014161938172</v>
       </c>
-      <c r="F20" s="66">
+      <c r="F20" s="67">
         <v>0.16157679433228925</v>
       </c>
-      <c r="G20" s="66">
+      <c r="G20" s="67">
         <v>0.14565446863431902</v>
       </c>
-      <c r="H20" s="68" t="s">
-        <v>389</v>
+      <c r="H20" s="69" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="C21" s="71">
+        <v>412</v>
+      </c>
+      <c r="C21" s="72">
         <v>0.15402985074626865</v>
       </c>
-      <c r="D21" s="66">
+      <c r="D21" s="67">
         <v>0.08770875965410257</v>
       </c>
-      <c r="E21" s="66">
+      <c r="E21" s="67">
         <v>0.06444381136251265</v>
       </c>
-      <c r="F21" s="66">
+      <c r="F21" s="67">
         <v>0.0538453657511746</v>
       </c>
-      <c r="G21" s="66">
+      <c r="G21" s="67">
         <v>0.04853926066127307</v>
       </c>
-      <c r="H21" s="68" t="s">
-        <v>391</v>
+      <c r="H21" s="69" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="C22" s="66">
+        <v>414</v>
+      </c>
+      <c r="C22" s="67">
         <v>0.41557462686567165</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D22" s="67">
         <v>0.5856324344841243</v>
       </c>
-      <c r="E22" s="66">
+      <c r="E22" s="67">
         <v>0.682873548960516</v>
       </c>
-      <c r="F22" s="66">
+      <c r="F22" s="67">
         <v>0.7271466702767484</v>
       </c>
-      <c r="G22" s="66">
+      <c r="G22" s="67">
         <v>0.7493686719814874</v>
       </c>
-      <c r="H22" s="68" t="s">
-        <v>393</v>
+      <c r="H22" s="69" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="C23" s="72">
+        <v>416</v>
+      </c>
+      <c r="C23" s="73">
         <v>3</v>
       </c>
-      <c r="D23" s="72">
+      <c r="D23" s="73">
         <v>3</v>
       </c>
-      <c r="E23" s="72">
+      <c r="E23" s="73">
         <v>3</v>
       </c>
-      <c r="F23" s="72">
+      <c r="F23" s="73">
         <v>3</v>
       </c>
-      <c r="G23" s="72">
+      <c r="G23" s="73">
         <v>3</v>
       </c>
-      <c r="H23" s="68" t="s">
-        <v>395</v>
+      <c r="H23" s="69" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="C24" s="73" t="s">
-        <v>331</v>
-      </c>
-      <c r="D24" s="73" t="s">
-        <v>331</v>
-      </c>
-      <c r="E24" s="73" t="s">
-        <v>331</v>
-      </c>
-      <c r="F24" s="73" t="s">
-        <v>331</v>
-      </c>
-      <c r="G24" s="73" t="s">
-        <v>331</v>
-      </c>
-      <c r="H24" s="68" t="s">
-        <v>331</v>
+        <v>344</v>
+      </c>
+      <c r="C24" s="74" t="s">
+        <v>345</v>
+      </c>
+      <c r="D24" s="74" t="s">
+        <v>345</v>
+      </c>
+      <c r="E24" s="74" t="s">
+        <v>345</v>
+      </c>
+      <c r="F24" s="74" t="s">
+        <v>345</v>
+      </c>
+      <c r="G24" s="74" t="s">
+        <v>345</v>
+      </c>
+      <c r="H24" s="69" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="C25" s="42" t="str">
-        <f>IF('5-Year Operating Stmt'!B17&gt;=0,"✓ Break-even","")</f>
+        <v>418</v>
+      </c>
+      <c r="C25" s="43" t="str">
+        <f>IF('5-Year Operating Stmt'!B18&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="74" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C17&gt;=0,'5-Year Operating Stmt'!B17&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="74" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D17&gt;=0,'5-Year Operating Stmt'!C17&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="74" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E17&gt;=0,'5-Year Operating Stmt'!D17&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="74" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F17&gt;=0,'5-Year Operating Stmt'!E17&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="68" t="s">
-        <v>377</v>
+      <c r="D25" s="75" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!C18&gt;=0,'5-Year Operating Stmt'!B18&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="75" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!D18&gt;=0,'5-Year Operating Stmt'!C18&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="75" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!E18&gt;=0,'5-Year Operating Stmt'!D18&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="75" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!F18&gt;=0,'5-Year Operating Stmt'!E18&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="69" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="C26" s="75">
+        <v>419</v>
+      </c>
+      <c r="C26" s="76">
         <v>13</v>
       </c>
-      <c r="D26" s="72">
+      <c r="D26" s="73">
         <v>27</v>
       </c>
-      <c r="E26" s="72">
+      <c r="E26" s="73">
         <v>51</v>
       </c>
-      <c r="F26" s="76" t="s">
-        <v>398</v>
-      </c>
-      <c r="G26" s="76" t="s">
-        <v>398</v>
-      </c>
-      <c r="H26" s="68" t="s">
-        <v>399</v>
+      <c r="F26" s="77" t="s">
+        <v>420</v>
+      </c>
+      <c r="G26" s="77" t="s">
+        <v>420</v>
+      </c>
+      <c r="H26" s="69" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="C27" s="72">
+        <v>349</v>
+      </c>
+      <c r="C27" s="73">
         <v>384</v>
       </c>
-      <c r="D27" s="72">
+      <c r="D27" s="73">
         <v>816</v>
       </c>
-      <c r="E27" s="72">
+      <c r="E27" s="73">
         <v>1546</v>
       </c>
-      <c r="F27" s="72">
+      <c r="F27" s="73">
         <v>2430</v>
       </c>
-      <c r="G27" s="72">
+      <c r="G27" s="73">
         <v>3407</v>
       </c>
-      <c r="H27" s="68" t="s">
-        <v>400</v>
+      <c r="H27" s="69" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="44" t="s">
-        <v>405</v>
-      </c>
-      <c r="C30" s="42" t="s">
-        <v>406</v>
-      </c>
-      <c r="D30" s="77" t="s">
-        <v>407</v>
-      </c>
-      <c r="E30" s="77"/>
-      <c r="F30" s="78" t="s">
-        <v>408</v>
-      </c>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
-      <c r="I30" s="78"/>
+      <c r="B30" s="45" t="s">
+        <v>427</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="D30" s="78" t="s">
+        <v>429</v>
+      </c>
+      <c r="E30" s="78"/>
+      <c r="F30" s="79" t="s">
+        <v>430</v>
+      </c>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="79"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="44" t="s">
-        <v>409</v>
-      </c>
-      <c r="C31" s="42" t="s">
-        <v>406</v>
-      </c>
-      <c r="D31" s="77" t="s">
-        <v>410</v>
-      </c>
-      <c r="E31" s="77"/>
-      <c r="F31" s="78" t="s">
-        <v>411</v>
-      </c>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="78"/>
+      <c r="B31" s="45" t="s">
+        <v>431</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="D31" s="78" t="s">
+        <v>432</v>
+      </c>
+      <c r="E31" s="78"/>
+      <c r="F31" s="79" t="s">
+        <v>433</v>
+      </c>
+      <c r="G31" s="79"/>
+      <c r="H31" s="79"/>
+      <c r="I31" s="79"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="44" t="s">
-        <v>412</v>
-      </c>
-      <c r="C32" s="42" t="s">
-        <v>406</v>
-      </c>
-      <c r="D32" s="77" t="s">
-        <v>413</v>
-      </c>
-      <c r="E32" s="77"/>
-      <c r="F32" s="78" t="s">
-        <v>414</v>
-      </c>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="78"/>
+      <c r="B32" s="45" t="s">
+        <v>434</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="D32" s="78" t="s">
+        <v>435</v>
+      </c>
+      <c r="E32" s="78"/>
+      <c r="F32" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="G32" s="79"/>
+      <c r="H32" s="79"/>
+      <c r="I32" s="79"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="44" t="s">
-        <v>415</v>
-      </c>
-      <c r="C33" s="42" t="s">
-        <v>406</v>
-      </c>
-      <c r="D33" s="77" t="s">
-        <v>416</v>
-      </c>
-      <c r="E33" s="77"/>
-      <c r="F33" s="78" t="s">
-        <v>417</v>
-      </c>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
+      <c r="B33" s="45" t="s">
+        <v>437</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="D33" s="78" t="s">
+        <v>438</v>
+      </c>
+      <c r="E33" s="78"/>
+      <c r="F33" s="79" t="s">
+        <v>439</v>
+      </c>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="79"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="44" t="s">
-        <v>418</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>406</v>
-      </c>
-      <c r="D34" s="77" t="s">
-        <v>419</v>
-      </c>
-      <c r="E34" s="77"/>
-      <c r="F34" s="78" t="s">
-        <v>420</v>
-      </c>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
+      <c r="B34" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="D34" s="78" t="s">
+        <v>441</v>
+      </c>
+      <c r="E34" s="78"/>
+      <c r="F34" s="79" t="s">
+        <v>442</v>
+      </c>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="44" t="s">
-        <v>421</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>406</v>
-      </c>
-      <c r="D35" s="77" t="s">
-        <v>422</v>
-      </c>
-      <c r="E35" s="77"/>
-      <c r="F35" s="78" t="s">
-        <v>423</v>
-      </c>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
-      <c r="I35" s="78"/>
+      <c r="B35" s="45" t="s">
+        <v>443</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="D35" s="78" t="s">
+        <v>444</v>
+      </c>
+      <c r="E35" s="78"/>
+      <c r="F35" s="79" t="s">
+        <v>445</v>
+      </c>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="44" t="s">
-        <v>424</v>
+      <c r="B37" s="45" t="s">
+        <v>446</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="79" t="s">
-        <v>426</v>
-      </c>
-      <c r="C39" s="79"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="79"/>
-      <c r="F39" s="79"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="79"/>
-      <c r="I39" s="79"/>
+      <c r="B39" s="80" t="s">
+        <v>448</v>
+      </c>
+      <c r="C39" s="80"/>
+      <c r="D39" s="80"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="80"/>
+      <c r="G39" s="80"/>
+      <c r="H39" s="80"/>
+      <c r="I39" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -7354,111 +7633,111 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="B3" s="19"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="80" t="s">
-        <v>428</v>
-      </c>
-      <c r="B4" s="80"/>
+      <c r="A4" s="81" t="s">
+        <v>450</v>
+      </c>
+      <c r="B4" s="81"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="B6" s="19"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="80" t="s">
-        <v>428</v>
-      </c>
-      <c r="B7" s="80"/>
+      <c r="A7" s="81" t="s">
+        <v>450</v>
+      </c>
+      <c r="B7" s="81"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="B9" s="19"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="80" t="s">
-        <v>428</v>
-      </c>
-      <c r="B10" s="80"/>
+      <c r="A10" s="81" t="s">
+        <v>450</v>
+      </c>
+      <c r="B10" s="81"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="B12" s="19"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="80" t="s">
-        <v>428</v>
-      </c>
-      <c r="B13" s="80"/>
+      <c r="A13" s="81" t="s">
+        <v>450</v>
+      </c>
+      <c r="B13" s="81"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B15" s="19"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="80" t="s">
-        <v>428</v>
-      </c>
-      <c r="B16" s="80"/>
+      <c r="A16" s="81" t="s">
+        <v>450</v>
+      </c>
+      <c r="B16" s="81"/>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="B18" s="19"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="80" t="s">
-        <v>428</v>
-      </c>
-      <c r="B19" s="80"/>
+      <c r="A19" s="81" t="s">
+        <v>450</v>
+      </c>
+      <c r="B19" s="81"/>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="B21" s="19"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="80" t="s">
-        <v>428</v>
-      </c>
-      <c r="B22" s="80"/>
+      <c r="A22" s="81" t="s">
+        <v>450</v>
+      </c>
+      <c r="B22" s="81"/>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="B24" s="19"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="80" t="s">
-        <v>428</v>
-      </c>
-      <c r="B25" s="80"/>
+      <c r="A25" s="81" t="s">
+        <v>450</v>
+      </c>
+      <c r="B25" s="81"/>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="B27" s="19"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="80" t="s">
-        <v>428</v>
-      </c>
-      <c r="B28" s="80"/>
+      <c r="A28" s="81" t="s">
+        <v>450</v>
+      </c>
+      <c r="B28" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -7486,6 +7765,52 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="81" t="s">
+        <v>459</v>
+      </c>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -7496,24 +7821,24 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
-        <v>438</v>
-      </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
+      <c r="A2" s="82" t="s">
+        <v>461</v>
+      </c>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
-        <v>439</v>
-      </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
+      <c r="A4" s="83" t="s">
+        <v>462</v>
+      </c>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7529,7 +7854,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -7550,7 +7875,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="15" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -7560,26 +7885,26 @@
       <c r="H1" s="15"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="83" t="s">
-        <v>441</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
+      <c r="B2" s="84" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="84" t="s">
-        <v>442</v>
-      </c>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
+      <c r="B4" s="85" t="s">
+        <v>465</v>
+      </c>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7600,7 +7925,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -7610,7 +7935,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -7624,18 +7949,18 @@
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -7678,10 +8003,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -7702,7 +8027,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B12" s="20">
         <v>7</v>
@@ -7710,7 +8035,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" s="20">
         <v>40</v>
@@ -7718,7 +8043,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -7731,24 +8056,24 @@
         <v>7</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B17" s="22">
         <v>15</v>
@@ -7768,7 +8093,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7779,33 +8104,33 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D21" s="23">
         <v>6000</v>
@@ -7814,18 +8139,18 @@
         <v>0</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>121</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>119</v>
       </c>
       <c r="D22" s="23">
         <v>200</v>
@@ -7834,18 +8159,18 @@
         <v>0</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D23" s="23">
         <v>7000</v>
@@ -7854,18 +8179,18 @@
         <v>0</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D24" s="23">
         <v>3000</v>
@@ -7874,250 +8199,302 @@
         <v>0</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="E27" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="B28" s="25">
+        <v>0</v>
+      </c>
+      <c r="C28" s="25">
+        <v>0</v>
+      </c>
+      <c r="D28" s="25">
+        <v>0</v>
+      </c>
+      <c r="E28" s="25">
+        <v>0</v>
+      </c>
+      <c r="F28" s="25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="B29" s="25">
+        <v>77500</v>
+      </c>
+      <c r="C29" s="25">
+        <v>140360</v>
+      </c>
+      <c r="D29" s="25">
+        <v>196962</v>
+      </c>
+      <c r="E29" s="25">
+        <v>243229.032</v>
+      </c>
+      <c r="F29" s="25">
+        <v>278122.1144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="B30" s="25">
+        <v>2500</v>
+      </c>
+      <c r="C30" s="25">
+        <v>3090</v>
+      </c>
+      <c r="D30" s="25">
+        <v>3182.7</v>
+      </c>
+      <c r="E30" s="25">
+        <v>3278.181</v>
+      </c>
+      <c r="F30" s="25">
+        <v>3376.5264300000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B31" s="25">
+        <v>87500</v>
+      </c>
+      <c r="C31" s="25">
+        <v>158620</v>
+      </c>
+      <c r="D31" s="25">
+        <v>222788.99999999997</v>
+      </c>
+      <c r="E31" s="25">
+        <v>275367.204</v>
+      </c>
+      <c r="F31" s="25">
+        <v>315142.46680000005</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="B32" s="26">
+        <v>0</v>
+      </c>
+      <c r="C32" s="26">
+        <v>0</v>
+      </c>
+      <c r="D32" s="26">
+        <v>0</v>
+      </c>
+      <c r="E32" s="26">
+        <v>0</v>
+      </c>
+      <c r="F32" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D28" s="25">
+      <c r="B33" s="26">
+        <v>0.4626865671641791</v>
+      </c>
+      <c r="C33" s="26">
+        <v>0.4646605091535075</v>
+      </c>
+      <c r="D33" s="26">
+        <v>0.46570419902693966</v>
+      </c>
+      <c r="E33" s="26">
+        <v>0.46606812688425003</v>
+      </c>
+      <c r="F33" s="26">
+        <v>0.4661464167374705</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B34" s="26">
+        <v>0.014925373134328358</v>
+      </c>
+      <c r="C34" s="26">
+        <v>0.010229417022544443</v>
+      </c>
+      <c r="D34" s="26">
+        <v>0.007525292971451553</v>
+      </c>
+      <c r="E34" s="26">
+        <v>0.006281551448420588</v>
+      </c>
+      <c r="F34" s="26">
+        <v>0.005659225264267096</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="26">
+        <v>0.5223880597014925</v>
+      </c>
+      <c r="C35" s="26">
+        <v>0.5251100738239481</v>
+      </c>
+      <c r="D35" s="26">
+        <v>0.5267705080016086</v>
+      </c>
+      <c r="E35" s="26">
+        <v>0.5276503216673294</v>
+      </c>
+      <c r="F35" s="26">
+        <v>0.5281943579982623</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="27">
+        <v>0</v>
+      </c>
+      <c r="C36" s="27">
+        <v>0</v>
+      </c>
+      <c r="D36" s="27">
+        <v>0</v>
+      </c>
+      <c r="E36" s="27">
+        <v>0</v>
+      </c>
+      <c r="F36" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+    </row>
+    <row r="39" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" s="28">
         <v>1</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E40" s="23">
         <v>48000</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F40" s="24">
         <v>0.2</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G40" s="24">
         <v>0.0765</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D29" s="25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" s="28">
         <v>0.5</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E41" s="23">
         <v>30000</v>
       </c>
-      <c r="F29" s="24">
-        <v>0</v>
-      </c>
-      <c r="G29" s="24">
+      <c r="F41" s="24">
+        <v>0</v>
+      </c>
+      <c r="G41" s="24">
         <v>0.0765</v>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-    </row>
-    <row r="32" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D33" s="23">
-        <v>1800</v>
-      </c>
-      <c r="E33" s="24">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D34" s="23">
-        <v>200</v>
-      </c>
-      <c r="E34" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35" s="23">
-        <v>1800</v>
-      </c>
-      <c r="E35" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D36" s="23">
-        <v>4500</v>
-      </c>
-      <c r="E36" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D37" s="23">
-        <v>400</v>
-      </c>
-      <c r="E37" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" s="23">
-        <v>250</v>
-      </c>
-      <c r="E38" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-    </row>
-    <row r="41" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B43" s="19"/>
       <c r="C43" s="19"/>
@@ -8126,116 +8503,183 @@
       <c r="F43" s="19"/>
       <c r="G43" s="19"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
+    <row r="44" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B44" s="24">
+      <c r="D45" s="23">
+        <v>1800</v>
+      </c>
+      <c r="E45" s="24">
         <v>0.03</v>
       </c>
-      <c r="C44" s="26" t="s">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
+      <c r="B46" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D46" s="23">
+        <v>200</v>
+      </c>
+      <c r="E46" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B45" s="24">
+      <c r="B47" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" s="23">
+        <v>1800</v>
+      </c>
+      <c r="E47" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="23">
+        <v>4500</v>
+      </c>
+      <c r="E48" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D49" s="23">
+        <v>400</v>
+      </c>
+      <c r="E49" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D50" s="23">
+        <v>250</v>
+      </c>
+      <c r="E50" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+    </row>
+    <row r="53" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B56" s="24">
         <v>0.03</v>
       </c>
-      <c r="C45" s="26" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B46" s="25">
-        <v>0.8333333333333334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B47" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B49" s="24">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B50" s="24">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B51" s="24">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B52" s="24">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B53" s="24">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="B54" s="24">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="56" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="19" t="s">
+      <c r="C56" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="24">
+        <v>0.03</v>
+      </c>
+      <c r="C57" s="29" t="s">
         <v>172</v>
       </c>
     </row>
@@ -8243,113 +8687,204 @@
       <c r="A58" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="B58" s="20" t="s">
-        <v>174</v>
+      <c r="B58" s="28">
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="B59" s="24">
-        <v>1</v>
+        <v>174</v>
+      </c>
+      <c r="B59" s="23">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B60" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="B60" s="20" t="s">
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="62" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="19" t="s">
+      <c r="B61" s="24">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-    </row>
-    <row r="63" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="21" t="s">
+      <c r="B62" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="B63" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C63" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="E63" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="F63" s="21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B63" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B64" s="22">
-        <v>3</v>
-      </c>
-      <c r="C64" s="22">
-        <v>4</v>
-      </c>
-      <c r="D64" s="22">
-        <v>5</v>
-      </c>
-      <c r="E64" s="22">
-        <v>6</v>
-      </c>
-      <c r="F64" s="22">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B64" s="24">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B65" s="22">
-        <v>2</v>
-      </c>
-      <c r="C65" s="22">
-        <v>3</v>
-      </c>
-      <c r="D65" s="22">
-        <v>4</v>
-      </c>
-      <c r="E65" s="22">
-        <v>5</v>
-      </c>
-      <c r="F65" s="22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B65" s="24">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="B66" s="22">
+      <c r="B66" s="24">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B71" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
+    </row>
+    <row r="75" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E75" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F75" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B76" s="22">
+        <v>3</v>
+      </c>
+      <c r="C76" s="22">
+        <v>4</v>
+      </c>
+      <c r="D76" s="22">
         <v>5</v>
       </c>
-      <c r="C66" s="22">
+      <c r="E76" s="22">
+        <v>6</v>
+      </c>
+      <c r="F76" s="22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B77" s="22">
+        <v>2</v>
+      </c>
+      <c r="C77" s="22">
+        <v>3</v>
+      </c>
+      <c r="D77" s="22">
+        <v>4</v>
+      </c>
+      <c r="E77" s="22">
+        <v>5</v>
+      </c>
+      <c r="F77" s="22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B78" s="22">
+        <v>5</v>
+      </c>
+      <c r="C78" s="22">
         <v>7</v>
       </c>
-      <c r="D66" s="22">
+      <c r="D78" s="22">
         <v>9</v>
       </c>
-      <c r="E66" s="22">
+      <c r="E78" s="22">
         <v>10</v>
       </c>
-      <c r="F66" s="22">
+      <c r="F78" s="22">
         <v>12</v>
       </c>
     </row>
@@ -8385,10 +8920,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -8409,10 +8944,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -8425,7 +8960,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -8433,66 +8968,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -8535,24 +9070,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -8562,27 +9097,27 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B6" s="27">
+        <v>111</v>
+      </c>
+      <c r="B6" s="30">
         <v>15</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="30">
         <v>22</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="30">
         <v>30</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="30">
         <v>36</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="30">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B7" s="22">
         <v>40</v>
@@ -8590,56 +9125,56 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="B8" s="28">
+        <v>213</v>
+      </c>
+      <c r="B8" s="31">
         <f>B6/$B$7</f>
         <v>0.375</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="31">
         <f>C6/$B$7</f>
         <v>0.55</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="31">
         <f>D6/$B$7</f>
         <v>0.75</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="31">
         <f>E6/$B$7</f>
         <v>0.9</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="31">
         <f>F6/$B$7</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="C10" s="29">
+        <v>214</v>
+      </c>
+      <c r="C10" s="26">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
         <v>0.46666667</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="26">
         <f>IF(C6=0,0,(D6-C6)/C6)</f>
         <v>0.36363636</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="26">
         <f>IF(D6=0,0,(E6-D6)/D6)</f>
         <v>0.2</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="26">
         <f>IF(E6=0,0,(F6-E6)/E6)</f>
         <v>0.11111111</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -8649,125 +9184,125 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B14" s="30">
-        <f>Assumptions!B64</f>
+        <v>193</v>
+      </c>
+      <c r="B14" s="32">
+        <f>Assumptions!B76</f>
         <v>3</v>
       </c>
-      <c r="C14" s="30">
-        <f>Assumptions!C64</f>
+      <c r="C14" s="32">
+        <f>Assumptions!C76</f>
         <v>4</v>
       </c>
-      <c r="D14" s="30">
-        <f>Assumptions!D64</f>
+      <c r="D14" s="32">
+        <f>Assumptions!D76</f>
         <v>5</v>
       </c>
-      <c r="E14" s="30">
-        <f>Assumptions!E64</f>
+      <c r="E14" s="32">
+        <f>Assumptions!E76</f>
         <v>6</v>
       </c>
-      <c r="F14" s="30">
-        <f>Assumptions!F64</f>
+      <c r="F14" s="32">
+        <f>Assumptions!F76</f>
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B15" s="30">
-        <f>Assumptions!B65</f>
+        <v>194</v>
+      </c>
+      <c r="B15" s="32">
+        <f>Assumptions!B77</f>
         <v>2</v>
       </c>
-      <c r="C15" s="30">
-        <f>Assumptions!C65</f>
+      <c r="C15" s="32">
+        <f>Assumptions!C77</f>
         <v>3</v>
       </c>
-      <c r="D15" s="30">
-        <f>Assumptions!D65</f>
+      <c r="D15" s="32">
+        <f>Assumptions!D77</f>
         <v>4</v>
       </c>
-      <c r="E15" s="30">
-        <f>Assumptions!E65</f>
+      <c r="E15" s="32">
+        <f>Assumptions!E77</f>
         <v>5</v>
       </c>
-      <c r="F15" s="30">
-        <f>Assumptions!F65</f>
+      <c r="F15" s="32">
+        <f>Assumptions!F77</f>
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B16" s="30">
-        <f>Assumptions!B66</f>
+        <v>195</v>
+      </c>
+      <c r="B16" s="32">
+        <f>Assumptions!B78</f>
         <v>5</v>
       </c>
-      <c r="C16" s="30">
-        <f>Assumptions!C66</f>
+      <c r="C16" s="32">
+        <f>Assumptions!C78</f>
         <v>7</v>
       </c>
-      <c r="D16" s="30">
-        <f>Assumptions!D66</f>
+      <c r="D16" s="32">
+        <f>Assumptions!D78</f>
         <v>9</v>
       </c>
-      <c r="E16" s="30">
-        <f>Assumptions!E66</f>
+      <c r="E16" s="32">
+        <f>Assumptions!E78</f>
         <v>10</v>
       </c>
-      <c r="F16" s="30">
-        <f>Assumptions!F66</f>
+      <c r="F16" s="32">
+        <f>Assumptions!F78</f>
         <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B17" s="27">
+        <v>215</v>
+      </c>
+      <c r="B17" s="30">
         <f>B14+B15+B16</f>
         <v>10</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="30">
         <f>C14+C15+C16</f>
         <v>14</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="30">
         <f>D14+D15+D16</f>
         <v>18</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="30">
         <f>E14+E15+E16</f>
         <v>21</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="30">
         <f>F14+F15+F16</f>
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="B18" s="28">
+        <v>216</v>
+      </c>
+      <c r="B18" s="31">
         <f>IF(B6=0,0,B17/B6)</f>
         <v>0.66666667</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="31">
         <f>IF(C6=0,0,C17/C6)</f>
         <v>0.63636364</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="31">
         <f>IF(D6=0,0,D17/D6)</f>
         <v>0.6</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="31">
         <f>IF(E6=0,0,E17/E6)</f>
         <v>0.58333333</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="31">
         <f>IF(F6=0,0,F17/F6)</f>
         <v>0.575</v>
       </c>
@@ -8798,7 +9333,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8811,24 +9346,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -8838,72 +9373,72 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="31">
+        <v>119</v>
+      </c>
+      <c r="B5" s="25">
         <v>90000</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="25">
         <v>135960</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="25">
         <v>190962</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="25">
         <v>236029</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="25">
         <v>270122</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="31">
+        <v>123</v>
+      </c>
+      <c r="B6" s="25">
         <v>3000</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="25">
         <v>4400</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="25">
         <v>6000</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="25">
         <v>7200</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="25">
         <v>8000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="B7" s="32">
+        <v>219</v>
+      </c>
+      <c r="B7" s="33">
         <f>SUM(B5,B6)</f>
         <v>93000</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <f>SUM(C5,C6)</f>
         <v>140360</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="33">
         <f>SUM(D5,D6)</f>
         <v>196962</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="33">
         <f>SUM(E5,E6)</f>
         <v>243229</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="33">
         <f>SUM(F5,F6)</f>
         <v>278122</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -8913,52 +9448,52 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="31">
+        <v>124</v>
+      </c>
+      <c r="B9" s="25">
         <v>105000</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="25">
         <v>158620</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="25">
         <v>222789</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="25">
         <v>275367</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="25">
         <v>315142</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="B10" s="32">
+        <v>221</v>
+      </c>
+      <c r="B10" s="33">
         <f>SUM(B9)</f>
         <v>105000</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="33">
         <f>SUM(C9)</f>
         <v>158620</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="33">
         <f>SUM(D9)</f>
         <v>222789</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="33">
         <f>SUM(E9)</f>
         <v>275367</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="33">
         <f>SUM(F9)</f>
         <v>315142</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -8968,70 +9503,70 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B12" s="23">
         <v>3000</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="25">
         <v>3090</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="25">
         <v>3183</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="25">
         <v>3278</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="25">
         <v>3377</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="B13" s="32">
+        <v>223</v>
+      </c>
+      <c r="B13" s="33">
         <f>SUM(B12)</f>
         <v>3000</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <f>SUM(C12)</f>
         <v>3090</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="33">
         <f>SUM(D12)</f>
         <v>3183</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="33">
         <f>SUM(E12)</f>
         <v>3278</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <f>SUM(F12)</f>
         <v>3377</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="B15" s="33">
+        <v>224</v>
+      </c>
+      <c r="B15" s="34">
         <f>SUM(B7,B10,B13)</f>
         <v>201000</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="34">
         <f>SUM(C7,C10,C13)</f>
         <v>302070</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="34">
         <f>SUM(D7,D10,D13)</f>
         <v>422934</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="34">
         <f>SUM(E7,E10,E13)</f>
         <v>521874</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="34">
         <f>SUM(F7,F10,F13)</f>
         <v>596641</v>
       </c>
@@ -9079,38 +9614,38 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="25">
+        <v>148</v>
+      </c>
+      <c r="C4" s="28">
         <v>1</v>
       </c>
       <c r="D4" s="23">
@@ -9122,21 +9657,21 @@
       <c r="F4" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="34">
+      <c r="G4" s="35">
         <v>61272</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="25">
+        <v>151</v>
+      </c>
+      <c r="C5" s="28">
         <v>0.5</v>
       </c>
       <c r="D5" s="23">
@@ -9148,16 +9683,16 @@
       <c r="F5" s="24">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="35">
         <v>16148</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -9170,78 +9705,78 @@
         <v>7</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="B9" s="33">
+        <v>229</v>
+      </c>
+      <c r="B9" s="34">
         <v>64516</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <v>79742</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="34">
         <v>82134</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="34">
         <v>84598</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="34">
         <v>87136</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="29">
+        <v>230</v>
+      </c>
+      <c r="B10" s="26">
         <v>0.320976368159204</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="26">
         <v>0.2639854503922932</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="26">
         <v>0.1942014730677645</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="26">
         <v>0.16210485745366593</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="26">
         <v>0.14604479678230883</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B11" s="35">
+        <v>231</v>
+      </c>
+      <c r="B11" s="36">
         <v>10</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="36">
         <v>14.7</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="36">
         <v>20</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="36">
         <v>24</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="36">
         <v>26.7</v>
       </c>
     </row>
@@ -9271,7 +9806,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9284,24 +9819,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -9311,52 +9846,52 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="B5" s="31">
+        <v>233</v>
+      </c>
+      <c r="B5" s="25">
         <v>6000</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="25">
         <v>9064</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="25">
         <v>12731</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="25">
         <v>15735</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="25">
         <v>18008</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="B6" s="32">
+        <v>234</v>
+      </c>
+      <c r="B6" s="33">
         <f>SUM(B5:B5)</f>
         <v>6000</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="33">
         <f>SUM(C5:C5)</f>
         <v>9064</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="33">
         <f>SUM(D5:D5)</f>
         <v>12731</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="33">
         <f>SUM(E5:E5)</f>
         <v>15735</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="33">
         <f>SUM(F5:F5)</f>
         <v>18008</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -9366,52 +9901,52 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B8" s="31">
+        <v>235</v>
+      </c>
+      <c r="B8" s="25">
         <v>3750</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="25">
         <v>5665</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="25">
         <v>7957</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="25">
         <v>9835</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="25">
         <v>11255</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="B9" s="32">
+        <v>236</v>
+      </c>
+      <c r="B9" s="33">
         <f>SUM(B8:B8)</f>
         <v>3750</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <f>SUM(C8:C8)</f>
         <v>5665</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <f>SUM(D8:D8)</f>
         <v>7957</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <f>SUM(E8:E8)</f>
         <v>9835</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <f>SUM(F8:F8)</f>
         <v>11255</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -9421,92 +9956,92 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="B11" s="31">
+        <v>237</v>
+      </c>
+      <c r="B11" s="25">
         <v>21600</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="25">
         <v>22248</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="25">
         <v>22915</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="25">
         <v>23603</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="25">
         <v>24311</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B12" s="31">
+        <v>238</v>
+      </c>
+      <c r="B12" s="25">
         <v>2400</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="25">
         <v>2472</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="25">
         <v>2546</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="25">
         <v>2623</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="25">
         <v>2701</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="B13" s="31">
+        <v>239</v>
+      </c>
+      <c r="B13" s="25">
         <v>1800</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="25">
         <v>1854</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="25">
         <v>1910</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="25">
         <v>1967</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="25">
         <v>2026</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="B14" s="32">
+        <v>240</v>
+      </c>
+      <c r="B14" s="33">
         <f>SUM(B11:B13)</f>
         <v>25800</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>SUM(C11:C13)</f>
         <v>26574</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <f>SUM(D11:D13)</f>
         <v>27371</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>SUM(E11:E13)</f>
         <v>28192</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>SUM(F11:F13)</f>
         <v>29038</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -9516,70 +10051,70 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B16" s="31">
+        <v>241</v>
+      </c>
+      <c r="B16" s="25">
         <v>4500</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="25">
         <v>4500</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="25">
         <v>4500</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="25">
         <v>4500</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="25">
         <v>4500</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="B17" s="32">
+        <v>242</v>
+      </c>
+      <c r="B17" s="33">
         <f>SUM(B16:B16)</f>
         <v>4500</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>SUM(C16:C16)</f>
         <v>4500</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="33">
         <f>SUM(D16:D16)</f>
         <v>4500</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <f>SUM(E16:E16)</f>
         <v>4500</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="33">
         <f>SUM(F16:F16)</f>
         <v>4500</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="B19" s="33">
+        <v>243</v>
+      </c>
+      <c r="B19" s="34">
         <f>B6+B9+B14+B17</f>
         <v>40050</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="34">
         <f>C6+C9+C14+C17</f>
         <v>45803</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="34">
         <f>D6+D9+D14+D17</f>
         <v>52559</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="34">
         <f>E6+E9+E14+E17</f>
         <v>58262</v>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="34">
         <f>F6+F9+F14+F17</f>
         <v>62801</v>
       </c>
@@ -9611,7 +10146,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9621,37 +10156,37 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="F5" s="33">
+        <v>246</v>
+      </c>
+      <c r="F5" s="34">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="F6" s="32">
+        <v>247</v>
+      </c>
+      <c r="F6" s="33">
         <v>0</v>
       </c>
     </row>
